--- a/SDHL 2026-2027 scoring chances.xlsx
+++ b/SDHL 2026-2027 scoring chances.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikko\Documents\Luleå Damjun\Advanced stats_data\SDHL stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAB19D44-8BD6-4D8D-AEBD-780E51D46E18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A77E08C-600D-4CE3-8392-7EEE67BA753F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
+    <workbookView xWindow="33480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="48">
   <si>
     <t>Goal For</t>
   </si>
@@ -559,7 +559,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4EB1DA-C9FF-4BF6-849D-6254FD5C05A8}">
-  <dimension ref="A1:P43"/>
+  <dimension ref="A1:P64"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="10.08984375" style="2" bestFit="1" customWidth="1"/>
@@ -2715,6 +2715,1056 @@
         <v>0</v>
       </c>
     </row>
+    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A44">
+        <v>3</v>
+      </c>
+      <c r="B44" t="s">
+        <v>46</v>
+      </c>
+      <c r="C44" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D44">
+        <v>81</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+      <c r="F44">
+        <v>0</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+      <c r="H44">
+        <v>0</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>0</v>
+      </c>
+      <c r="K44">
+        <v>0</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>1</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A45">
+        <v>3</v>
+      </c>
+      <c r="B45" t="s">
+        <v>46</v>
+      </c>
+      <c r="C45" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D45">
+        <v>15</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>1</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+      <c r="H45">
+        <v>0</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>1</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>1</v>
+      </c>
+      <c r="N45">
+        <v>2</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A46">
+        <v>3</v>
+      </c>
+      <c r="B46" t="s">
+        <v>46</v>
+      </c>
+      <c r="C46" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D46">
+        <v>11</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+      <c r="F46">
+        <v>0</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+      <c r="H46">
+        <v>0</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>0</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>0</v>
+      </c>
+      <c r="N46">
+        <v>0</v>
+      </c>
+      <c r="O46">
+        <v>0</v>
+      </c>
+      <c r="P46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A47">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D47">
+        <v>25</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+      <c r="F47">
+        <v>0</v>
+      </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
+      <c r="H47">
+        <v>0</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>0</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A48">
+        <v>3</v>
+      </c>
+      <c r="B48" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D48">
+        <v>39</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+      <c r="F48">
+        <v>1</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+      <c r="H48">
+        <v>0</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>0</v>
+      </c>
+      <c r="K48">
+        <v>0</v>
+      </c>
+      <c r="L48">
+        <v>0</v>
+      </c>
+      <c r="M48">
+        <v>0</v>
+      </c>
+      <c r="N48">
+        <v>0</v>
+      </c>
+      <c r="O48">
+        <v>0</v>
+      </c>
+      <c r="P48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A49">
+        <v>3</v>
+      </c>
+      <c r="B49" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D49">
+        <v>13</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49">
+        <v>0</v>
+      </c>
+      <c r="G49">
+        <v>2</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>0</v>
+      </c>
+      <c r="L49">
+        <v>0</v>
+      </c>
+      <c r="M49">
+        <v>0</v>
+      </c>
+      <c r="N49">
+        <v>0</v>
+      </c>
+      <c r="O49">
+        <v>0</v>
+      </c>
+      <c r="P49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A50">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D50">
+        <v>27</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50">
+        <v>1</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+      <c r="H50">
+        <v>2</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>0</v>
+      </c>
+      <c r="K50">
+        <v>0</v>
+      </c>
+      <c r="L50">
+        <v>0</v>
+      </c>
+      <c r="M50">
+        <v>0</v>
+      </c>
+      <c r="N50">
+        <v>1</v>
+      </c>
+      <c r="O50">
+        <v>0</v>
+      </c>
+      <c r="P50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A51">
+        <v>3</v>
+      </c>
+      <c r="B51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D51">
+        <v>9</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+      <c r="F51">
+        <v>0</v>
+      </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
+      <c r="H51">
+        <v>0</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>0</v>
+      </c>
+      <c r="L51">
+        <v>0</v>
+      </c>
+      <c r="M51">
+        <v>0</v>
+      </c>
+      <c r="N51">
+        <v>2</v>
+      </c>
+      <c r="O51">
+        <v>0</v>
+      </c>
+      <c r="P51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A52">
+        <v>3</v>
+      </c>
+      <c r="B52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D52">
+        <v>24</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>0</v>
+      </c>
+      <c r="K52">
+        <v>0</v>
+      </c>
+      <c r="L52">
+        <v>0</v>
+      </c>
+      <c r="M52">
+        <v>0</v>
+      </c>
+      <c r="N52">
+        <v>0</v>
+      </c>
+      <c r="O52">
+        <v>0</v>
+      </c>
+      <c r="P52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A53">
+        <v>3</v>
+      </c>
+      <c r="B53" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D53">
+        <v>19</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>0</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+      <c r="H53">
+        <v>0</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>0</v>
+      </c>
+      <c r="K53">
+        <v>0</v>
+      </c>
+      <c r="L53">
+        <v>0</v>
+      </c>
+      <c r="M53">
+        <v>0</v>
+      </c>
+      <c r="N53">
+        <v>0</v>
+      </c>
+      <c r="O53">
+        <v>0</v>
+      </c>
+      <c r="P53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A54">
+        <v>3</v>
+      </c>
+      <c r="B54" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D54">
+        <v>44</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+      <c r="F54">
+        <v>0</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+      <c r="H54">
+        <v>0</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>0</v>
+      </c>
+      <c r="K54">
+        <v>0</v>
+      </c>
+      <c r="L54">
+        <v>0</v>
+      </c>
+      <c r="M54">
+        <v>0</v>
+      </c>
+      <c r="N54">
+        <v>0</v>
+      </c>
+      <c r="O54">
+        <v>0</v>
+      </c>
+      <c r="P54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A55">
+        <v>3</v>
+      </c>
+      <c r="B55" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D55">
+        <v>6</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+      <c r="F55">
+        <v>0</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+      <c r="H55">
+        <v>0</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>1</v>
+      </c>
+      <c r="L55">
+        <v>0</v>
+      </c>
+      <c r="M55">
+        <v>0</v>
+      </c>
+      <c r="N55">
+        <v>3</v>
+      </c>
+      <c r="O55">
+        <v>0</v>
+      </c>
+      <c r="P55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A56">
+        <v>3</v>
+      </c>
+      <c r="B56" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D56">
+        <v>8</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>0</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>0</v>
+      </c>
+      <c r="L56">
+        <v>0</v>
+      </c>
+      <c r="M56">
+        <v>0</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+      <c r="O56">
+        <v>0</v>
+      </c>
+      <c r="P56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D57">
+        <v>72</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+      <c r="F57">
+        <v>2</v>
+      </c>
+      <c r="G57">
+        <v>0</v>
+      </c>
+      <c r="H57">
+        <v>0</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>0</v>
+      </c>
+      <c r="K57">
+        <v>0</v>
+      </c>
+      <c r="L57">
+        <v>1</v>
+      </c>
+      <c r="M57">
+        <v>0</v>
+      </c>
+      <c r="N57">
+        <v>2</v>
+      </c>
+      <c r="O57">
+        <v>0</v>
+      </c>
+      <c r="P57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A58">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D58">
+        <v>21</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+      <c r="F58">
+        <v>0</v>
+      </c>
+      <c r="G58">
+        <v>0</v>
+      </c>
+      <c r="H58">
+        <v>0</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>0</v>
+      </c>
+      <c r="K58">
+        <v>0</v>
+      </c>
+      <c r="L58">
+        <v>0</v>
+      </c>
+      <c r="M58">
+        <v>0</v>
+      </c>
+      <c r="N58">
+        <v>2</v>
+      </c>
+      <c r="O58">
+        <v>1</v>
+      </c>
+      <c r="P58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A59">
+        <v>3</v>
+      </c>
+      <c r="B59" t="s">
+        <v>46</v>
+      </c>
+      <c r="C59" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D59">
+        <v>42</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+      <c r="F59">
+        <v>0</v>
+      </c>
+      <c r="G59">
+        <v>0</v>
+      </c>
+      <c r="H59">
+        <v>0</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>0</v>
+      </c>
+      <c r="K59">
+        <v>0</v>
+      </c>
+      <c r="L59">
+        <v>0</v>
+      </c>
+      <c r="M59">
+        <v>0</v>
+      </c>
+      <c r="N59">
+        <v>0</v>
+      </c>
+      <c r="O59">
+        <v>0</v>
+      </c>
+      <c r="P59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D60">
+        <v>18</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+      <c r="M60">
+        <v>1</v>
+      </c>
+      <c r="N60">
+        <v>0</v>
+      </c>
+      <c r="O60">
+        <v>0</v>
+      </c>
+      <c r="P60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D61">
+        <v>14</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>1</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+      <c r="M61">
+        <v>0</v>
+      </c>
+      <c r="N61">
+        <v>1</v>
+      </c>
+      <c r="O61">
+        <v>0</v>
+      </c>
+      <c r="P61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D62">
+        <v>56</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+      <c r="M62">
+        <v>0</v>
+      </c>
+      <c r="N62">
+        <v>0</v>
+      </c>
+      <c r="O62">
+        <v>0</v>
+      </c>
+      <c r="P62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D63">
+        <v>71</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>2</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>1</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="M63">
+        <v>0</v>
+      </c>
+      <c r="N63">
+        <v>1</v>
+      </c>
+      <c r="O63">
+        <v>0</v>
+      </c>
+      <c r="P63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D64">
+        <v>23</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+      <c r="M64">
+        <v>0</v>
+      </c>
+      <c r="N64">
+        <v>0</v>
+      </c>
+      <c r="O64">
+        <v>0</v>
+      </c>
+      <c r="P64">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2722,7 +3772,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE8C601-DC7D-42D2-865D-643789981902}">
-  <dimension ref="A1:L59"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -4971,6 +6021,1108 @@
         <v>0</v>
       </c>
     </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A60">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D60" t="s">
+        <v>19</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+      <c r="F60">
+        <v>0</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
+      </c>
+      <c r="H60">
+        <v>0</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>0</v>
+      </c>
+      <c r="L60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A61">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D61" t="s">
+        <v>20</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+      <c r="F61">
+        <v>0</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
+      </c>
+      <c r="H61">
+        <v>0</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>0</v>
+      </c>
+      <c r="K61">
+        <v>0</v>
+      </c>
+      <c r="L61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D62" t="s">
+        <v>21</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>0</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>3</v>
+      </c>
+      <c r="K62">
+        <v>0</v>
+      </c>
+      <c r="L62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A63">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D63" t="s">
+        <v>22</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
+        <v>0</v>
+      </c>
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63">
+        <v>0</v>
+      </c>
+      <c r="K63">
+        <v>0</v>
+      </c>
+      <c r="L63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A64">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D64" t="s">
+        <v>23</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+      <c r="F64">
+        <v>0</v>
+      </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
+      <c r="H64">
+        <v>0</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>3</v>
+      </c>
+      <c r="K64">
+        <v>0</v>
+      </c>
+      <c r="L64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D65" t="s">
+        <v>24</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D66" t="s">
+        <v>18</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>0</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>1</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>46</v>
+      </c>
+      <c r="C67" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D67" t="s">
+        <v>25</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>3</v>
+      </c>
+      <c r="B68" t="s">
+        <v>46</v>
+      </c>
+      <c r="C68" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D68" t="s">
+        <v>26</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>0</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>3</v>
+      </c>
+      <c r="B69" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D69" t="s">
+        <v>27</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>3</v>
+      </c>
+      <c r="B70" t="s">
+        <v>46</v>
+      </c>
+      <c r="C70" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D70" t="s">
+        <v>28</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>1</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>3</v>
+      </c>
+      <c r="B71" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D71" t="s">
+        <v>29</v>
+      </c>
+      <c r="E71">
+        <v>1</v>
+      </c>
+      <c r="F71">
+        <v>1</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>3</v>
+      </c>
+      <c r="B72" t="s">
+        <v>46</v>
+      </c>
+      <c r="C72" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D72" t="s">
+        <v>34</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>2</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>4</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>3</v>
+      </c>
+      <c r="B73" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D73" t="s">
+        <v>32</v>
+      </c>
+      <c r="E73">
+        <v>1</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>1</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>3</v>
+      </c>
+      <c r="B74" t="s">
+        <v>46</v>
+      </c>
+      <c r="C74" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D74" t="s">
+        <v>33</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>1</v>
+      </c>
+      <c r="J74">
+        <v>3</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>3</v>
+      </c>
+      <c r="B75" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D75" t="s">
+        <v>31</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>3</v>
+      </c>
+      <c r="B76" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D76" t="s">
+        <v>30</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>3</v>
+      </c>
+      <c r="B77" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D77" t="s">
+        <v>35</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>1</v>
+      </c>
+      <c r="H77">
+        <v>1</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>3</v>
+      </c>
+      <c r="B78" t="s">
+        <v>46</v>
+      </c>
+      <c r="C78" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D78" t="s">
+        <v>37</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>3</v>
+      </c>
+      <c r="B79" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D79" t="s">
+        <v>38</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>1</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>3</v>
+      </c>
+      <c r="B80" t="s">
+        <v>46</v>
+      </c>
+      <c r="C80" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D80" t="s">
+        <v>36</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>0</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>3</v>
+      </c>
+      <c r="B81" t="s">
+        <v>46</v>
+      </c>
+      <c r="C81" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D81" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>0</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>3</v>
+      </c>
+      <c r="B82" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D82" t="s">
+        <v>40</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>0</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>3</v>
+      </c>
+      <c r="B83" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D83" t="s">
+        <v>41</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>3</v>
+      </c>
+      <c r="B84" t="s">
+        <v>46</v>
+      </c>
+      <c r="C84" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D84" t="s">
+        <v>42</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>3</v>
+      </c>
+      <c r="B85" t="s">
+        <v>46</v>
+      </c>
+      <c r="C85" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D85" t="s">
+        <v>14</v>
+      </c>
+      <c r="E85">
+        <v>1</v>
+      </c>
+      <c r="F85">
+        <v>1</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85">
+        <v>2</v>
+      </c>
+      <c r="I85">
+        <v>1</v>
+      </c>
+      <c r="J85">
+        <v>6</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>3</v>
+      </c>
+      <c r="B86" t="s">
+        <v>46</v>
+      </c>
+      <c r="C86" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D86" t="s">
+        <v>15</v>
+      </c>
+      <c r="E86">
+        <v>1</v>
+      </c>
+      <c r="F86">
+        <v>2</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>6</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>3</v>
+      </c>
+      <c r="B87" t="s">
+        <v>46</v>
+      </c>
+      <c r="C87" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D87" t="s">
+        <v>16</v>
+      </c>
+      <c r="E87">
+        <v>1</v>
+      </c>
+      <c r="F87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>4</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>3</v>
+      </c>
+      <c r="B88" t="s">
+        <v>46</v>
+      </c>
+      <c r="C88" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D88" t="s">
+        <v>17</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SDHL 2026-2027 scoring chances.xlsx
+++ b/SDHL 2026-2027 scoring chances.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikko\Documents\Luleå Damjun\Advanced stats_data\SDHL stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A77E08C-600D-4CE3-8392-7EEE67BA753F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960E84D3-CC86-47A8-966F-E7763068E14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="55">
   <si>
     <t>Goal For</t>
   </si>
@@ -184,6 +184,27 @@
   </si>
   <si>
     <t>Modo</t>
+  </si>
+  <si>
+    <t>Brynas</t>
+  </si>
+  <si>
+    <t>OZ 2 area</t>
+  </si>
+  <si>
+    <t>OZ blueline+screen</t>
+  </si>
+  <si>
+    <t>TA Oz</t>
+  </si>
+  <si>
+    <t>T over Dz</t>
+  </si>
+  <si>
+    <t>T over Nz</t>
+  </si>
+  <si>
+    <t>T over Oz</t>
   </si>
 </sst>
 </file>
@@ -559,7 +580,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4EB1DA-C9FF-4BF6-849D-6254FD5C05A8}">
-  <dimension ref="A1:P64"/>
+  <dimension ref="A1:P95"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="10.08984375" style="2" bestFit="1" customWidth="1"/>
@@ -3765,6 +3786,1556 @@
         <v>0</v>
       </c>
     </row>
+    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A65">
+        <v>4</v>
+      </c>
+      <c r="B65" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D65">
+        <v>11</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>0</v>
+      </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
+      <c r="H65">
+        <v>0</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>0</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65">
+        <v>0</v>
+      </c>
+      <c r="M65">
+        <v>0</v>
+      </c>
+      <c r="N65">
+        <v>0</v>
+      </c>
+      <c r="O65">
+        <v>0</v>
+      </c>
+      <c r="P65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A66">
+        <v>4</v>
+      </c>
+      <c r="B66" t="s">
+        <v>48</v>
+      </c>
+      <c r="C66" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D66">
+        <v>15</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+      <c r="F66">
+        <v>0</v>
+      </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
+      <c r="H66">
+        <v>3</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>0</v>
+      </c>
+      <c r="L66">
+        <v>0</v>
+      </c>
+      <c r="M66">
+        <v>0</v>
+      </c>
+      <c r="N66">
+        <v>2</v>
+      </c>
+      <c r="O66">
+        <v>0</v>
+      </c>
+      <c r="P66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A67">
+        <v>4</v>
+      </c>
+      <c r="B67" t="s">
+        <v>48</v>
+      </c>
+      <c r="C67" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D67">
+        <v>81</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+      <c r="F67">
+        <v>0</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+      <c r="H67">
+        <v>0</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>0</v>
+      </c>
+      <c r="K67">
+        <v>0</v>
+      </c>
+      <c r="L67">
+        <v>0</v>
+      </c>
+      <c r="M67">
+        <v>2</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="O67">
+        <v>0</v>
+      </c>
+      <c r="P67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A68">
+        <v>4</v>
+      </c>
+      <c r="B68" t="s">
+        <v>48</v>
+      </c>
+      <c r="C68" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D68">
+        <v>23</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+      <c r="F68">
+        <v>0</v>
+      </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
+      <c r="H68">
+        <v>4</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>0</v>
+      </c>
+      <c r="L68">
+        <v>0</v>
+      </c>
+      <c r="M68">
+        <v>0</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68">
+        <v>0</v>
+      </c>
+      <c r="P68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A69">
+        <v>4</v>
+      </c>
+      <c r="B69" t="s">
+        <v>48</v>
+      </c>
+      <c r="C69" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D69">
+        <v>25</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+      <c r="F69">
+        <v>0</v>
+      </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
+      <c r="H69">
+        <v>0</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="L69">
+        <v>0</v>
+      </c>
+      <c r="M69">
+        <v>0</v>
+      </c>
+      <c r="N69">
+        <v>0</v>
+      </c>
+      <c r="O69">
+        <v>0</v>
+      </c>
+      <c r="P69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A70">
+        <v>4</v>
+      </c>
+      <c r="B70" t="s">
+        <v>48</v>
+      </c>
+      <c r="C70" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D70">
+        <v>21</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+      <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
+      <c r="H70">
+        <v>0</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>0</v>
+      </c>
+      <c r="K70">
+        <v>0</v>
+      </c>
+      <c r="L70">
+        <v>0</v>
+      </c>
+      <c r="M70">
+        <v>0</v>
+      </c>
+      <c r="N70">
+        <v>2</v>
+      </c>
+      <c r="O70">
+        <v>0</v>
+      </c>
+      <c r="P70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A71">
+        <v>4</v>
+      </c>
+      <c r="B71" t="s">
+        <v>48</v>
+      </c>
+      <c r="C71" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D71">
+        <v>39</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>0</v>
+      </c>
+      <c r="K71">
+        <v>0</v>
+      </c>
+      <c r="L71">
+        <v>0</v>
+      </c>
+      <c r="M71">
+        <v>0</v>
+      </c>
+      <c r="N71">
+        <v>1</v>
+      </c>
+      <c r="O71">
+        <v>0</v>
+      </c>
+      <c r="P71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A72">
+        <v>4</v>
+      </c>
+      <c r="B72" t="s">
+        <v>48</v>
+      </c>
+      <c r="C72" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D72">
+        <v>34</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72">
+        <v>0</v>
+      </c>
+      <c r="H72">
+        <v>0</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>0</v>
+      </c>
+      <c r="K72">
+        <v>0</v>
+      </c>
+      <c r="L72">
+        <v>0</v>
+      </c>
+      <c r="M72">
+        <v>0</v>
+      </c>
+      <c r="N72">
+        <v>0</v>
+      </c>
+      <c r="O72">
+        <v>0</v>
+      </c>
+      <c r="P72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A73">
+        <v>4</v>
+      </c>
+      <c r="B73" t="s">
+        <v>48</v>
+      </c>
+      <c r="C73" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D73">
+        <v>16</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>0</v>
+      </c>
+      <c r="G73">
+        <v>0</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>0</v>
+      </c>
+      <c r="K73">
+        <v>0</v>
+      </c>
+      <c r="L73">
+        <v>0</v>
+      </c>
+      <c r="M73">
+        <v>0</v>
+      </c>
+      <c r="N73">
+        <v>0</v>
+      </c>
+      <c r="O73">
+        <v>0</v>
+      </c>
+      <c r="P73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <v>4</v>
+      </c>
+      <c r="B74" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D74">
+        <v>26</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74">
+        <v>0</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>0</v>
+      </c>
+      <c r="K74">
+        <v>0</v>
+      </c>
+      <c r="L74">
+        <v>0</v>
+      </c>
+      <c r="M74">
+        <v>0</v>
+      </c>
+      <c r="N74">
+        <v>0</v>
+      </c>
+      <c r="O74">
+        <v>0</v>
+      </c>
+      <c r="P74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A75">
+        <v>4</v>
+      </c>
+      <c r="B75" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D75">
+        <v>24</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>0</v>
+      </c>
+      <c r="G75">
+        <v>0</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>0</v>
+      </c>
+      <c r="K75">
+        <v>0</v>
+      </c>
+      <c r="L75">
+        <v>0</v>
+      </c>
+      <c r="M75">
+        <v>0</v>
+      </c>
+      <c r="N75">
+        <v>0</v>
+      </c>
+      <c r="O75">
+        <v>0</v>
+      </c>
+      <c r="P75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A76">
+        <v>4</v>
+      </c>
+      <c r="B76" t="s">
+        <v>48</v>
+      </c>
+      <c r="C76" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D76">
+        <v>19</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>0</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>0</v>
+      </c>
+      <c r="L76">
+        <v>0</v>
+      </c>
+      <c r="M76">
+        <v>0</v>
+      </c>
+      <c r="N76">
+        <v>0</v>
+      </c>
+      <c r="O76">
+        <v>0</v>
+      </c>
+      <c r="P76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A77">
+        <v>4</v>
+      </c>
+      <c r="B77" t="s">
+        <v>48</v>
+      </c>
+      <c r="C77" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D77">
+        <v>7</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>0</v>
+      </c>
+      <c r="K77">
+        <v>0</v>
+      </c>
+      <c r="L77">
+        <v>0</v>
+      </c>
+      <c r="M77">
+        <v>0</v>
+      </c>
+      <c r="N77">
+        <v>0</v>
+      </c>
+      <c r="O77">
+        <v>0</v>
+      </c>
+      <c r="P77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A78">
+        <v>4</v>
+      </c>
+      <c r="B78" t="s">
+        <v>48</v>
+      </c>
+      <c r="C78" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D78">
+        <v>44</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>0</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>0</v>
+      </c>
+      <c r="L78">
+        <v>0</v>
+      </c>
+      <c r="M78">
+        <v>0</v>
+      </c>
+      <c r="N78">
+        <v>0</v>
+      </c>
+      <c r="O78">
+        <v>0</v>
+      </c>
+      <c r="P78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A79">
+        <v>4</v>
+      </c>
+      <c r="B79" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D79">
+        <v>10</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>0</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>0</v>
+      </c>
+      <c r="L79">
+        <v>0</v>
+      </c>
+      <c r="M79">
+        <v>0</v>
+      </c>
+      <c r="N79">
+        <v>0</v>
+      </c>
+      <c r="O79">
+        <v>0</v>
+      </c>
+      <c r="P79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A80">
+        <v>4</v>
+      </c>
+      <c r="B80" t="s">
+        <v>48</v>
+      </c>
+      <c r="C80" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D80">
+        <v>27</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>0</v>
+      </c>
+      <c r="G80">
+        <v>1</v>
+      </c>
+      <c r="H80">
+        <v>1</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>1</v>
+      </c>
+      <c r="K80">
+        <v>0</v>
+      </c>
+      <c r="L80">
+        <v>0</v>
+      </c>
+      <c r="M80">
+        <v>0</v>
+      </c>
+      <c r="N80">
+        <v>0</v>
+      </c>
+      <c r="O80">
+        <v>0</v>
+      </c>
+      <c r="P80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A81">
+        <v>4</v>
+      </c>
+      <c r="B81" t="s">
+        <v>48</v>
+      </c>
+      <c r="C81" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D81">
+        <v>13</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>0</v>
+      </c>
+      <c r="G81">
+        <v>1</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>0</v>
+      </c>
+      <c r="L81">
+        <v>0</v>
+      </c>
+      <c r="M81">
+        <v>1</v>
+      </c>
+      <c r="N81">
+        <v>0</v>
+      </c>
+      <c r="O81">
+        <v>0</v>
+      </c>
+      <c r="P81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A82">
+        <v>4</v>
+      </c>
+      <c r="B82" t="s">
+        <v>48</v>
+      </c>
+      <c r="C82" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D82">
+        <v>72</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>0</v>
+      </c>
+      <c r="G82">
+        <v>1</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>0</v>
+      </c>
+      <c r="L82">
+        <v>0</v>
+      </c>
+      <c r="M82">
+        <v>1</v>
+      </c>
+      <c r="N82">
+        <v>0</v>
+      </c>
+      <c r="O82">
+        <v>0</v>
+      </c>
+      <c r="P82">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A83">
+        <v>4</v>
+      </c>
+      <c r="B83" t="s">
+        <v>48</v>
+      </c>
+      <c r="C83" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D83">
+        <v>4</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>0</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>0</v>
+      </c>
+      <c r="K83">
+        <v>0</v>
+      </c>
+      <c r="L83">
+        <v>0</v>
+      </c>
+      <c r="M83">
+        <v>0</v>
+      </c>
+      <c r="N83">
+        <v>0</v>
+      </c>
+      <c r="O83">
+        <v>0</v>
+      </c>
+      <c r="P83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A84">
+        <v>4</v>
+      </c>
+      <c r="B84" t="s">
+        <v>48</v>
+      </c>
+      <c r="C84" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D84">
+        <v>5</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>0</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>0</v>
+      </c>
+      <c r="K84">
+        <v>0</v>
+      </c>
+      <c r="L84">
+        <v>0</v>
+      </c>
+      <c r="M84">
+        <v>0</v>
+      </c>
+      <c r="N84">
+        <v>0</v>
+      </c>
+      <c r="O84">
+        <v>0</v>
+      </c>
+      <c r="P84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <v>4</v>
+      </c>
+      <c r="B85" t="s">
+        <v>48</v>
+      </c>
+      <c r="C85" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D85">
+        <v>42</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>0</v>
+      </c>
+      <c r="G85">
+        <v>2</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>0</v>
+      </c>
+      <c r="L85">
+        <v>0</v>
+      </c>
+      <c r="M85">
+        <v>0</v>
+      </c>
+      <c r="N85">
+        <v>0</v>
+      </c>
+      <c r="O85">
+        <v>0</v>
+      </c>
+      <c r="P85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A86">
+        <v>4</v>
+      </c>
+      <c r="B86" t="s">
+        <v>48</v>
+      </c>
+      <c r="C86" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D86">
+        <v>20</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>0</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>0</v>
+      </c>
+      <c r="L86">
+        <v>0</v>
+      </c>
+      <c r="M86">
+        <v>0</v>
+      </c>
+      <c r="N86">
+        <v>0</v>
+      </c>
+      <c r="O86">
+        <v>0</v>
+      </c>
+      <c r="P86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A87">
+        <v>4</v>
+      </c>
+      <c r="B87" t="s">
+        <v>48</v>
+      </c>
+      <c r="C87" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D87">
+        <v>18</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>0</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>0</v>
+      </c>
+      <c r="L87">
+        <v>0</v>
+      </c>
+      <c r="M87">
+        <v>0</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
+      <c r="O87">
+        <v>0</v>
+      </c>
+      <c r="P87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <v>4</v>
+      </c>
+      <c r="B88" t="s">
+        <v>48</v>
+      </c>
+      <c r="C88" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D88">
+        <v>17</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>0</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>0</v>
+      </c>
+      <c r="L88">
+        <v>0</v>
+      </c>
+      <c r="M88">
+        <v>0</v>
+      </c>
+      <c r="N88">
+        <v>0</v>
+      </c>
+      <c r="O88">
+        <v>0</v>
+      </c>
+      <c r="P88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>4</v>
+      </c>
+      <c r="B89" t="s">
+        <v>48</v>
+      </c>
+      <c r="C89" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D89">
+        <v>14</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>2</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+      <c r="M89">
+        <v>0</v>
+      </c>
+      <c r="N89">
+        <v>1</v>
+      </c>
+      <c r="O89">
+        <v>1</v>
+      </c>
+      <c r="P89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>4</v>
+      </c>
+      <c r="B90" t="s">
+        <v>48</v>
+      </c>
+      <c r="C90" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D90">
+        <v>2</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+      <c r="M90">
+        <v>0</v>
+      </c>
+      <c r="N90">
+        <v>0</v>
+      </c>
+      <c r="O90">
+        <v>0</v>
+      </c>
+      <c r="P90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>4</v>
+      </c>
+      <c r="B91" t="s">
+        <v>48</v>
+      </c>
+      <c r="C91" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D91">
+        <v>56</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>0</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+      <c r="M91">
+        <v>0</v>
+      </c>
+      <c r="N91">
+        <v>0</v>
+      </c>
+      <c r="O91">
+        <v>0</v>
+      </c>
+      <c r="P91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>4</v>
+      </c>
+      <c r="B92" t="s">
+        <v>48</v>
+      </c>
+      <c r="C92" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D92">
+        <v>6</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>0</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>1</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+      <c r="M92">
+        <v>0</v>
+      </c>
+      <c r="N92">
+        <v>3</v>
+      </c>
+      <c r="O92">
+        <v>0</v>
+      </c>
+      <c r="P92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>4</v>
+      </c>
+      <c r="B93" t="s">
+        <v>48</v>
+      </c>
+      <c r="C93" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D93">
+        <v>71</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>0</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+      <c r="M93">
+        <v>0</v>
+      </c>
+      <c r="N93">
+        <v>0</v>
+      </c>
+      <c r="O93">
+        <v>0</v>
+      </c>
+      <c r="P93">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>4</v>
+      </c>
+      <c r="B94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D94">
+        <v>8</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+      <c r="M94">
+        <v>0</v>
+      </c>
+      <c r="N94">
+        <v>1</v>
+      </c>
+      <c r="O94">
+        <v>0</v>
+      </c>
+      <c r="P94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>4</v>
+      </c>
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D95">
+        <v>9</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+      <c r="M95">
+        <v>0</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95">
+        <v>0</v>
+      </c>
+      <c r="P95">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3772,7 +5343,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE8C601-DC7D-42D2-865D-643789981902}">
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L122"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -7123,6 +8694,1298 @@
         <v>0</v>
       </c>
     </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A89">
+        <v>4</v>
+      </c>
+      <c r="B89" t="s">
+        <v>48</v>
+      </c>
+      <c r="C89" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D89" t="s">
+        <v>30</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>0</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+      <c r="L89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A90">
+        <v>4</v>
+      </c>
+      <c r="B90" t="s">
+        <v>48</v>
+      </c>
+      <c r="C90" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D90" t="s">
+        <v>34</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>0</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>0</v>
+      </c>
+      <c r="L90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A91">
+        <v>4</v>
+      </c>
+      <c r="B91" t="s">
+        <v>48</v>
+      </c>
+      <c r="C91" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D91" t="s">
+        <v>31</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+      <c r="L91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A92">
+        <v>4</v>
+      </c>
+      <c r="B92" t="s">
+        <v>48</v>
+      </c>
+      <c r="C92" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D92" t="s">
+        <v>32</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>1</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>0</v>
+      </c>
+      <c r="L92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A93">
+        <v>4</v>
+      </c>
+      <c r="B93" t="s">
+        <v>48</v>
+      </c>
+      <c r="C93" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D93" t="s">
+        <v>33</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>1</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>0</v>
+      </c>
+      <c r="L93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A94">
+        <v>4</v>
+      </c>
+      <c r="B94" t="s">
+        <v>48</v>
+      </c>
+      <c r="C94" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D94" t="s">
+        <v>20</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>0</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>0</v>
+      </c>
+      <c r="L94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A95">
+        <v>4</v>
+      </c>
+      <c r="B95" t="s">
+        <v>48</v>
+      </c>
+      <c r="C95" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D95" t="s">
+        <v>19</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>0</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>0</v>
+      </c>
+      <c r="L95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>4</v>
+      </c>
+      <c r="B96" t="s">
+        <v>48</v>
+      </c>
+      <c r="C96" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D96" t="s">
+        <v>49</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>4</v>
+      </c>
+      <c r="B97" t="s">
+        <v>48</v>
+      </c>
+      <c r="C97" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D97" t="s">
+        <v>21</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>1</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>1</v>
+      </c>
+      <c r="J97">
+        <v>5</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>4</v>
+      </c>
+      <c r="B98" t="s">
+        <v>48</v>
+      </c>
+      <c r="C98" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D98" t="s">
+        <v>22</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>2</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>4</v>
+      </c>
+      <c r="B99" t="s">
+        <v>48</v>
+      </c>
+      <c r="C99" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D99" t="s">
+        <v>24</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>4</v>
+      </c>
+      <c r="B100" t="s">
+        <v>48</v>
+      </c>
+      <c r="C100" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D100" t="s">
+        <v>23</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>1</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>4</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>4</v>
+      </c>
+      <c r="B101" t="s">
+        <v>48</v>
+      </c>
+      <c r="C101" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D101" t="s">
+        <v>18</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>1</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>4</v>
+      </c>
+      <c r="B102" t="s">
+        <v>48</v>
+      </c>
+      <c r="C102" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D102" t="s">
+        <v>50</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>4</v>
+      </c>
+      <c r="B103" t="s">
+        <v>48</v>
+      </c>
+      <c r="C103" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D103" t="s">
+        <v>51</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>2</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>4</v>
+      </c>
+      <c r="B104" t="s">
+        <v>48</v>
+      </c>
+      <c r="C104" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D104" t="s">
+        <v>27</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>48</v>
+      </c>
+      <c r="C105" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D105" t="s">
+        <v>28</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>4</v>
+      </c>
+      <c r="B106" t="s">
+        <v>48</v>
+      </c>
+      <c r="C106" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D106" t="s">
+        <v>38</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>4</v>
+      </c>
+      <c r="B107" t="s">
+        <v>48</v>
+      </c>
+      <c r="C107" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D107" t="s">
+        <v>36</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>4</v>
+      </c>
+      <c r="B108" t="s">
+        <v>48</v>
+      </c>
+      <c r="C108" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D108" t="s">
+        <v>37</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>4</v>
+      </c>
+      <c r="B109" t="s">
+        <v>48</v>
+      </c>
+      <c r="C109" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D109" t="s">
+        <v>35</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>4</v>
+      </c>
+      <c r="B110" t="s">
+        <v>48</v>
+      </c>
+      <c r="C110" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D110" t="s">
+        <v>39</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>1</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>4</v>
+      </c>
+      <c r="B111" t="s">
+        <v>48</v>
+      </c>
+      <c r="C111" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D111" t="s">
+        <v>40</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>0</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>1</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>4</v>
+      </c>
+      <c r="B112" t="s">
+        <v>48</v>
+      </c>
+      <c r="C112" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D112" t="s">
+        <v>41</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>0</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>4</v>
+      </c>
+      <c r="B113" t="s">
+        <v>48</v>
+      </c>
+      <c r="C113" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D113" t="s">
+        <v>42</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>0</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>2</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>4</v>
+      </c>
+      <c r="B114" t="s">
+        <v>48</v>
+      </c>
+      <c r="C114" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D114" t="s">
+        <v>25</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>4</v>
+      </c>
+      <c r="B115" t="s">
+        <v>48</v>
+      </c>
+      <c r="C115" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D115" t="s">
+        <v>26</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>2</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>4</v>
+      </c>
+      <c r="B116" t="s">
+        <v>48</v>
+      </c>
+      <c r="C116" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D116" t="s">
+        <v>52</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>4</v>
+      </c>
+      <c r="B117" t="s">
+        <v>48</v>
+      </c>
+      <c r="C117" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D117" t="s">
+        <v>53</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>4</v>
+      </c>
+      <c r="B118" t="s">
+        <v>48</v>
+      </c>
+      <c r="C118" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D118" t="s">
+        <v>54</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>4</v>
+      </c>
+      <c r="B119" t="s">
+        <v>48</v>
+      </c>
+      <c r="C119" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D119" t="s">
+        <v>14</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>5</v>
+      </c>
+      <c r="G119">
+        <v>1</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="J119">
+        <v>5</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>4</v>
+      </c>
+      <c r="B120" t="s">
+        <v>48</v>
+      </c>
+      <c r="C120" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D120" t="s">
+        <v>15</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>5</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>2</v>
+      </c>
+      <c r="J120">
+        <v>3</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>4</v>
+      </c>
+      <c r="B121" t="s">
+        <v>48</v>
+      </c>
+      <c r="C121" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D121" t="s">
+        <v>16</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>1</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>1</v>
+      </c>
+      <c r="J121">
+        <v>5</v>
+      </c>
+      <c r="K121">
+        <v>1</v>
+      </c>
+      <c r="L121">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>4</v>
+      </c>
+      <c r="B122" t="s">
+        <v>48</v>
+      </c>
+      <c r="C122" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D122" t="s">
+        <v>17</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SDHL 2026-2027 scoring chances.xlsx
+++ b/SDHL 2026-2027 scoring chances.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikko\Documents\Luleå Damjun\Advanced stats_data\SDHL stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{960E84D3-CC86-47A8-966F-E7763068E14F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F773F6-97EB-4CB6-BD84-5DB795BD07C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="57">
   <si>
     <t>Goal For</t>
   </si>
@@ -206,15 +206,27 @@
   <si>
     <t>T over Oz</t>
   </si>
+  <si>
+    <t>HV71</t>
+  </si>
+  <si>
+    <t>Turnover NZ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -580,7 +592,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4EB1DA-C9FF-4BF6-849D-6254FD5C05A8}">
-  <dimension ref="A1:P95"/>
+  <dimension ref="A1:P126"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="10.08984375" style="2" bestFit="1" customWidth="1"/>
@@ -5336,14 +5348,1565 @@
         <v>0</v>
       </c>
     </row>
+    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A96">
+        <v>5</v>
+      </c>
+      <c r="B96" t="s">
+        <v>55</v>
+      </c>
+      <c r="C96" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D96">
+        <v>11</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>0</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>0</v>
+      </c>
+      <c r="L96">
+        <v>0</v>
+      </c>
+      <c r="M96">
+        <v>0</v>
+      </c>
+      <c r="N96">
+        <v>0</v>
+      </c>
+      <c r="O96">
+        <v>0</v>
+      </c>
+      <c r="P96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A97">
+        <v>5</v>
+      </c>
+      <c r="B97" t="s">
+        <v>55</v>
+      </c>
+      <c r="C97" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D97">
+        <v>15</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>0</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>0</v>
+      </c>
+      <c r="L97">
+        <v>1</v>
+      </c>
+      <c r="M97">
+        <v>0</v>
+      </c>
+      <c r="N97">
+        <v>0</v>
+      </c>
+      <c r="O97">
+        <v>0</v>
+      </c>
+      <c r="P97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A98">
+        <v>5</v>
+      </c>
+      <c r="B98" t="s">
+        <v>55</v>
+      </c>
+      <c r="C98" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D98">
+        <v>81</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>0</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>0</v>
+      </c>
+      <c r="L98">
+        <v>0</v>
+      </c>
+      <c r="M98">
+        <v>0</v>
+      </c>
+      <c r="N98">
+        <v>1</v>
+      </c>
+      <c r="O98">
+        <v>0</v>
+      </c>
+      <c r="P98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A99">
+        <v>5</v>
+      </c>
+      <c r="B99" t="s">
+        <v>55</v>
+      </c>
+      <c r="C99" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D99">
+        <v>23</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>0</v>
+      </c>
+      <c r="G99">
+        <v>2</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>0</v>
+      </c>
+      <c r="L99">
+        <v>0</v>
+      </c>
+      <c r="M99">
+        <v>0</v>
+      </c>
+      <c r="N99">
+        <v>1</v>
+      </c>
+      <c r="O99">
+        <v>0</v>
+      </c>
+      <c r="P99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A100">
+        <v>5</v>
+      </c>
+      <c r="B100" t="s">
+        <v>55</v>
+      </c>
+      <c r="C100" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D100">
+        <v>25</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>0</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>0</v>
+      </c>
+      <c r="L100">
+        <v>0</v>
+      </c>
+      <c r="M100">
+        <v>0</v>
+      </c>
+      <c r="N100">
+        <v>0</v>
+      </c>
+      <c r="O100">
+        <v>0</v>
+      </c>
+      <c r="P100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A101">
+        <v>5</v>
+      </c>
+      <c r="B101" t="s">
+        <v>55</v>
+      </c>
+      <c r="C101" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D101">
+        <v>21</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>0</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>1</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>0</v>
+      </c>
+      <c r="L101">
+        <v>0</v>
+      </c>
+      <c r="M101">
+        <v>0</v>
+      </c>
+      <c r="N101">
+        <v>3</v>
+      </c>
+      <c r="O101">
+        <v>0</v>
+      </c>
+      <c r="P101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A102">
+        <v>5</v>
+      </c>
+      <c r="B102" t="s">
+        <v>55</v>
+      </c>
+      <c r="C102" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D102">
+        <v>39</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>0</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>0</v>
+      </c>
+      <c r="L102">
+        <v>0</v>
+      </c>
+      <c r="M102">
+        <v>0</v>
+      </c>
+      <c r="N102">
+        <v>0</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A103">
+        <v>5</v>
+      </c>
+      <c r="B103" t="s">
+        <v>55</v>
+      </c>
+      <c r="C103" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D103">
+        <v>34</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>0</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>0</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>0</v>
+      </c>
+      <c r="L103">
+        <v>0</v>
+      </c>
+      <c r="M103">
+        <v>0</v>
+      </c>
+      <c r="N103">
+        <v>0</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A104">
+        <v>5</v>
+      </c>
+      <c r="B104" t="s">
+        <v>55</v>
+      </c>
+      <c r="C104" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D104">
+        <v>16</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>0</v>
+      </c>
+      <c r="G104">
+        <v>0</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>0</v>
+      </c>
+      <c r="L104">
+        <v>0</v>
+      </c>
+      <c r="M104">
+        <v>0</v>
+      </c>
+      <c r="N104">
+        <v>0</v>
+      </c>
+      <c r="O104">
+        <v>0</v>
+      </c>
+      <c r="P104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A105">
+        <v>5</v>
+      </c>
+      <c r="B105" t="s">
+        <v>55</v>
+      </c>
+      <c r="C105" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D105">
+        <v>26</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>0</v>
+      </c>
+      <c r="G105">
+        <v>0</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+      <c r="L105">
+        <v>0</v>
+      </c>
+      <c r="M105">
+        <v>0</v>
+      </c>
+      <c r="N105">
+        <v>0</v>
+      </c>
+      <c r="O105">
+        <v>0</v>
+      </c>
+      <c r="P105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A106">
+        <v>5</v>
+      </c>
+      <c r="B106" t="s">
+        <v>55</v>
+      </c>
+      <c r="C106" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D106">
+        <v>24</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>0</v>
+      </c>
+      <c r="G106">
+        <v>0</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>0</v>
+      </c>
+      <c r="L106">
+        <v>0</v>
+      </c>
+      <c r="M106">
+        <v>0</v>
+      </c>
+      <c r="N106">
+        <v>0</v>
+      </c>
+      <c r="O106">
+        <v>0</v>
+      </c>
+      <c r="P106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A107">
+        <v>5</v>
+      </c>
+      <c r="B107" t="s">
+        <v>55</v>
+      </c>
+      <c r="C107" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D107">
+        <v>19</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>0</v>
+      </c>
+      <c r="G107">
+        <v>0</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>0</v>
+      </c>
+      <c r="L107">
+        <v>0</v>
+      </c>
+      <c r="M107">
+        <v>0</v>
+      </c>
+      <c r="N107">
+        <v>0</v>
+      </c>
+      <c r="O107">
+        <v>0</v>
+      </c>
+      <c r="P107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A108">
+        <v>5</v>
+      </c>
+      <c r="B108" t="s">
+        <v>55</v>
+      </c>
+      <c r="C108" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D108">
+        <v>7</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>0</v>
+      </c>
+      <c r="G108">
+        <v>0</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>0</v>
+      </c>
+      <c r="L108">
+        <v>0</v>
+      </c>
+      <c r="M108">
+        <v>0</v>
+      </c>
+      <c r="N108">
+        <v>0</v>
+      </c>
+      <c r="O108">
+        <v>0</v>
+      </c>
+      <c r="P108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A109">
+        <v>5</v>
+      </c>
+      <c r="B109" t="s">
+        <v>55</v>
+      </c>
+      <c r="C109" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D109">
+        <v>44</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>0</v>
+      </c>
+      <c r="G109">
+        <v>0</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>0</v>
+      </c>
+      <c r="L109">
+        <v>0</v>
+      </c>
+      <c r="M109">
+        <v>0</v>
+      </c>
+      <c r="N109">
+        <v>0</v>
+      </c>
+      <c r="O109">
+        <v>0</v>
+      </c>
+      <c r="P109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A110">
+        <v>5</v>
+      </c>
+      <c r="B110" t="s">
+        <v>55</v>
+      </c>
+      <c r="C110" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D110">
+        <v>10</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>0</v>
+      </c>
+      <c r="G110">
+        <v>0</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+      <c r="L110">
+        <v>0</v>
+      </c>
+      <c r="M110">
+        <v>0</v>
+      </c>
+      <c r="N110">
+        <v>0</v>
+      </c>
+      <c r="O110">
+        <v>0</v>
+      </c>
+      <c r="P110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A111">
+        <v>5</v>
+      </c>
+      <c r="B111" t="s">
+        <v>55</v>
+      </c>
+      <c r="C111" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D111">
+        <v>27</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>0</v>
+      </c>
+      <c r="G111">
+        <v>3</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>0</v>
+      </c>
+      <c r="L111">
+        <v>1</v>
+      </c>
+      <c r="M111">
+        <v>0</v>
+      </c>
+      <c r="N111">
+        <v>0</v>
+      </c>
+      <c r="O111">
+        <v>0</v>
+      </c>
+      <c r="P111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A112">
+        <v>5</v>
+      </c>
+      <c r="B112" t="s">
+        <v>55</v>
+      </c>
+      <c r="C112" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D112">
+        <v>13</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>2</v>
+      </c>
+      <c r="H112">
+        <v>4</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>0</v>
+      </c>
+      <c r="L112">
+        <v>0</v>
+      </c>
+      <c r="M112">
+        <v>0</v>
+      </c>
+      <c r="N112">
+        <v>2</v>
+      </c>
+      <c r="O112">
+        <v>0</v>
+      </c>
+      <c r="P112">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A113">
+        <v>5</v>
+      </c>
+      <c r="B113" t="s">
+        <v>55</v>
+      </c>
+      <c r="C113" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D113">
+        <v>72</v>
+      </c>
+      <c r="E113">
+        <v>0</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>2</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>0</v>
+      </c>
+      <c r="L113">
+        <v>0</v>
+      </c>
+      <c r="M113">
+        <v>0</v>
+      </c>
+      <c r="N113">
+        <v>0</v>
+      </c>
+      <c r="O113">
+        <v>0</v>
+      </c>
+      <c r="P113">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A114">
+        <v>5</v>
+      </c>
+      <c r="B114" t="s">
+        <v>55</v>
+      </c>
+      <c r="C114" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D114">
+        <v>4</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>0</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>0</v>
+      </c>
+      <c r="L114">
+        <v>0</v>
+      </c>
+      <c r="M114">
+        <v>0</v>
+      </c>
+      <c r="N114">
+        <v>0</v>
+      </c>
+      <c r="O114">
+        <v>0</v>
+      </c>
+      <c r="P114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A115">
+        <v>5</v>
+      </c>
+      <c r="B115" t="s">
+        <v>55</v>
+      </c>
+      <c r="C115" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D115">
+        <v>5</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>0</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>0</v>
+      </c>
+      <c r="L115">
+        <v>0</v>
+      </c>
+      <c r="M115">
+        <v>0</v>
+      </c>
+      <c r="N115">
+        <v>0</v>
+      </c>
+      <c r="O115">
+        <v>0</v>
+      </c>
+      <c r="P115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A116">
+        <v>5</v>
+      </c>
+      <c r="B116" t="s">
+        <v>55</v>
+      </c>
+      <c r="C116" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D116">
+        <v>42</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>0</v>
+      </c>
+      <c r="G116">
+        <v>3</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>1</v>
+      </c>
+      <c r="L116">
+        <v>0</v>
+      </c>
+      <c r="M116">
+        <v>0</v>
+      </c>
+      <c r="N116">
+        <v>1</v>
+      </c>
+      <c r="O116">
+        <v>0</v>
+      </c>
+      <c r="P116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A117">
+        <v>5</v>
+      </c>
+      <c r="B117" t="s">
+        <v>55</v>
+      </c>
+      <c r="C117" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D117">
+        <v>20</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>0</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>0</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>0</v>
+      </c>
+      <c r="L117">
+        <v>0</v>
+      </c>
+      <c r="M117">
+        <v>0</v>
+      </c>
+      <c r="N117">
+        <v>0</v>
+      </c>
+      <c r="O117">
+        <v>0</v>
+      </c>
+      <c r="P117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A118">
+        <v>5</v>
+      </c>
+      <c r="B118" t="s">
+        <v>55</v>
+      </c>
+      <c r="C118" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D118">
+        <v>18</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>0</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>0</v>
+      </c>
+      <c r="L118">
+        <v>0</v>
+      </c>
+      <c r="M118">
+        <v>0</v>
+      </c>
+      <c r="N118">
+        <v>1</v>
+      </c>
+      <c r="O118">
+        <v>0</v>
+      </c>
+      <c r="P118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A119">
+        <v>5</v>
+      </c>
+      <c r="B119" t="s">
+        <v>55</v>
+      </c>
+      <c r="C119" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D119">
+        <v>17</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>0</v>
+      </c>
+      <c r="G119">
+        <v>0</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>0</v>
+      </c>
+      <c r="K119">
+        <v>0</v>
+      </c>
+      <c r="L119">
+        <v>0</v>
+      </c>
+      <c r="M119">
+        <v>0</v>
+      </c>
+      <c r="N119">
+        <v>0</v>
+      </c>
+      <c r="O119">
+        <v>0</v>
+      </c>
+      <c r="P119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A120">
+        <v>5</v>
+      </c>
+      <c r="B120" t="s">
+        <v>55</v>
+      </c>
+      <c r="C120" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D120">
+        <v>14</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>0</v>
+      </c>
+      <c r="G120">
+        <v>0</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+      <c r="K120">
+        <v>0</v>
+      </c>
+      <c r="L120">
+        <v>0</v>
+      </c>
+      <c r="M120">
+        <v>0</v>
+      </c>
+      <c r="N120">
+        <v>0</v>
+      </c>
+      <c r="O120">
+        <v>0</v>
+      </c>
+      <c r="P120">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A121">
+        <v>5</v>
+      </c>
+      <c r="B121" t="s">
+        <v>55</v>
+      </c>
+      <c r="C121" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D121">
+        <v>2</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>0</v>
+      </c>
+      <c r="G121">
+        <v>0</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>0</v>
+      </c>
+      <c r="L121">
+        <v>0</v>
+      </c>
+      <c r="M121">
+        <v>0</v>
+      </c>
+      <c r="N121">
+        <v>0</v>
+      </c>
+      <c r="O121">
+        <v>0</v>
+      </c>
+      <c r="P121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A122">
+        <v>5</v>
+      </c>
+      <c r="B122" t="s">
+        <v>55</v>
+      </c>
+      <c r="C122" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D122">
+        <v>56</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>0</v>
+      </c>
+      <c r="G122">
+        <v>0</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>0</v>
+      </c>
+      <c r="L122">
+        <v>0</v>
+      </c>
+      <c r="M122">
+        <v>0</v>
+      </c>
+      <c r="N122">
+        <v>0</v>
+      </c>
+      <c r="O122">
+        <v>0</v>
+      </c>
+      <c r="P122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>5</v>
+      </c>
+      <c r="B123" t="s">
+        <v>55</v>
+      </c>
+      <c r="C123" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D123">
+        <v>6</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>0</v>
+      </c>
+      <c r="G123">
+        <v>1</v>
+      </c>
+      <c r="H123">
+        <v>2</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+      <c r="M123">
+        <v>0</v>
+      </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
+      <c r="O123">
+        <v>0</v>
+      </c>
+      <c r="P123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>5</v>
+      </c>
+      <c r="B124" t="s">
+        <v>55</v>
+      </c>
+      <c r="C124" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D124">
+        <v>71</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>0</v>
+      </c>
+      <c r="G124">
+        <v>5</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>0</v>
+      </c>
+      <c r="K124">
+        <v>2</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+      <c r="M124">
+        <v>0</v>
+      </c>
+      <c r="N124">
+        <v>1</v>
+      </c>
+      <c r="O124">
+        <v>0</v>
+      </c>
+      <c r="P124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>5</v>
+      </c>
+      <c r="B125" t="s">
+        <v>55</v>
+      </c>
+      <c r="C125" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D125">
+        <v>8</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>0</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+      <c r="M125">
+        <v>0</v>
+      </c>
+      <c r="N125">
+        <v>0</v>
+      </c>
+      <c r="O125">
+        <v>0</v>
+      </c>
+      <c r="P125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>5</v>
+      </c>
+      <c r="B126" t="s">
+        <v>55</v>
+      </c>
+      <c r="C126" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D126">
+        <v>9</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>0</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>1</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+      <c r="M126">
+        <v>0</v>
+      </c>
+      <c r="N126">
+        <v>1</v>
+      </c>
+      <c r="O126">
+        <v>0</v>
+      </c>
+      <c r="P126">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE8C601-DC7D-42D2-865D-643789981902}">
-  <dimension ref="A1:L122"/>
+  <dimension ref="A1:L150"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -9986,7 +11549,1072 @@
         <v>0</v>
       </c>
     </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A123">
+        <v>5</v>
+      </c>
+      <c r="B123" t="s">
+        <v>55</v>
+      </c>
+      <c r="C123" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D123" t="s">
+        <v>34</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>1</v>
+      </c>
+      <c r="G123">
+        <v>0</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>0</v>
+      </c>
+      <c r="K123">
+        <v>0</v>
+      </c>
+      <c r="L123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A124">
+        <v>5</v>
+      </c>
+      <c r="B124" t="s">
+        <v>55</v>
+      </c>
+      <c r="C124" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D124" t="s">
+        <v>31</v>
+      </c>
+      <c r="E124">
+        <v>0</v>
+      </c>
+      <c r="F124">
+        <v>1</v>
+      </c>
+      <c r="G124">
+        <v>0</v>
+      </c>
+      <c r="H124">
+        <v>0</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>1</v>
+      </c>
+      <c r="K124">
+        <v>0</v>
+      </c>
+      <c r="L124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A125">
+        <v>5</v>
+      </c>
+      <c r="B125" t="s">
+        <v>55</v>
+      </c>
+      <c r="C125" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D125" t="s">
+        <v>32</v>
+      </c>
+      <c r="E125">
+        <v>0</v>
+      </c>
+      <c r="F125">
+        <v>1</v>
+      </c>
+      <c r="G125">
+        <v>0</v>
+      </c>
+      <c r="H125">
+        <v>0</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>1</v>
+      </c>
+      <c r="K125">
+        <v>0</v>
+      </c>
+      <c r="L125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A126">
+        <v>5</v>
+      </c>
+      <c r="B126" t="s">
+        <v>55</v>
+      </c>
+      <c r="C126" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D126" t="s">
+        <v>30</v>
+      </c>
+      <c r="E126">
+        <v>0</v>
+      </c>
+      <c r="F126">
+        <v>1</v>
+      </c>
+      <c r="G126">
+        <v>0</v>
+      </c>
+      <c r="H126">
+        <v>0</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>0</v>
+      </c>
+      <c r="L126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>5</v>
+      </c>
+      <c r="B127" t="s">
+        <v>55</v>
+      </c>
+      <c r="C127" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D127" t="s">
+        <v>33</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>3</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>0</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>2</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>5</v>
+      </c>
+      <c r="B128" t="s">
+        <v>55</v>
+      </c>
+      <c r="C128" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D128" t="s">
+        <v>20</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>1</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>5</v>
+      </c>
+      <c r="B129" t="s">
+        <v>55</v>
+      </c>
+      <c r="C129" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D129" t="s">
+        <v>19</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>1</v>
+      </c>
+      <c r="G129">
+        <v>0</v>
+      </c>
+      <c r="H129">
+        <v>0</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>5</v>
+      </c>
+      <c r="B130" t="s">
+        <v>55</v>
+      </c>
+      <c r="C130" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D130" t="s">
+        <v>49</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>0</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>5</v>
+      </c>
+      <c r="B131" t="s">
+        <v>55</v>
+      </c>
+      <c r="C131" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D131" t="s">
+        <v>21</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>2</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>2</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>5</v>
+      </c>
+      <c r="B132" t="s">
+        <v>55</v>
+      </c>
+      <c r="C132" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D132" t="s">
+        <v>22</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+      <c r="F132">
+        <v>2</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>5</v>
+      </c>
+      <c r="B133" t="s">
+        <v>55</v>
+      </c>
+      <c r="C133" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D133" t="s">
+        <v>24</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>5</v>
+      </c>
+      <c r="B134" t="s">
+        <v>55</v>
+      </c>
+      <c r="C134" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D134" t="s">
+        <v>18</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>5</v>
+      </c>
+      <c r="B135" t="s">
+        <v>55</v>
+      </c>
+      <c r="C135" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D135" t="s">
+        <v>50</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>5</v>
+      </c>
+      <c r="B136" t="s">
+        <v>55</v>
+      </c>
+      <c r="C136" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D136" t="s">
+        <v>23</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="F136">
+        <v>2</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>5</v>
+      </c>
+      <c r="B137" t="s">
+        <v>55</v>
+      </c>
+      <c r="C137" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D137" t="s">
+        <v>25</v>
+      </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
+      <c r="F137">
+        <v>1</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>2</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>5</v>
+      </c>
+      <c r="B138" t="s">
+        <v>55</v>
+      </c>
+      <c r="C138" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D138" t="s">
+        <v>56</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>0</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>5</v>
+      </c>
+      <c r="B139" t="s">
+        <v>55</v>
+      </c>
+      <c r="C139" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D139" t="s">
+        <v>26</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>5</v>
+      </c>
+      <c r="B140" t="s">
+        <v>55</v>
+      </c>
+      <c r="C140" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D140" t="s">
+        <v>51</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>5</v>
+      </c>
+      <c r="B141" t="s">
+        <v>55</v>
+      </c>
+      <c r="C141" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D141" t="s">
+        <v>27</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>5</v>
+      </c>
+      <c r="B142" t="s">
+        <v>55</v>
+      </c>
+      <c r="C142" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D142" t="s">
+        <v>28</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>5</v>
+      </c>
+      <c r="B143" t="s">
+        <v>55</v>
+      </c>
+      <c r="C143" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D143" t="s">
+        <v>38</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>0</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>5</v>
+      </c>
+      <c r="B144" t="s">
+        <v>55</v>
+      </c>
+      <c r="C144" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D144" t="s">
+        <v>37</v>
+      </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <v>0</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>5</v>
+      </c>
+      <c r="B145" t="s">
+        <v>55</v>
+      </c>
+      <c r="C145" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D145" t="s">
+        <v>36</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>5</v>
+      </c>
+      <c r="B146" t="s">
+        <v>55</v>
+      </c>
+      <c r="C146" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D146" t="s">
+        <v>39</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <v>1</v>
+      </c>
+      <c r="G146">
+        <v>0</v>
+      </c>
+      <c r="H146">
+        <v>1</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>5</v>
+      </c>
+      <c r="B147" t="s">
+        <v>55</v>
+      </c>
+      <c r="C147" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D147" t="s">
+        <v>35</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+      <c r="F147">
+        <v>0</v>
+      </c>
+      <c r="G147">
+        <v>1</v>
+      </c>
+      <c r="H147">
+        <v>2</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A148">
+        <v>5</v>
+      </c>
+      <c r="B148" t="s">
+        <v>55</v>
+      </c>
+      <c r="C148" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D148" t="s">
+        <v>40</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="F148">
+        <v>0</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>0</v>
+      </c>
+      <c r="K148">
+        <v>0</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A149">
+        <v>5</v>
+      </c>
+      <c r="B149" t="s">
+        <v>55</v>
+      </c>
+      <c r="C149" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D149" t="s">
+        <v>41</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A150">
+        <v>5</v>
+      </c>
+      <c r="B150" t="s">
+        <v>55</v>
+      </c>
+      <c r="C150" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D150" t="s">
+        <v>42</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>0</v>
+      </c>
+      <c r="J150">
+        <v>1</v>
+      </c>
+      <c r="K150">
+        <v>0</v>
+      </c>
+      <c r="L150">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/SDHL 2026-2027 scoring chances.xlsx
+++ b/SDHL 2026-2027 scoring chances.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikko\Documents\Luleå Damjun\Advanced stats_data\SDHL stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31F773F6-97EB-4CB6-BD84-5DB795BD07C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597AA593-5C3A-42AE-A4BE-F18FDC84C232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="33480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="57">
   <si>
     <t>Goal For</t>
   </si>
@@ -6906,7 +6906,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE8C601-DC7D-42D2-865D-643789981902}">
-  <dimension ref="A1:L150"/>
+  <dimension ref="A1:L154"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -12613,6 +12613,158 @@
         <v>0</v>
       </c>
     </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A151">
+        <v>5</v>
+      </c>
+      <c r="B151" t="s">
+        <v>55</v>
+      </c>
+      <c r="C151" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D151" t="s">
+        <v>14</v>
+      </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
+      <c r="F151">
+        <v>6</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>6</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A152">
+        <v>5</v>
+      </c>
+      <c r="B152" t="s">
+        <v>55</v>
+      </c>
+      <c r="C152" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D152" t="s">
+        <v>15</v>
+      </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
+      <c r="F152">
+        <v>4</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>1</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A153">
+        <v>5</v>
+      </c>
+      <c r="B153" t="s">
+        <v>55</v>
+      </c>
+      <c r="C153" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D153" t="s">
+        <v>16</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+      <c r="F153">
+        <v>8</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>2</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>5</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A154">
+        <v>5</v>
+      </c>
+      <c r="B154" t="s">
+        <v>55</v>
+      </c>
+      <c r="C154" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D154" t="s">
+        <v>17</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SDHL 2026-2027 scoring chances.xlsx
+++ b/SDHL 2026-2027 scoring chances.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikko\Documents\Luleå Damjun\Advanced stats_data\SDHL stats\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{597AA593-5C3A-42AE-A4BE-F18FDC84C232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B02F51-984B-4EF6-A905-4B224A9F7CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33480" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
+    <workbookView xWindow="33465" yWindow="135" windowWidth="24945" windowHeight="16950" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="58">
   <si>
     <t>Goal For</t>
   </si>
@@ -211,6 +211,9 @@
   </si>
   <si>
     <t>Turnover NZ</t>
+  </si>
+  <si>
+    <t>Farjestad</t>
   </si>
 </sst>
 </file>
@@ -592,7 +595,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4EB1DA-C9FF-4BF6-849D-6254FD5C05A8}">
-  <dimension ref="A1:P126"/>
+  <dimension ref="A1:P147"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="10.08984375" style="2" bestFit="1" customWidth="1"/>
@@ -6898,6 +6901,1056 @@
         <v>0</v>
       </c>
     </row>
+    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A127">
+        <v>6</v>
+      </c>
+      <c r="B127" t="s">
+        <v>57</v>
+      </c>
+      <c r="C127" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D127">
+        <v>15</v>
+      </c>
+      <c r="E127">
+        <v>0</v>
+      </c>
+      <c r="F127">
+        <v>0</v>
+      </c>
+      <c r="G127">
+        <v>0</v>
+      </c>
+      <c r="H127">
+        <v>1</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>0</v>
+      </c>
+      <c r="K127">
+        <v>0</v>
+      </c>
+      <c r="L127">
+        <v>0</v>
+      </c>
+      <c r="M127">
+        <v>0</v>
+      </c>
+      <c r="N127">
+        <v>3</v>
+      </c>
+      <c r="O127">
+        <v>0</v>
+      </c>
+      <c r="P127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A128">
+        <v>6</v>
+      </c>
+      <c r="B128" t="s">
+        <v>57</v>
+      </c>
+      <c r="C128" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D128">
+        <v>11</v>
+      </c>
+      <c r="E128">
+        <v>0</v>
+      </c>
+      <c r="F128">
+        <v>0</v>
+      </c>
+      <c r="G128">
+        <v>0</v>
+      </c>
+      <c r="H128">
+        <v>0</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>0</v>
+      </c>
+      <c r="L128">
+        <v>0</v>
+      </c>
+      <c r="M128">
+        <v>0</v>
+      </c>
+      <c r="N128">
+        <v>0</v>
+      </c>
+      <c r="O128">
+        <v>0</v>
+      </c>
+      <c r="P128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A129">
+        <v>6</v>
+      </c>
+      <c r="B129" t="s">
+        <v>57</v>
+      </c>
+      <c r="C129" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D129">
+        <v>81</v>
+      </c>
+      <c r="E129">
+        <v>0</v>
+      </c>
+      <c r="F129">
+        <v>0</v>
+      </c>
+      <c r="G129">
+        <v>1</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>0</v>
+      </c>
+      <c r="K129">
+        <v>0</v>
+      </c>
+      <c r="L129">
+        <v>0</v>
+      </c>
+      <c r="M129">
+        <v>0</v>
+      </c>
+      <c r="N129">
+        <v>0</v>
+      </c>
+      <c r="O129">
+        <v>0</v>
+      </c>
+      <c r="P129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A130">
+        <v>6</v>
+      </c>
+      <c r="B130" t="s">
+        <v>57</v>
+      </c>
+      <c r="C130" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D130">
+        <v>25</v>
+      </c>
+      <c r="E130">
+        <v>0</v>
+      </c>
+      <c r="F130">
+        <v>0</v>
+      </c>
+      <c r="G130">
+        <v>0</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>0</v>
+      </c>
+      <c r="K130">
+        <v>0</v>
+      </c>
+      <c r="L130">
+        <v>0</v>
+      </c>
+      <c r="M130">
+        <v>0</v>
+      </c>
+      <c r="N130">
+        <v>0</v>
+      </c>
+      <c r="O130">
+        <v>0</v>
+      </c>
+      <c r="P130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A131">
+        <v>6</v>
+      </c>
+      <c r="B131" t="s">
+        <v>57</v>
+      </c>
+      <c r="C131" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D131">
+        <v>39</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>0</v>
+      </c>
+      <c r="G131">
+        <v>1</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>0</v>
+      </c>
+      <c r="J131">
+        <v>0</v>
+      </c>
+      <c r="K131">
+        <v>0</v>
+      </c>
+      <c r="L131">
+        <v>0</v>
+      </c>
+      <c r="M131">
+        <v>0</v>
+      </c>
+      <c r="N131">
+        <v>0</v>
+      </c>
+      <c r="O131">
+        <v>0</v>
+      </c>
+      <c r="P131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A132">
+        <v>6</v>
+      </c>
+      <c r="B132" t="s">
+        <v>57</v>
+      </c>
+      <c r="C132" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D132">
+        <v>13</v>
+      </c>
+      <c r="E132">
+        <v>1</v>
+      </c>
+      <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>1</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
+        <v>0</v>
+      </c>
+      <c r="K132">
+        <v>0</v>
+      </c>
+      <c r="L132">
+        <v>0</v>
+      </c>
+      <c r="M132">
+        <v>0</v>
+      </c>
+      <c r="N132">
+        <v>0</v>
+      </c>
+      <c r="O132">
+        <v>0</v>
+      </c>
+      <c r="P132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A133">
+        <v>6</v>
+      </c>
+      <c r="B133" t="s">
+        <v>57</v>
+      </c>
+      <c r="C133" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D133">
+        <v>27</v>
+      </c>
+      <c r="E133">
+        <v>1</v>
+      </c>
+      <c r="F133">
+        <v>0</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>4</v>
+      </c>
+      <c r="I133">
+        <v>0</v>
+      </c>
+      <c r="J133">
+        <v>0</v>
+      </c>
+      <c r="K133">
+        <v>0</v>
+      </c>
+      <c r="L133">
+        <v>0</v>
+      </c>
+      <c r="M133">
+        <v>0</v>
+      </c>
+      <c r="N133">
+        <v>0</v>
+      </c>
+      <c r="O133">
+        <v>0</v>
+      </c>
+      <c r="P133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A134">
+        <v>6</v>
+      </c>
+      <c r="B134" t="s">
+        <v>57</v>
+      </c>
+      <c r="C134" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D134">
+        <v>24</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="F134">
+        <v>0</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>0</v>
+      </c>
+      <c r="J134">
+        <v>0</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+      <c r="L134">
+        <v>0</v>
+      </c>
+      <c r="M134">
+        <v>0</v>
+      </c>
+      <c r="N134">
+        <v>0</v>
+      </c>
+      <c r="O134">
+        <v>0</v>
+      </c>
+      <c r="P134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A135">
+        <v>6</v>
+      </c>
+      <c r="B135" t="s">
+        <v>57</v>
+      </c>
+      <c r="C135" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D135">
+        <v>19</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <v>0</v>
+      </c>
+      <c r="G135">
+        <v>0</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>0</v>
+      </c>
+      <c r="K135">
+        <v>0</v>
+      </c>
+      <c r="L135">
+        <v>0</v>
+      </c>
+      <c r="M135">
+        <v>0</v>
+      </c>
+      <c r="N135">
+        <v>0</v>
+      </c>
+      <c r="O135">
+        <v>0</v>
+      </c>
+      <c r="P135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A136">
+        <v>6</v>
+      </c>
+      <c r="B136" t="s">
+        <v>57</v>
+      </c>
+      <c r="C136" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D136">
+        <v>9</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="F136">
+        <v>0</v>
+      </c>
+      <c r="G136">
+        <v>0</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0</v>
+      </c>
+      <c r="K136">
+        <v>0</v>
+      </c>
+      <c r="L136">
+        <v>0</v>
+      </c>
+      <c r="M136">
+        <v>0</v>
+      </c>
+      <c r="N136">
+        <v>3</v>
+      </c>
+      <c r="O136">
+        <v>0</v>
+      </c>
+      <c r="P136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A137">
+        <v>6</v>
+      </c>
+      <c r="B137" t="s">
+        <v>57</v>
+      </c>
+      <c r="C137" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D137">
+        <v>44</v>
+      </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
+      <c r="F137">
+        <v>0</v>
+      </c>
+      <c r="G137">
+        <v>0</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>0</v>
+      </c>
+      <c r="K137">
+        <v>0</v>
+      </c>
+      <c r="L137">
+        <v>0</v>
+      </c>
+      <c r="M137">
+        <v>0</v>
+      </c>
+      <c r="N137">
+        <v>0</v>
+      </c>
+      <c r="O137">
+        <v>0</v>
+      </c>
+      <c r="P137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A138">
+        <v>6</v>
+      </c>
+      <c r="B138" t="s">
+        <v>57</v>
+      </c>
+      <c r="C138" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D138">
+        <v>6</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>1</v>
+      </c>
+      <c r="G138">
+        <v>0</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>0</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+      <c r="L138">
+        <v>0</v>
+      </c>
+      <c r="M138">
+        <v>0</v>
+      </c>
+      <c r="N138">
+        <v>0</v>
+      </c>
+      <c r="O138">
+        <v>0</v>
+      </c>
+      <c r="P138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A139">
+        <v>6</v>
+      </c>
+      <c r="B139" t="s">
+        <v>57</v>
+      </c>
+      <c r="C139" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D139">
+        <v>8</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <v>0</v>
+      </c>
+      <c r="G139">
+        <v>0</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>0</v>
+      </c>
+      <c r="K139">
+        <v>0</v>
+      </c>
+      <c r="L139">
+        <v>0</v>
+      </c>
+      <c r="M139">
+        <v>0</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+      <c r="O139">
+        <v>0</v>
+      </c>
+      <c r="P139">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A140">
+        <v>6</v>
+      </c>
+      <c r="B140" t="s">
+        <v>57</v>
+      </c>
+      <c r="C140" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D140">
+        <v>72</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <v>0</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>0</v>
+      </c>
+      <c r="J140">
+        <v>0</v>
+      </c>
+      <c r="K140">
+        <v>0</v>
+      </c>
+      <c r="L140">
+        <v>0</v>
+      </c>
+      <c r="M140">
+        <v>0</v>
+      </c>
+      <c r="N140">
+        <v>1</v>
+      </c>
+      <c r="O140">
+        <v>0</v>
+      </c>
+      <c r="P140">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A141">
+        <v>6</v>
+      </c>
+      <c r="B141" t="s">
+        <v>57</v>
+      </c>
+      <c r="C141" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D141">
+        <v>21</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="F141">
+        <v>0</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>0</v>
+      </c>
+      <c r="J141">
+        <v>0</v>
+      </c>
+      <c r="K141">
+        <v>0</v>
+      </c>
+      <c r="L141">
+        <v>0</v>
+      </c>
+      <c r="M141">
+        <v>1</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="O141">
+        <v>0</v>
+      </c>
+      <c r="P141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A142">
+        <v>6</v>
+      </c>
+      <c r="B142" t="s">
+        <v>57</v>
+      </c>
+      <c r="C142" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D142">
+        <v>42</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="F142">
+        <v>0</v>
+      </c>
+      <c r="G142">
+        <v>1</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>0</v>
+      </c>
+      <c r="J142">
+        <v>0</v>
+      </c>
+      <c r="K142">
+        <v>0</v>
+      </c>
+      <c r="L142">
+        <v>0</v>
+      </c>
+      <c r="M142">
+        <v>0</v>
+      </c>
+      <c r="N142">
+        <v>0</v>
+      </c>
+      <c r="O142">
+        <v>0</v>
+      </c>
+      <c r="P142">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A143">
+        <v>6</v>
+      </c>
+      <c r="B143" t="s">
+        <v>57</v>
+      </c>
+      <c r="C143" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D143">
+        <v>18</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>0</v>
+      </c>
+      <c r="G143">
+        <v>1</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>0</v>
+      </c>
+      <c r="K143">
+        <v>0</v>
+      </c>
+      <c r="L143">
+        <v>0</v>
+      </c>
+      <c r="M143">
+        <v>0</v>
+      </c>
+      <c r="N143">
+        <v>1</v>
+      </c>
+      <c r="O143">
+        <v>0</v>
+      </c>
+      <c r="P143">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A144">
+        <v>6</v>
+      </c>
+      <c r="B144" t="s">
+        <v>57</v>
+      </c>
+      <c r="C144" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D144">
+        <v>14</v>
+      </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
+      <c r="F144">
+        <v>0</v>
+      </c>
+      <c r="G144">
+        <v>1</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>0</v>
+      </c>
+      <c r="K144">
+        <v>0</v>
+      </c>
+      <c r="L144">
+        <v>0</v>
+      </c>
+      <c r="M144">
+        <v>0</v>
+      </c>
+      <c r="N144">
+        <v>2</v>
+      </c>
+      <c r="O144">
+        <v>0</v>
+      </c>
+      <c r="P144">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A145">
+        <v>6</v>
+      </c>
+      <c r="B145" t="s">
+        <v>57</v>
+      </c>
+      <c r="C145" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D145">
+        <v>56</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+      <c r="F145">
+        <v>0</v>
+      </c>
+      <c r="G145">
+        <v>0</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>0</v>
+      </c>
+      <c r="K145">
+        <v>0</v>
+      </c>
+      <c r="L145">
+        <v>0</v>
+      </c>
+      <c r="M145">
+        <v>0</v>
+      </c>
+      <c r="N145">
+        <v>0</v>
+      </c>
+      <c r="O145">
+        <v>0</v>
+      </c>
+      <c r="P145">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A146">
+        <v>6</v>
+      </c>
+      <c r="B146" t="s">
+        <v>57</v>
+      </c>
+      <c r="C146" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D146">
+        <v>71</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <v>0</v>
+      </c>
+      <c r="G146">
+        <v>4</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>0</v>
+      </c>
+      <c r="K146">
+        <v>0</v>
+      </c>
+      <c r="L146">
+        <v>0</v>
+      </c>
+      <c r="M146">
+        <v>0</v>
+      </c>
+      <c r="N146">
+        <v>2</v>
+      </c>
+      <c r="O146">
+        <v>0</v>
+      </c>
+      <c r="P146">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A147">
+        <v>6</v>
+      </c>
+      <c r="B147" t="s">
+        <v>57</v>
+      </c>
+      <c r="C147" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D147">
+        <v>23</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+      <c r="F147">
+        <v>1</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>2</v>
+      </c>
+      <c r="I147">
+        <v>0</v>
+      </c>
+      <c r="J147">
+        <v>0</v>
+      </c>
+      <c r="K147">
+        <v>0</v>
+      </c>
+      <c r="L147">
+        <v>0</v>
+      </c>
+      <c r="M147">
+        <v>0</v>
+      </c>
+      <c r="N147">
+        <v>1</v>
+      </c>
+      <c r="O147">
+        <v>0</v>
+      </c>
+      <c r="P147">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6906,7 +7959,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE8C601-DC7D-42D2-865D-643789981902}">
-  <dimension ref="A1:L154"/>
+  <dimension ref="A1:L184"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
@@ -12765,6 +13818,1146 @@
         <v>0</v>
       </c>
     </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A155">
+        <v>6</v>
+      </c>
+      <c r="B155" t="s">
+        <v>57</v>
+      </c>
+      <c r="C155" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D155" t="s">
+        <v>19</v>
+      </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
+      <c r="F155">
+        <v>1</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>0</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A156">
+        <v>6</v>
+      </c>
+      <c r="B156" t="s">
+        <v>57</v>
+      </c>
+      <c r="C156" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D156" t="s">
+        <v>20</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A157">
+        <v>6</v>
+      </c>
+      <c r="B157" t="s">
+        <v>57</v>
+      </c>
+      <c r="C157" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D157" t="s">
+        <v>21</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+      <c r="F157">
+        <v>3</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>5</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A158">
+        <v>6</v>
+      </c>
+      <c r="B158" t="s">
+        <v>57</v>
+      </c>
+      <c r="C158" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D158" t="s">
+        <v>22</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158">
+        <v>0</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A159">
+        <v>6</v>
+      </c>
+      <c r="B159" t="s">
+        <v>57</v>
+      </c>
+      <c r="C159" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D159" t="s">
+        <v>23</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+      <c r="F159">
+        <v>0</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>2</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A160">
+        <v>6</v>
+      </c>
+      <c r="B160" t="s">
+        <v>57</v>
+      </c>
+      <c r="C160" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D160" t="s">
+        <v>24</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+      <c r="F160">
+        <v>0</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A161">
+        <v>6</v>
+      </c>
+      <c r="B161" t="s">
+        <v>57</v>
+      </c>
+      <c r="C161" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D161" t="s">
+        <v>25</v>
+      </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
+      <c r="F161">
+        <v>1</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>1</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A162">
+        <v>6</v>
+      </c>
+      <c r="B162" t="s">
+        <v>57</v>
+      </c>
+      <c r="C162" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D162" t="s">
+        <v>27</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
+      <c r="F162">
+        <v>0</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A163">
+        <v>6</v>
+      </c>
+      <c r="B163" t="s">
+        <v>57</v>
+      </c>
+      <c r="C163" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D163" t="s">
+        <v>28</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
+      <c r="F163">
+        <v>0</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A164">
+        <v>6</v>
+      </c>
+      <c r="B164" t="s">
+        <v>57</v>
+      </c>
+      <c r="C164" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D164" t="s">
+        <v>31</v>
+      </c>
+      <c r="E164">
+        <v>0</v>
+      </c>
+      <c r="F164">
+        <v>0</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A165">
+        <v>6</v>
+      </c>
+      <c r="B165" t="s">
+        <v>57</v>
+      </c>
+      <c r="C165" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D165" t="s">
+        <v>33</v>
+      </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A166">
+        <v>6</v>
+      </c>
+      <c r="B166" t="s">
+        <v>57</v>
+      </c>
+      <c r="C166" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D166" t="s">
+        <v>37</v>
+      </c>
+      <c r="E166">
+        <v>0</v>
+      </c>
+      <c r="F166">
+        <v>0</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A167">
+        <v>6</v>
+      </c>
+      <c r="B167" t="s">
+        <v>57</v>
+      </c>
+      <c r="C167" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D167" t="s">
+        <v>38</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="F167">
+        <v>0</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A168">
+        <v>6</v>
+      </c>
+      <c r="B168" t="s">
+        <v>57</v>
+      </c>
+      <c r="C168" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D168" t="s">
+        <v>39</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+      <c r="F168">
+        <v>0</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A169">
+        <v>6</v>
+      </c>
+      <c r="B169" t="s">
+        <v>57</v>
+      </c>
+      <c r="C169" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D169" t="s">
+        <v>40</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A170">
+        <v>6</v>
+      </c>
+      <c r="B170" t="s">
+        <v>57</v>
+      </c>
+      <c r="C170" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D170" t="s">
+        <v>41</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
+      <c r="F170">
+        <v>0</v>
+      </c>
+      <c r="G170">
+        <v>0</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A171">
+        <v>6</v>
+      </c>
+      <c r="B171" t="s">
+        <v>57</v>
+      </c>
+      <c r="C171" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D171" t="s">
+        <v>42</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>0</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A172">
+        <v>6</v>
+      </c>
+      <c r="B172" t="s">
+        <v>57</v>
+      </c>
+      <c r="C172" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D172" t="s">
+        <v>32</v>
+      </c>
+      <c r="E172">
+        <v>1</v>
+      </c>
+      <c r="F172">
+        <v>4</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>1</v>
+      </c>
+      <c r="J172">
+        <v>1</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A173">
+        <v>6</v>
+      </c>
+      <c r="B173" t="s">
+        <v>57</v>
+      </c>
+      <c r="C173" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D173" t="s">
+        <v>56</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+      <c r="F173">
+        <v>0</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>1</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A174">
+        <v>6</v>
+      </c>
+      <c r="B174" t="s">
+        <v>57</v>
+      </c>
+      <c r="C174" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D174" t="s">
+        <v>30</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+      <c r="F174">
+        <v>0</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>0</v>
+      </c>
+      <c r="J174">
+        <v>1</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A175">
+        <v>6</v>
+      </c>
+      <c r="B175" t="s">
+        <v>57</v>
+      </c>
+      <c r="C175" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D175" t="s">
+        <v>26</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A176">
+        <v>6</v>
+      </c>
+      <c r="B176" t="s">
+        <v>57</v>
+      </c>
+      <c r="C176" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D176" t="s">
+        <v>29</v>
+      </c>
+      <c r="E176">
+        <v>0</v>
+      </c>
+      <c r="F176">
+        <v>0</v>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A177">
+        <v>6</v>
+      </c>
+      <c r="B177" t="s">
+        <v>57</v>
+      </c>
+      <c r="C177" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D177" t="s">
+        <v>36</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
+      <c r="F177">
+        <v>0</v>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A178">
+        <v>6</v>
+      </c>
+      <c r="B178" t="s">
+        <v>57</v>
+      </c>
+      <c r="C178" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D178" t="s">
+        <v>35</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+      <c r="F178">
+        <v>0</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A179">
+        <v>6</v>
+      </c>
+      <c r="B179" t="s">
+        <v>57</v>
+      </c>
+      <c r="C179" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D179" t="s">
+        <v>18</v>
+      </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
+      <c r="F179">
+        <v>1</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>2</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A180">
+        <v>6</v>
+      </c>
+      <c r="B180" t="s">
+        <v>57</v>
+      </c>
+      <c r="C180" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D180" t="s">
+        <v>34</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+      <c r="F180">
+        <v>0</v>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>2</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A181">
+        <v>6</v>
+      </c>
+      <c r="B181" t="s">
+        <v>57</v>
+      </c>
+      <c r="C181" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D181" t="s">
+        <v>14</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
+      <c r="F181">
+        <v>7</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>3</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A182">
+        <v>6</v>
+      </c>
+      <c r="B182" t="s">
+        <v>57</v>
+      </c>
+      <c r="C182" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D182" t="s">
+        <v>15</v>
+      </c>
+      <c r="E182">
+        <v>2</v>
+      </c>
+      <c r="F182">
+        <v>2</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>9</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A183">
+        <v>6</v>
+      </c>
+      <c r="B183" t="s">
+        <v>57</v>
+      </c>
+      <c r="C183" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D183" t="s">
+        <v>16</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
+      <c r="F183">
+        <v>1</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>1</v>
+      </c>
+      <c r="J183">
+        <v>4</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="A184">
+        <v>6</v>
+      </c>
+      <c r="B184" t="s">
+        <v>57</v>
+      </c>
+      <c r="C184" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D184" t="s">
+        <v>17</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/SDHL 2026-2027 scoring chances.xlsx
+++ b/SDHL 2026-2027 scoring chances.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mikko\Documents\Luleå Damjun\Advanced stats_data\SDHL stats\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mikko/Desktop/Luleå Damjun/Advanced stats_data/SDHL stats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B02F51-984B-4EF6-A905-4B224A9F7CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B6B245-2387-E840-912E-A7D80C90C54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33465" yWindow="135" windowWidth="24945" windowHeight="16950" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
+    <workbookView xWindow="29620" yWindow="600" windowWidth="30400" windowHeight="22780" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="59">
   <si>
     <t>Goal For</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t>Period 3</t>
-  </si>
-  <si>
-    <t>OT</t>
   </si>
   <si>
     <t>OZ tip</t>
@@ -214,6 +211,12 @@
   </si>
   <si>
     <t>Farjestad</t>
+  </si>
+  <si>
+    <t>Period OT</t>
+  </si>
+  <si>
+    <t>OT</t>
   </si>
 </sst>
 </file>
@@ -595,21 +598,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4EB1DA-C9FF-4BF6-849D-6254FD5C05A8}">
-  <dimension ref="A1:P147"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:P166"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="10.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -651,12 +654,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2">
         <v>46278</v>
@@ -701,12 +704,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2">
         <v>46278</v>
@@ -751,12 +754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2">
         <v>46278</v>
@@ -801,12 +804,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2">
         <v>46278</v>
@@ -851,12 +854,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2">
         <v>46278</v>
@@ -901,12 +904,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2">
         <v>46278</v>
@@ -951,12 +954,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2">
         <v>46278</v>
@@ -1001,12 +1004,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2">
         <v>46278</v>
@@ -1051,12 +1054,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" s="2">
         <v>46278</v>
@@ -1101,12 +1104,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2">
         <v>46278</v>
@@ -1151,12 +1154,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="2">
         <v>46278</v>
@@ -1201,12 +1204,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="2">
         <v>46278</v>
@@ -1251,12 +1254,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2">
         <v>46278</v>
@@ -1301,12 +1304,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="2">
         <v>46278</v>
@@ -1351,12 +1354,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2">
         <v>46278</v>
@@ -1401,12 +1404,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="2">
         <v>46278</v>
@@ -1451,12 +1454,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2">
         <v>46278</v>
@@ -1501,12 +1504,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2">
         <v>46278</v>
@@ -1551,12 +1554,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C20" s="2">
         <v>46278</v>
@@ -1601,12 +1604,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2">
         <v>46278</v>
@@ -1651,12 +1654,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2">
         <v>46278</v>
@@ -1701,12 +1704,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C23" s="2">
         <v>46282</v>
@@ -1751,12 +1754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24" s="2">
         <v>46282</v>
@@ -1801,12 +1804,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2">
         <v>46282</v>
@@ -1851,12 +1854,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C26" s="2">
         <v>46282</v>
@@ -1901,12 +1904,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C27" s="2">
         <v>46282</v>
@@ -1951,12 +1954,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C28" s="2">
         <v>46282</v>
@@ -2001,12 +2004,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C29" s="2">
         <v>46282</v>
@@ -2051,12 +2054,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C30" s="2">
         <v>46282</v>
@@ -2101,12 +2104,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31" s="2">
         <v>46282</v>
@@ -2151,12 +2154,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C32" s="2">
         <v>46282</v>
@@ -2201,12 +2204,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" s="2">
         <v>46282</v>
@@ -2251,12 +2254,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34" s="2">
         <v>46282</v>
@@ -2301,12 +2304,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="2">
         <v>46282</v>
@@ -2351,12 +2354,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="2">
         <v>46282</v>
@@ -2401,12 +2404,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="2">
         <v>46282</v>
@@ -2451,12 +2454,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" s="2">
         <v>46282</v>
@@ -2501,12 +2504,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" s="2">
         <v>46282</v>
@@ -2551,12 +2554,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="2">
         <v>46282</v>
@@ -2601,12 +2604,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" s="2">
         <v>46282</v>
@@ -2651,12 +2654,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C42" s="2">
         <v>46282</v>
@@ -2701,12 +2704,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" s="2">
         <v>46282</v>
@@ -2751,12 +2754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C44" s="2">
         <v>46285</v>
@@ -2801,12 +2804,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C45" s="2">
         <v>46285</v>
@@ -2851,12 +2854,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C46" s="2">
         <v>46285</v>
@@ -2901,12 +2904,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C47" s="2">
         <v>46285</v>
@@ -2951,12 +2954,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C48" s="2">
         <v>46285</v>
@@ -3001,12 +3004,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C49" s="2">
         <v>46285</v>
@@ -3051,12 +3054,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" s="2">
         <v>46285</v>
@@ -3101,12 +3104,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C51" s="2">
         <v>46285</v>
@@ -3151,12 +3154,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" s="2">
         <v>46285</v>
@@ -3201,12 +3204,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C53" s="2">
         <v>46285</v>
@@ -3251,12 +3254,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C54" s="2">
         <v>46285</v>
@@ -3301,12 +3304,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C55" s="2">
         <v>46285</v>
@@ -3351,12 +3354,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C56" s="2">
         <v>46285</v>
@@ -3401,12 +3404,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C57" s="2">
         <v>46285</v>
@@ -3451,12 +3454,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C58" s="2">
         <v>46285</v>
@@ -3501,12 +3504,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C59" s="2">
         <v>46285</v>
@@ -3551,12 +3554,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C60" s="2">
         <v>46285</v>
@@ -3601,12 +3604,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C61" s="2">
         <v>46285</v>
@@ -3651,12 +3654,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C62" s="2">
         <v>46285</v>
@@ -3701,12 +3704,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C63" s="2">
         <v>46285</v>
@@ -3751,12 +3754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C64" s="2">
         <v>46285</v>
@@ -3801,12 +3804,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C65" s="2">
         <v>46291</v>
@@ -3851,12 +3854,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C66" s="2">
         <v>46291</v>
@@ -3901,12 +3904,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C67" s="2">
         <v>46291</v>
@@ -3951,12 +3954,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>4</v>
       </c>
       <c r="B68" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C68" s="2">
         <v>46291</v>
@@ -4001,12 +4004,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C69" s="2">
         <v>46291</v>
@@ -4051,12 +4054,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C70" s="2">
         <v>46291</v>
@@ -4101,12 +4104,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C71" s="2">
         <v>46291</v>
@@ -4151,12 +4154,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C72" s="2">
         <v>46291</v>
@@ -4201,12 +4204,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C73" s="2">
         <v>46291</v>
@@ -4251,12 +4254,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C74" s="2">
         <v>46291</v>
@@ -4301,12 +4304,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C75" s="2">
         <v>46291</v>
@@ -4351,12 +4354,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>4</v>
       </c>
       <c r="B76" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C76" s="2">
         <v>46291</v>
@@ -4401,12 +4404,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>4</v>
       </c>
       <c r="B77" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C77" s="2">
         <v>46291</v>
@@ -4451,12 +4454,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>4</v>
       </c>
       <c r="B78" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C78" s="2">
         <v>46291</v>
@@ -4501,12 +4504,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>4</v>
       </c>
       <c r="B79" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C79" s="2">
         <v>46291</v>
@@ -4551,12 +4554,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C80" s="2">
         <v>46291</v>
@@ -4601,12 +4604,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>4</v>
       </c>
       <c r="B81" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C81" s="2">
         <v>46291</v>
@@ -4651,12 +4654,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>4</v>
       </c>
       <c r="B82" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C82" s="2">
         <v>46291</v>
@@ -4701,12 +4704,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>4</v>
       </c>
       <c r="B83" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C83" s="2">
         <v>46291</v>
@@ -4751,12 +4754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>4</v>
       </c>
       <c r="B84" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C84" s="2">
         <v>46291</v>
@@ -4801,12 +4804,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C85" s="2">
         <v>46291</v>
@@ -4851,12 +4854,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>4</v>
       </c>
       <c r="B86" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C86" s="2">
         <v>46291</v>
@@ -4901,12 +4904,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C87" s="2">
         <v>46291</v>
@@ -4951,12 +4954,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>4</v>
       </c>
       <c r="B88" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C88" s="2">
         <v>46291</v>
@@ -5001,12 +5004,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C89" s="2">
         <v>46291</v>
@@ -5051,12 +5054,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C90" s="2">
         <v>46291</v>
@@ -5101,12 +5104,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C91" s="2">
         <v>46291</v>
@@ -5151,12 +5154,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C92" s="2">
         <v>46291</v>
@@ -5201,12 +5204,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>4</v>
       </c>
       <c r="B93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C93" s="2">
         <v>46291</v>
@@ -5251,12 +5254,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>4</v>
       </c>
       <c r="B94" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C94" s="2">
         <v>46291</v>
@@ -5301,12 +5304,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>4</v>
       </c>
       <c r="B95" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C95" s="2">
         <v>46291</v>
@@ -5351,12 +5354,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C96" s="2">
         <v>46304</v>
@@ -5401,12 +5404,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C97" s="2">
         <v>46304</v>
@@ -5451,12 +5454,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C98" s="2">
         <v>46304</v>
@@ -5501,12 +5504,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C99" s="2">
         <v>46304</v>
@@ -5551,12 +5554,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C100" s="2">
         <v>46304</v>
@@ -5601,12 +5604,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>5</v>
       </c>
       <c r="B101" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C101" s="2">
         <v>46304</v>
@@ -5651,12 +5654,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>5</v>
       </c>
       <c r="B102" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C102" s="2">
         <v>46304</v>
@@ -5701,12 +5704,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C103" s="2">
         <v>46304</v>
@@ -5751,12 +5754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>5</v>
       </c>
       <c r="B104" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C104" s="2">
         <v>46304</v>
@@ -5801,12 +5804,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C105" s="2">
         <v>46304</v>
@@ -5851,12 +5854,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C106" s="2">
         <v>46304</v>
@@ -5901,12 +5904,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>5</v>
       </c>
       <c r="B107" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C107" s="2">
         <v>46304</v>
@@ -5951,12 +5954,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>5</v>
       </c>
       <c r="B108" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C108" s="2">
         <v>46304</v>
@@ -6001,12 +6004,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>5</v>
       </c>
       <c r="B109" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C109" s="2">
         <v>46304</v>
@@ -6051,12 +6054,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>5</v>
       </c>
       <c r="B110" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C110" s="2">
         <v>46304</v>
@@ -6101,12 +6104,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>5</v>
       </c>
       <c r="B111" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C111" s="2">
         <v>46304</v>
@@ -6151,12 +6154,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C112" s="2">
         <v>46304</v>
@@ -6201,12 +6204,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>5</v>
       </c>
       <c r="B113" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C113" s="2">
         <v>46304</v>
@@ -6251,12 +6254,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>5</v>
       </c>
       <c r="B114" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C114" s="2">
         <v>46304</v>
@@ -6301,12 +6304,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>5</v>
       </c>
       <c r="B115" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C115" s="2">
         <v>46304</v>
@@ -6351,12 +6354,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>5</v>
       </c>
       <c r="B116" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C116" s="2">
         <v>46304</v>
@@ -6401,12 +6404,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>5</v>
       </c>
       <c r="B117" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C117" s="2">
         <v>46304</v>
@@ -6451,12 +6454,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>5</v>
       </c>
       <c r="B118" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C118" s="2">
         <v>46304</v>
@@ -6501,12 +6504,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>5</v>
       </c>
       <c r="B119" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C119" s="2">
         <v>46304</v>
@@ -6551,12 +6554,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>5</v>
       </c>
       <c r="B120" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C120" s="2">
         <v>46304</v>
@@ -6601,12 +6604,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>5</v>
       </c>
       <c r="B121" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C121" s="2">
         <v>46304</v>
@@ -6651,12 +6654,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>5</v>
       </c>
       <c r="B122" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C122" s="2">
         <v>46304</v>
@@ -6701,12 +6704,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>5</v>
       </c>
       <c r="B123" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C123" s="2">
         <v>46304</v>
@@ -6751,12 +6754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>5</v>
       </c>
       <c r="B124" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C124" s="2">
         <v>46304</v>
@@ -6801,12 +6804,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>5</v>
       </c>
       <c r="B125" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C125" s="2">
         <v>46304</v>
@@ -6851,12 +6854,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>5</v>
       </c>
       <c r="B126" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C126" s="2">
         <v>46304</v>
@@ -6901,12 +6904,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>6</v>
       </c>
       <c r="B127" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C127" s="2">
         <v>46306</v>
@@ -6951,12 +6954,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>6</v>
       </c>
       <c r="B128" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C128" s="2">
         <v>46306</v>
@@ -7001,12 +7004,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>6</v>
       </c>
       <c r="B129" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C129" s="2">
         <v>46306</v>
@@ -7051,12 +7054,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>6</v>
       </c>
       <c r="B130" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C130" s="2">
         <v>46306</v>
@@ -7101,12 +7104,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>6</v>
       </c>
       <c r="B131" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C131" s="2">
         <v>46306</v>
@@ -7151,12 +7154,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>6</v>
       </c>
       <c r="B132" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C132" s="2">
         <v>46306</v>
@@ -7201,12 +7204,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>6</v>
       </c>
       <c r="B133" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C133" s="2">
         <v>46306</v>
@@ -7251,12 +7254,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>6</v>
       </c>
       <c r="B134" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C134" s="2">
         <v>46306</v>
@@ -7301,12 +7304,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>6</v>
       </c>
       <c r="B135" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C135" s="2">
         <v>46306</v>
@@ -7351,12 +7354,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>6</v>
       </c>
       <c r="B136" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C136" s="2">
         <v>46306</v>
@@ -7401,12 +7404,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>6</v>
       </c>
       <c r="B137" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C137" s="2">
         <v>46306</v>
@@ -7451,12 +7454,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>6</v>
       </c>
       <c r="B138" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C138" s="2">
         <v>46306</v>
@@ -7501,12 +7504,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>6</v>
       </c>
       <c r="B139" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C139" s="2">
         <v>46306</v>
@@ -7551,12 +7554,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>6</v>
       </c>
       <c r="B140" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C140" s="2">
         <v>46306</v>
@@ -7601,12 +7604,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>6</v>
       </c>
       <c r="B141" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C141" s="2">
         <v>46306</v>
@@ -7651,12 +7654,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>6</v>
       </c>
       <c r="B142" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C142" s="2">
         <v>46306</v>
@@ -7701,12 +7704,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>6</v>
       </c>
       <c r="B143" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C143" s="2">
         <v>46306</v>
@@ -7751,12 +7754,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>6</v>
       </c>
       <c r="B144" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C144" s="2">
         <v>46306</v>
@@ -7801,12 +7804,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C145" s="2">
         <v>46306</v>
@@ -7851,12 +7854,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C146" s="2">
         <v>46306</v>
@@ -7901,12 +7904,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>6</v>
       </c>
       <c r="B147" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C147" s="2">
         <v>46306</v>
@@ -7948,6 +7951,956 @@
         <v>0</v>
       </c>
       <c r="P147">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A148">
+        <v>7</v>
+      </c>
+      <c r="B148" t="s">
+        <v>56</v>
+      </c>
+      <c r="C148" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D148">
+        <v>71</v>
+      </c>
+      <c r="E148">
+        <v>2</v>
+      </c>
+      <c r="F148">
+        <v>1</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>0</v>
+      </c>
+      <c r="J148">
+        <v>1</v>
+      </c>
+      <c r="K148">
+        <v>1</v>
+      </c>
+      <c r="L148">
+        <v>0</v>
+      </c>
+      <c r="M148">
+        <v>0</v>
+      </c>
+      <c r="N148">
+        <v>1</v>
+      </c>
+      <c r="O148">
+        <v>0</v>
+      </c>
+      <c r="P148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A149">
+        <v>7</v>
+      </c>
+      <c r="B149" t="s">
+        <v>56</v>
+      </c>
+      <c r="C149" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D149">
+        <v>13</v>
+      </c>
+      <c r="E149">
+        <v>1</v>
+      </c>
+      <c r="F149">
+        <v>0</v>
+      </c>
+      <c r="G149">
+        <v>1</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>0</v>
+      </c>
+      <c r="J149">
+        <v>0</v>
+      </c>
+      <c r="K149">
+        <v>0</v>
+      </c>
+      <c r="L149">
+        <v>1</v>
+      </c>
+      <c r="M149">
+        <v>0</v>
+      </c>
+      <c r="N149">
+        <v>0</v>
+      </c>
+      <c r="O149">
+        <v>0</v>
+      </c>
+      <c r="P149">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A150">
+        <v>7</v>
+      </c>
+      <c r="B150" t="s">
+        <v>56</v>
+      </c>
+      <c r="C150" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D150">
+        <v>27</v>
+      </c>
+      <c r="E150">
+        <v>3</v>
+      </c>
+      <c r="F150">
+        <v>0</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150">
+        <v>1</v>
+      </c>
+      <c r="J150">
+        <v>0</v>
+      </c>
+      <c r="K150">
+        <v>1</v>
+      </c>
+      <c r="L150">
+        <v>1</v>
+      </c>
+      <c r="M150">
+        <v>0</v>
+      </c>
+      <c r="N150">
+        <v>1</v>
+      </c>
+      <c r="O150">
+        <v>0</v>
+      </c>
+      <c r="P150">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A151">
+        <v>7</v>
+      </c>
+      <c r="B151" t="s">
+        <v>56</v>
+      </c>
+      <c r="C151" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D151">
+        <v>23</v>
+      </c>
+      <c r="E151">
+        <v>2</v>
+      </c>
+      <c r="F151">
+        <v>0</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151">
+        <v>0</v>
+      </c>
+      <c r="J151">
+        <v>0</v>
+      </c>
+      <c r="K151">
+        <v>0</v>
+      </c>
+      <c r="L151">
+        <v>0</v>
+      </c>
+      <c r="M151">
+        <v>0</v>
+      </c>
+      <c r="N151">
+        <v>0</v>
+      </c>
+      <c r="O151">
+        <v>0</v>
+      </c>
+      <c r="P151">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A152">
+        <v>7</v>
+      </c>
+      <c r="B152" t="s">
+        <v>56</v>
+      </c>
+      <c r="C152" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D152">
+        <v>14</v>
+      </c>
+      <c r="E152">
+        <v>1</v>
+      </c>
+      <c r="F152">
+        <v>0</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>0</v>
+      </c>
+      <c r="J152">
+        <v>0</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+      <c r="L152">
+        <v>1</v>
+      </c>
+      <c r="M152">
+        <v>0</v>
+      </c>
+      <c r="N152">
+        <v>2</v>
+      </c>
+      <c r="O152">
+        <v>0</v>
+      </c>
+      <c r="P152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A153">
+        <v>7</v>
+      </c>
+      <c r="B153" t="s">
+        <v>56</v>
+      </c>
+      <c r="C153" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D153">
+        <v>15</v>
+      </c>
+      <c r="E153">
+        <v>2</v>
+      </c>
+      <c r="F153">
+        <v>0</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>2</v>
+      </c>
+      <c r="I153">
+        <v>0</v>
+      </c>
+      <c r="J153">
+        <v>0</v>
+      </c>
+      <c r="K153">
+        <v>1</v>
+      </c>
+      <c r="L153">
+        <v>0</v>
+      </c>
+      <c r="M153">
+        <v>1</v>
+      </c>
+      <c r="N153">
+        <v>2</v>
+      </c>
+      <c r="O153">
+        <v>0</v>
+      </c>
+      <c r="P153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A154">
+        <v>7</v>
+      </c>
+      <c r="B154" t="s">
+        <v>56</v>
+      </c>
+      <c r="C154" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D154">
+        <v>42</v>
+      </c>
+      <c r="E154">
+        <v>1</v>
+      </c>
+      <c r="F154">
+        <v>0</v>
+      </c>
+      <c r="G154">
+        <v>1</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>0</v>
+      </c>
+      <c r="J154">
+        <v>0</v>
+      </c>
+      <c r="K154">
+        <v>0</v>
+      </c>
+      <c r="L154">
+        <v>0</v>
+      </c>
+      <c r="M154">
+        <v>0</v>
+      </c>
+      <c r="N154">
+        <v>0</v>
+      </c>
+      <c r="O154">
+        <v>0</v>
+      </c>
+      <c r="P154">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A155">
+        <v>7</v>
+      </c>
+      <c r="B155" t="s">
+        <v>56</v>
+      </c>
+      <c r="C155" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D155">
+        <v>6</v>
+      </c>
+      <c r="E155">
+        <v>1</v>
+      </c>
+      <c r="F155">
+        <v>0</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="H155">
+        <v>1</v>
+      </c>
+      <c r="I155">
+        <v>0</v>
+      </c>
+      <c r="J155">
+        <v>2</v>
+      </c>
+      <c r="K155">
+        <v>0</v>
+      </c>
+      <c r="L155">
+        <v>0</v>
+      </c>
+      <c r="M155">
+        <v>0</v>
+      </c>
+      <c r="N155">
+        <v>1</v>
+      </c>
+      <c r="O155">
+        <v>1</v>
+      </c>
+      <c r="P155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A156">
+        <v>7</v>
+      </c>
+      <c r="B156" t="s">
+        <v>56</v>
+      </c>
+      <c r="C156" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D156">
+        <v>8</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+      <c r="F156">
+        <v>0</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>0</v>
+      </c>
+      <c r="J156">
+        <v>0</v>
+      </c>
+      <c r="K156">
+        <v>0</v>
+      </c>
+      <c r="L156">
+        <v>0</v>
+      </c>
+      <c r="M156">
+        <v>0</v>
+      </c>
+      <c r="N156">
+        <v>0</v>
+      </c>
+      <c r="O156">
+        <v>0</v>
+      </c>
+      <c r="P156">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A157">
+        <v>7</v>
+      </c>
+      <c r="B157" t="s">
+        <v>56</v>
+      </c>
+      <c r="C157" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D157">
+        <v>9</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+      <c r="F157">
+        <v>0</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>0</v>
+      </c>
+      <c r="J157">
+        <v>0</v>
+      </c>
+      <c r="K157">
+        <v>0</v>
+      </c>
+      <c r="L157">
+        <v>0</v>
+      </c>
+      <c r="M157">
+        <v>0</v>
+      </c>
+      <c r="N157">
+        <v>0</v>
+      </c>
+      <c r="O157">
+        <v>0</v>
+      </c>
+      <c r="P157">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A158">
+        <v>7</v>
+      </c>
+      <c r="B158" t="s">
+        <v>56</v>
+      </c>
+      <c r="C158" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D158">
+        <v>18</v>
+      </c>
+      <c r="E158">
+        <v>1</v>
+      </c>
+      <c r="F158">
+        <v>1</v>
+      </c>
+      <c r="G158">
+        <v>1</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>0</v>
+      </c>
+      <c r="J158">
+        <v>0</v>
+      </c>
+      <c r="K158">
+        <v>0</v>
+      </c>
+      <c r="L158">
+        <v>0</v>
+      </c>
+      <c r="M158">
+        <v>0</v>
+      </c>
+      <c r="N158">
+        <v>0</v>
+      </c>
+      <c r="O158">
+        <v>0</v>
+      </c>
+      <c r="P158">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A159">
+        <v>7</v>
+      </c>
+      <c r="B159" t="s">
+        <v>56</v>
+      </c>
+      <c r="C159" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D159">
+        <v>21</v>
+      </c>
+      <c r="E159">
+        <v>1</v>
+      </c>
+      <c r="F159">
+        <v>1</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>0</v>
+      </c>
+      <c r="J159">
+        <v>0</v>
+      </c>
+      <c r="K159">
+        <v>0</v>
+      </c>
+      <c r="L159">
+        <v>0</v>
+      </c>
+      <c r="M159">
+        <v>0</v>
+      </c>
+      <c r="N159">
+        <v>1</v>
+      </c>
+      <c r="O159">
+        <v>0</v>
+      </c>
+      <c r="P159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A160">
+        <v>7</v>
+      </c>
+      <c r="B160" t="s">
+        <v>56</v>
+      </c>
+      <c r="C160" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D160">
+        <v>39</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+      <c r="F160">
+        <v>0</v>
+      </c>
+      <c r="G160">
+        <v>2</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
+        <v>0</v>
+      </c>
+      <c r="J160">
+        <v>0</v>
+      </c>
+      <c r="K160">
+        <v>0</v>
+      </c>
+      <c r="L160">
+        <v>0</v>
+      </c>
+      <c r="M160">
+        <v>0</v>
+      </c>
+      <c r="N160">
+        <v>0</v>
+      </c>
+      <c r="O160">
+        <v>0</v>
+      </c>
+      <c r="P160">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A161">
+        <v>7</v>
+      </c>
+      <c r="B161" t="s">
+        <v>56</v>
+      </c>
+      <c r="C161" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D161">
+        <v>20</v>
+      </c>
+      <c r="E161">
+        <v>1</v>
+      </c>
+      <c r="F161">
+        <v>0</v>
+      </c>
+      <c r="G161">
+        <v>1</v>
+      </c>
+      <c r="H161">
+        <v>1</v>
+      </c>
+      <c r="I161">
+        <v>0</v>
+      </c>
+      <c r="J161">
+        <v>0</v>
+      </c>
+      <c r="K161">
+        <v>0</v>
+      </c>
+      <c r="L161">
+        <v>0</v>
+      </c>
+      <c r="M161">
+        <v>0</v>
+      </c>
+      <c r="N161">
+        <v>0</v>
+      </c>
+      <c r="O161">
+        <v>0</v>
+      </c>
+      <c r="P161">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A162">
+        <v>7</v>
+      </c>
+      <c r="B162" t="s">
+        <v>56</v>
+      </c>
+      <c r="C162" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D162">
+        <v>72</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
+      <c r="F162">
+        <v>0</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>0</v>
+      </c>
+      <c r="J162">
+        <v>0</v>
+      </c>
+      <c r="K162">
+        <v>0</v>
+      </c>
+      <c r="L162">
+        <v>0</v>
+      </c>
+      <c r="M162">
+        <v>1</v>
+      </c>
+      <c r="N162">
+        <v>0</v>
+      </c>
+      <c r="O162">
+        <v>0</v>
+      </c>
+      <c r="P162">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A163">
+        <v>7</v>
+      </c>
+      <c r="B163" t="s">
+        <v>56</v>
+      </c>
+      <c r="C163" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D163">
+        <v>81</v>
+      </c>
+      <c r="E163">
+        <v>1</v>
+      </c>
+      <c r="F163">
+        <v>0</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>0</v>
+      </c>
+      <c r="J163">
+        <v>0</v>
+      </c>
+      <c r="K163">
+        <v>0</v>
+      </c>
+      <c r="L163">
+        <v>0</v>
+      </c>
+      <c r="M163">
+        <v>0</v>
+      </c>
+      <c r="N163">
+        <v>1</v>
+      </c>
+      <c r="O163">
+        <v>0</v>
+      </c>
+      <c r="P163">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A164">
+        <v>7</v>
+      </c>
+      <c r="B164" t="s">
+        <v>56</v>
+      </c>
+      <c r="C164" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D164">
+        <v>25</v>
+      </c>
+      <c r="E164">
+        <v>1</v>
+      </c>
+      <c r="F164">
+        <v>0</v>
+      </c>
+      <c r="G164">
+        <v>2</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>0</v>
+      </c>
+      <c r="J164">
+        <v>0</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+      <c r="L164">
+        <v>0</v>
+      </c>
+      <c r="M164">
+        <v>0</v>
+      </c>
+      <c r="N164">
+        <v>0</v>
+      </c>
+      <c r="O164">
+        <v>0</v>
+      </c>
+      <c r="P164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A165">
+        <v>7</v>
+      </c>
+      <c r="B165" t="s">
+        <v>56</v>
+      </c>
+      <c r="C165" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D165">
+        <v>56</v>
+      </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
+      <c r="F165">
+        <v>0</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="J165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>0</v>
+      </c>
+      <c r="L165">
+        <v>0</v>
+      </c>
+      <c r="M165">
+        <v>0</v>
+      </c>
+      <c r="N165">
+        <v>0</v>
+      </c>
+      <c r="O165">
+        <v>0</v>
+      </c>
+      <c r="P165">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A166">
+        <v>7</v>
+      </c>
+      <c r="B166" t="s">
+        <v>56</v>
+      </c>
+      <c r="C166" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D166">
+        <v>44</v>
+      </c>
+      <c r="E166">
+        <v>1</v>
+      </c>
+      <c r="F166">
+        <v>0</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="J166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>0</v>
+      </c>
+      <c r="L166">
+        <v>0</v>
+      </c>
+      <c r="M166">
+        <v>0</v>
+      </c>
+      <c r="N166">
+        <v>2</v>
+      </c>
+      <c r="O166">
+        <v>0</v>
+      </c>
+      <c r="P166">
         <v>0</v>
       </c>
     </row>
@@ -7959,25 +8912,25 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE8C601-DC7D-42D2-865D-643789981902}">
-  <dimension ref="A1:L184"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L215"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="3" width="11.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.54296875" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>12</v>
       </c>
       <c r="B1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" t="s">
         <v>44</v>
       </c>
-      <c r="C1" t="s">
-        <v>45</v>
-      </c>
       <c r="D1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -8004,12 +8957,12 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="2">
         <v>46278</v>
@@ -8042,12 +8995,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C3" s="2">
         <v>46278</v>
@@ -8080,12 +9033,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C4" s="2">
         <v>46278</v>
@@ -8118,18 +9071,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C5" s="2">
         <v>46278</v>
       </c>
       <c r="D5" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -8156,18 +9109,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C6" s="2">
         <v>46278</v>
       </c>
       <c r="D6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -8194,18 +9147,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C7" s="2">
         <v>46278</v>
       </c>
       <c r="D7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -8232,18 +9185,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C8" s="2">
         <v>46278</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -8270,18 +9223,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C9" s="2">
         <v>46278</v>
       </c>
       <c r="D9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -8308,18 +9261,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C10" s="2">
         <v>46278</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -8346,18 +9299,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C11" s="2">
         <v>46278</v>
       </c>
       <c r="D11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -8384,18 +9337,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C12" s="2">
         <v>46278</v>
       </c>
       <c r="D12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -8422,18 +9375,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C13" s="2">
         <v>46278</v>
       </c>
       <c r="D13" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -8460,18 +9413,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C14" s="2">
         <v>46278</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -8498,18 +9451,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C15" s="2">
         <v>46278</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -8536,18 +9489,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2">
         <v>46278</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E16">
         <v>1</v>
@@ -8574,18 +9527,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C17" s="2">
         <v>46278</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -8612,18 +9565,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2">
         <v>46278</v>
       </c>
       <c r="D18" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -8650,18 +9603,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C19" s="2">
         <v>46278</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -8688,18 +9641,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C20" s="2">
         <v>46278</v>
       </c>
       <c r="D20" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E20">
         <v>1</v>
@@ -8726,18 +9679,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2">
         <v>46278</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -8764,18 +9717,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2">
         <v>46278</v>
       </c>
       <c r="D22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -8802,18 +9755,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>1</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="2">
         <v>46278</v>
       </c>
       <c r="D23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -8840,18 +9793,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2">
         <v>46278</v>
       </c>
       <c r="D24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -8878,18 +9831,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>1</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="2">
         <v>46278</v>
       </c>
       <c r="D25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -8916,18 +9869,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>1</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="2">
         <v>46278</v>
       </c>
       <c r="D26" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -8954,18 +9907,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2">
         <v>46278</v>
       </c>
       <c r="D27" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -8992,18 +9945,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="2">
         <v>46278</v>
       </c>
       <c r="D28" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -9030,18 +9983,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>1</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C29" s="2">
         <v>46278</v>
       </c>
       <c r="D29" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -9068,18 +10021,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>1</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30" s="2">
         <v>46278</v>
       </c>
       <c r="D30" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -9106,18 +10059,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C31" s="2">
         <v>46282</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E31">
         <v>1</v>
@@ -9144,18 +10097,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C32" s="2">
         <v>46282</v>
       </c>
       <c r="D32" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -9182,18 +10135,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C33" s="2">
         <v>46282</v>
       </c>
       <c r="D33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -9220,18 +10173,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C34" s="2">
         <v>46282</v>
       </c>
       <c r="D34" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -9258,18 +10211,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C35" s="2">
         <v>46282</v>
       </c>
       <c r="D35" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -9296,18 +10249,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C36" s="2">
         <v>46282</v>
       </c>
       <c r="D36" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -9334,18 +10287,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C37" s="2">
         <v>46282</v>
       </c>
       <c r="D37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -9372,18 +10325,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C38" s="2">
         <v>46282</v>
       </c>
       <c r="D38" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -9410,18 +10363,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C39" s="2">
         <v>46282</v>
       </c>
       <c r="D39" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -9448,18 +10401,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C40" s="2">
         <v>46282</v>
       </c>
       <c r="D40" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -9486,18 +10439,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C41" s="2">
         <v>46282</v>
       </c>
       <c r="D41" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -9524,18 +10477,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C42" s="2">
         <v>46282</v>
       </c>
       <c r="D42" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -9562,18 +10515,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C43" s="2">
         <v>46282</v>
       </c>
       <c r="D43" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -9600,18 +10553,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C44" s="2">
         <v>46282</v>
       </c>
       <c r="D44" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -9638,18 +10591,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>2</v>
       </c>
       <c r="B45" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C45" s="2">
         <v>46282</v>
       </c>
       <c r="D45" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -9676,18 +10629,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C46" s="2">
         <v>46282</v>
       </c>
       <c r="D46" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -9714,18 +10667,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>2</v>
       </c>
       <c r="B47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C47" s="2">
         <v>46282</v>
       </c>
       <c r="D47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -9752,18 +10705,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>2</v>
       </c>
       <c r="B48" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C48" s="2">
         <v>46282</v>
       </c>
       <c r="D48" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -9790,18 +10743,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>2</v>
       </c>
       <c r="B49" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C49" s="2">
         <v>46282</v>
       </c>
       <c r="D49" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -9828,18 +10781,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>2</v>
       </c>
       <c r="B50" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C50" s="2">
         <v>46282</v>
       </c>
       <c r="D50" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -9866,18 +10819,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C51" s="2">
         <v>46282</v>
       </c>
       <c r="D51" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -9904,18 +10857,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52">
         <v>2</v>
       </c>
       <c r="B52" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C52" s="2">
         <v>46282</v>
       </c>
       <c r="D52" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -9942,18 +10895,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53">
         <v>2</v>
       </c>
       <c r="B53" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C53" s="2">
         <v>46282</v>
       </c>
       <c r="D53" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -9980,18 +10933,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54">
         <v>2</v>
       </c>
       <c r="B54" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C54" s="2">
         <v>46282</v>
       </c>
       <c r="D54" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -10018,18 +10971,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55">
         <v>2</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C55" s="2">
         <v>46282</v>
       </c>
       <c r="D55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -10056,12 +11009,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56">
         <v>2</v>
       </c>
       <c r="B56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C56" s="2">
         <v>46282</v>
@@ -10094,12 +11047,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57">
         <v>2</v>
       </c>
       <c r="B57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C57" s="2">
         <v>46282</v>
@@ -10132,12 +11085,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58">
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C58" s="2">
         <v>46282</v>
@@ -10170,18 +11123,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59">
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C59" s="2">
         <v>46282</v>
       </c>
       <c r="D59" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -10208,18 +11161,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60">
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C60" s="2">
         <v>46285</v>
       </c>
       <c r="D60" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -10246,18 +11199,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61">
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C61" s="2">
         <v>46285</v>
       </c>
       <c r="D61" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E61">
         <v>1</v>
@@ -10284,18 +11237,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62">
         <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C62" s="2">
         <v>46285</v>
       </c>
       <c r="D62" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -10322,18 +11275,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63">
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C63" s="2">
         <v>46285</v>
       </c>
       <c r="D63" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -10360,18 +11313,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64">
         <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C64" s="2">
         <v>46285</v>
       </c>
       <c r="D64" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -10398,18 +11351,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65">
         <v>3</v>
       </c>
       <c r="B65" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C65" s="2">
         <v>46285</v>
       </c>
       <c r="D65" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -10436,18 +11389,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66">
         <v>3</v>
       </c>
       <c r="B66" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C66" s="2">
         <v>46285</v>
       </c>
       <c r="D66" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -10474,18 +11427,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67">
         <v>3</v>
       </c>
       <c r="B67" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C67" s="2">
         <v>46285</v>
       </c>
       <c r="D67" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -10512,18 +11465,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68">
         <v>3</v>
       </c>
       <c r="B68" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C68" s="2">
         <v>46285</v>
       </c>
       <c r="D68" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -10550,18 +11503,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69">
         <v>3</v>
       </c>
       <c r="B69" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C69" s="2">
         <v>46285</v>
       </c>
       <c r="D69" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -10588,18 +11541,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70">
         <v>3</v>
       </c>
       <c r="B70" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C70" s="2">
         <v>46285</v>
       </c>
       <c r="D70" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -10626,18 +11579,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71">
         <v>3</v>
       </c>
       <c r="B71" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C71" s="2">
         <v>46285</v>
       </c>
       <c r="D71" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E71">
         <v>1</v>
@@ -10664,18 +11617,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72">
         <v>3</v>
       </c>
       <c r="B72" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C72" s="2">
         <v>46285</v>
       </c>
       <c r="D72" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -10702,18 +11655,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73">
         <v>3</v>
       </c>
       <c r="B73" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C73" s="2">
         <v>46285</v>
       </c>
       <c r="D73" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E73">
         <v>1</v>
@@ -10740,18 +11693,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74">
         <v>3</v>
       </c>
       <c r="B74" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C74" s="2">
         <v>46285</v>
       </c>
       <c r="D74" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -10778,18 +11731,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75">
         <v>3</v>
       </c>
       <c r="B75" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C75" s="2">
         <v>46285</v>
       </c>
       <c r="D75" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -10816,18 +11769,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76">
         <v>3</v>
       </c>
       <c r="B76" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C76" s="2">
         <v>46285</v>
       </c>
       <c r="D76" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -10854,18 +11807,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77">
         <v>3</v>
       </c>
       <c r="B77" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C77" s="2">
         <v>46285</v>
       </c>
       <c r="D77" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -10892,18 +11845,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78">
         <v>3</v>
       </c>
       <c r="B78" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C78" s="2">
         <v>46285</v>
       </c>
       <c r="D78" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -10930,18 +11883,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79">
         <v>3</v>
       </c>
       <c r="B79" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C79" s="2">
         <v>46285</v>
       </c>
       <c r="D79" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -10968,18 +11921,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80">
         <v>3</v>
       </c>
       <c r="B80" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C80" s="2">
         <v>46285</v>
       </c>
       <c r="D80" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -11006,18 +11959,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81">
         <v>3</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C81" s="2">
         <v>46285</v>
       </c>
       <c r="D81" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -11044,18 +11997,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82">
         <v>3</v>
       </c>
       <c r="B82" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C82" s="2">
         <v>46285</v>
       </c>
       <c r="D82" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -11082,18 +12035,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83">
         <v>3</v>
       </c>
       <c r="B83" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C83" s="2">
         <v>46285</v>
       </c>
       <c r="D83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -11120,18 +12073,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84">
         <v>3</v>
       </c>
       <c r="B84" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C84" s="2">
         <v>46285</v>
       </c>
       <c r="D84" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -11158,12 +12111,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85">
         <v>3</v>
       </c>
       <c r="B85" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C85" s="2">
         <v>46285</v>
@@ -11196,12 +12149,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86">
         <v>3</v>
       </c>
       <c r="B86" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C86" s="2">
         <v>46285</v>
@@ -11234,12 +12187,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87">
         <v>3</v>
       </c>
       <c r="B87" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C87" s="2">
         <v>46285</v>
@@ -11272,18 +12225,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88">
         <v>3</v>
       </c>
       <c r="B88" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C88" s="2">
         <v>46285</v>
       </c>
       <c r="D88" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -11310,18 +12263,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89">
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C89" s="2">
         <v>46291</v>
       </c>
       <c r="D89" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -11348,18 +12301,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90">
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C90" s="2">
         <v>46291</v>
       </c>
       <c r="D90" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -11386,18 +12339,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91">
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C91" s="2">
         <v>46291</v>
       </c>
       <c r="D91" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -11424,18 +12377,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92">
         <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C92" s="2">
         <v>46291</v>
       </c>
       <c r="D92" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -11462,18 +12415,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93">
         <v>4</v>
       </c>
       <c r="B93" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C93" s="2">
         <v>46291</v>
       </c>
       <c r="D93" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -11500,18 +12453,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94">
         <v>4</v>
       </c>
       <c r="B94" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C94" s="2">
         <v>46291</v>
       </c>
       <c r="D94" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -11538,18 +12491,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95">
         <v>4</v>
       </c>
       <c r="B95" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C95" s="2">
         <v>46291</v>
       </c>
       <c r="D95" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -11576,18 +12529,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96">
         <v>4</v>
       </c>
       <c r="B96" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C96" s="2">
         <v>46291</v>
       </c>
       <c r="D96" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -11614,18 +12567,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97">
         <v>4</v>
       </c>
       <c r="B97" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C97" s="2">
         <v>46291</v>
       </c>
       <c r="D97" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -11652,18 +12605,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98">
         <v>4</v>
       </c>
       <c r="B98" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C98" s="2">
         <v>46291</v>
       </c>
       <c r="D98" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -11690,18 +12643,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99">
         <v>4</v>
       </c>
       <c r="B99" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C99" s="2">
         <v>46291</v>
       </c>
       <c r="D99" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -11728,18 +12681,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100">
         <v>4</v>
       </c>
       <c r="B100" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C100" s="2">
         <v>46291</v>
       </c>
       <c r="D100" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -11766,18 +12719,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101">
         <v>4</v>
       </c>
       <c r="B101" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C101" s="2">
         <v>46291</v>
       </c>
       <c r="D101" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -11804,18 +12757,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102">
         <v>4</v>
       </c>
       <c r="B102" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C102" s="2">
         <v>46291</v>
       </c>
       <c r="D102" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -11842,18 +12795,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103">
         <v>4</v>
       </c>
       <c r="B103" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C103" s="2">
         <v>46291</v>
       </c>
       <c r="D103" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -11880,18 +12833,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104">
         <v>4</v>
       </c>
       <c r="B104" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C104" s="2">
         <v>46291</v>
       </c>
       <c r="D104" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -11918,18 +12871,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105">
         <v>4</v>
       </c>
       <c r="B105" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C105" s="2">
         <v>46291</v>
       </c>
       <c r="D105" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -11956,18 +12909,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106">
         <v>4</v>
       </c>
       <c r="B106" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C106" s="2">
         <v>46291</v>
       </c>
       <c r="D106" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -11994,18 +12947,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107">
         <v>4</v>
       </c>
       <c r="B107" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C107" s="2">
         <v>46291</v>
       </c>
       <c r="D107" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -12032,18 +12985,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108">
         <v>4</v>
       </c>
       <c r="B108" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C108" s="2">
         <v>46291</v>
       </c>
       <c r="D108" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -12070,18 +13023,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109">
         <v>4</v>
       </c>
       <c r="B109" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C109" s="2">
         <v>46291</v>
       </c>
       <c r="D109" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -12108,18 +13061,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110">
         <v>4</v>
       </c>
       <c r="B110" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C110" s="2">
         <v>46291</v>
       </c>
       <c r="D110" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -12146,18 +13099,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111">
         <v>4</v>
       </c>
       <c r="B111" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C111" s="2">
         <v>46291</v>
       </c>
       <c r="D111" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -12184,18 +13137,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112">
         <v>4</v>
       </c>
       <c r="B112" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C112" s="2">
         <v>46291</v>
       </c>
       <c r="D112" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E112">
         <v>0</v>
@@ -12222,18 +13175,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113">
         <v>4</v>
       </c>
       <c r="B113" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C113" s="2">
         <v>46291</v>
       </c>
       <c r="D113" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -12260,18 +13213,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A114">
         <v>4</v>
       </c>
       <c r="B114" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C114" s="2">
         <v>46291</v>
       </c>
       <c r="D114" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -12298,18 +13251,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A115">
         <v>4</v>
       </c>
       <c r="B115" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C115" s="2">
         <v>46291</v>
       </c>
       <c r="D115" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -12336,18 +13289,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A116">
         <v>4</v>
       </c>
       <c r="B116" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C116" s="2">
         <v>46291</v>
       </c>
       <c r="D116" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -12374,18 +13327,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117">
         <v>4</v>
       </c>
       <c r="B117" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C117" s="2">
         <v>46291</v>
       </c>
       <c r="D117" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -12412,18 +13365,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118">
         <v>4</v>
       </c>
       <c r="B118" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C118" s="2">
         <v>46291</v>
       </c>
       <c r="D118" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -12450,12 +13403,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A119">
         <v>4</v>
       </c>
       <c r="B119" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C119" s="2">
         <v>46291</v>
@@ -12488,12 +13441,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120">
         <v>4</v>
       </c>
       <c r="B120" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C120" s="2">
         <v>46291</v>
@@ -12526,12 +13479,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="121" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121">
         <v>4</v>
       </c>
       <c r="B121" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C121" s="2">
         <v>46291</v>
@@ -12564,18 +13517,18 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A122">
         <v>4</v>
       </c>
       <c r="B122" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C122" s="2">
         <v>46291</v>
       </c>
       <c r="D122" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -12602,18 +13555,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123">
         <v>5</v>
       </c>
       <c r="B123" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C123" s="2">
         <v>46304</v>
       </c>
       <c r="D123" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -12640,18 +13593,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124">
         <v>5</v>
       </c>
       <c r="B124" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C124" s="2">
         <v>46304</v>
       </c>
       <c r="D124" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E124">
         <v>0</v>
@@ -12678,18 +13631,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125">
         <v>5</v>
       </c>
       <c r="B125" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C125" s="2">
         <v>46304</v>
       </c>
       <c r="D125" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E125">
         <v>0</v>
@@ -12716,18 +13669,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126">
         <v>5</v>
       </c>
       <c r="B126" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C126" s="2">
         <v>46304</v>
       </c>
       <c r="D126" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -12754,18 +13707,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127">
         <v>5</v>
       </c>
       <c r="B127" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C127" s="2">
         <v>46304</v>
       </c>
       <c r="D127" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E127">
         <v>0</v>
@@ -12792,18 +13745,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128">
         <v>5</v>
       </c>
       <c r="B128" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C128" s="2">
         <v>46304</v>
       </c>
       <c r="D128" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E128">
         <v>0</v>
@@ -12830,18 +13783,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129">
         <v>5</v>
       </c>
       <c r="B129" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C129" s="2">
         <v>46304</v>
       </c>
       <c r="D129" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E129">
         <v>0</v>
@@ -12868,18 +13821,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130">
         <v>5</v>
       </c>
       <c r="B130" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C130" s="2">
         <v>46304</v>
       </c>
       <c r="D130" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -12906,18 +13859,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131">
         <v>5</v>
       </c>
       <c r="B131" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C131" s="2">
         <v>46304</v>
       </c>
       <c r="D131" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -12944,18 +13897,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132">
         <v>5</v>
       </c>
       <c r="B132" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C132" s="2">
         <v>46304</v>
       </c>
       <c r="D132" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -12982,18 +13935,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133">
         <v>5</v>
       </c>
       <c r="B133" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C133" s="2">
         <v>46304</v>
       </c>
       <c r="D133" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -13020,18 +13973,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134">
         <v>5</v>
       </c>
       <c r="B134" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C134" s="2">
         <v>46304</v>
       </c>
       <c r="D134" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -13058,18 +14011,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135">
         <v>5</v>
       </c>
       <c r="B135" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C135" s="2">
         <v>46304</v>
       </c>
       <c r="D135" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -13096,18 +14049,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136">
         <v>5</v>
       </c>
       <c r="B136" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C136" s="2">
         <v>46304</v>
       </c>
       <c r="D136" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -13134,18 +14087,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137">
         <v>5</v>
       </c>
       <c r="B137" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C137" s="2">
         <v>46304</v>
       </c>
       <c r="D137" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -13172,18 +14125,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138">
         <v>5</v>
       </c>
       <c r="B138" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C138" s="2">
         <v>46304</v>
       </c>
       <c r="D138" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -13210,18 +14163,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139">
         <v>5</v>
       </c>
       <c r="B139" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C139" s="2">
         <v>46304</v>
       </c>
       <c r="D139" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -13248,18 +14201,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140">
         <v>5</v>
       </c>
       <c r="B140" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C140" s="2">
         <v>46304</v>
       </c>
       <c r="D140" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -13286,18 +14239,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141">
         <v>5</v>
       </c>
       <c r="B141" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C141" s="2">
         <v>46304</v>
       </c>
       <c r="D141" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -13324,18 +14277,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A142">
         <v>5</v>
       </c>
       <c r="B142" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C142" s="2">
         <v>46304</v>
       </c>
       <c r="D142" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -13362,18 +14315,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A143">
         <v>5</v>
       </c>
       <c r="B143" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C143" s="2">
         <v>46304</v>
       </c>
       <c r="D143" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -13400,18 +14353,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A144">
         <v>5</v>
       </c>
       <c r="B144" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C144" s="2">
         <v>46304</v>
       </c>
       <c r="D144" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -13438,18 +14391,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145">
         <v>5</v>
       </c>
       <c r="B145" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C145" s="2">
         <v>46304</v>
       </c>
       <c r="D145" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -13476,18 +14429,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146">
         <v>5</v>
       </c>
       <c r="B146" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C146" s="2">
         <v>46304</v>
       </c>
       <c r="D146" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -13514,18 +14467,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147">
         <v>5</v>
       </c>
       <c r="B147" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C147" s="2">
         <v>46304</v>
       </c>
       <c r="D147" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -13552,18 +14505,18 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148">
         <v>5</v>
       </c>
       <c r="B148" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C148" s="2">
         <v>46304</v>
       </c>
       <c r="D148" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -13590,18 +14543,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A149">
         <v>5</v>
       </c>
       <c r="B149" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C149" s="2">
         <v>46304</v>
       </c>
       <c r="D149" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -13628,18 +14581,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150">
         <v>5</v>
       </c>
       <c r="B150" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C150" s="2">
         <v>46304</v>
       </c>
       <c r="D150" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -13666,12 +14619,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151">
         <v>5</v>
       </c>
       <c r="B151" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C151" s="2">
         <v>46304</v>
@@ -13704,12 +14657,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152">
         <v>5</v>
       </c>
       <c r="B152" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C152" s="2">
         <v>46304</v>
@@ -13742,12 +14695,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153">
         <v>5</v>
       </c>
       <c r="B153" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C153" s="2">
         <v>46304</v>
@@ -13780,18 +14733,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154">
         <v>5</v>
       </c>
       <c r="B154" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C154" s="2">
         <v>46304</v>
       </c>
       <c r="D154" t="s">
-        <v>17</v>
+        <v>57</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -13818,18 +14771,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155">
         <v>6</v>
       </c>
       <c r="B155" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C155" s="2">
         <v>46306</v>
       </c>
       <c r="D155" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -13856,18 +14809,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156">
         <v>6</v>
       </c>
       <c r="B156" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C156" s="2">
         <v>46306</v>
       </c>
       <c r="D156" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -13894,18 +14847,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157">
         <v>6</v>
       </c>
       <c r="B157" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C157" s="2">
         <v>46306</v>
       </c>
       <c r="D157" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -13932,18 +14885,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158">
         <v>6</v>
       </c>
       <c r="B158" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C158" s="2">
         <v>46306</v>
       </c>
       <c r="D158" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -13970,18 +14923,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159">
         <v>6</v>
       </c>
       <c r="B159" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C159" s="2">
         <v>46306</v>
       </c>
       <c r="D159" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E159">
         <v>1</v>
@@ -14008,18 +14961,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160">
         <v>6</v>
       </c>
       <c r="B160" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C160" s="2">
         <v>46306</v>
       </c>
       <c r="D160" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -14046,18 +14999,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161">
         <v>6</v>
       </c>
       <c r="B161" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C161" s="2">
         <v>46306</v>
       </c>
       <c r="D161" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -14084,18 +15037,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162">
         <v>6</v>
       </c>
       <c r="B162" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C162" s="2">
         <v>46306</v>
       </c>
       <c r="D162" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -14122,18 +15075,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163">
         <v>6</v>
       </c>
       <c r="B163" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C163" s="2">
         <v>46306</v>
       </c>
       <c r="D163" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -14160,18 +15113,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164">
         <v>6</v>
       </c>
       <c r="B164" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C164" s="2">
         <v>46306</v>
       </c>
       <c r="D164" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -14198,18 +15151,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165">
         <v>6</v>
       </c>
       <c r="B165" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C165" s="2">
         <v>46306</v>
       </c>
       <c r="D165" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -14236,18 +15189,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166">
         <v>6</v>
       </c>
       <c r="B166" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C166" s="2">
         <v>46306</v>
       </c>
       <c r="D166" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -14274,18 +15227,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167">
         <v>6</v>
       </c>
       <c r="B167" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C167" s="2">
         <v>46306</v>
       </c>
       <c r="D167" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -14312,18 +15265,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168">
         <v>6</v>
       </c>
       <c r="B168" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C168" s="2">
         <v>46306</v>
       </c>
       <c r="D168" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -14350,18 +15303,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169">
         <v>6</v>
       </c>
       <c r="B169" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C169" s="2">
         <v>46306</v>
       </c>
       <c r="D169" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -14388,18 +15341,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170">
         <v>6</v>
       </c>
       <c r="B170" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C170" s="2">
         <v>46306</v>
       </c>
       <c r="D170" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -14426,18 +15379,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171">
         <v>6</v>
       </c>
       <c r="B171" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C171" s="2">
         <v>46306</v>
       </c>
       <c r="D171" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -14464,18 +15417,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172">
         <v>6</v>
       </c>
       <c r="B172" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C172" s="2">
         <v>46306</v>
       </c>
       <c r="D172" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E172">
         <v>1</v>
@@ -14502,18 +15455,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A173">
         <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C173" s="2">
         <v>46306</v>
       </c>
       <c r="D173" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -14540,18 +15493,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A174">
         <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C174" s="2">
         <v>46306</v>
       </c>
       <c r="D174" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -14578,18 +15531,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A175">
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C175" s="2">
         <v>46306</v>
       </c>
       <c r="D175" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -14616,18 +15569,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A176">
         <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C176" s="2">
         <v>46306</v>
       </c>
       <c r="D176" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -14654,18 +15607,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177">
         <v>6</v>
       </c>
       <c r="B177" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C177" s="2">
         <v>46306</v>
       </c>
       <c r="D177" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -14692,18 +15645,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178">
         <v>6</v>
       </c>
       <c r="B178" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C178" s="2">
         <v>46306</v>
       </c>
       <c r="D178" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -14730,18 +15683,18 @@
         <v>4</v>
       </c>
     </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A179">
         <v>6</v>
       </c>
       <c r="B179" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C179" s="2">
         <v>46306</v>
       </c>
       <c r="D179" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -14768,18 +15721,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A180">
         <v>6</v>
       </c>
       <c r="B180" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C180" s="2">
         <v>46306</v>
       </c>
       <c r="D180" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -14806,12 +15759,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A181">
         <v>6</v>
       </c>
       <c r="B181" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C181" s="2">
         <v>46306</v>
@@ -14844,12 +15797,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A182">
         <v>6</v>
       </c>
       <c r="B182" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C182" s="2">
         <v>46306</v>
@@ -14882,12 +15835,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A183">
         <v>6</v>
       </c>
       <c r="B183" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C183" s="2">
         <v>46306</v>
@@ -14920,43 +15873,1151 @@
         <v>3</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184">
         <v>6</v>
       </c>
       <c r="B184" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C184" s="2">
         <v>46306</v>
       </c>
       <c r="D184" t="s">
+        <v>57</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>7</v>
+      </c>
+      <c r="B185" t="s">
+        <v>56</v>
+      </c>
+      <c r="C185" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D185" t="s">
+        <v>14</v>
+      </c>
+      <c r="E185">
+        <v>1</v>
+      </c>
+      <c r="F185">
+        <v>4</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>1</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>4</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A186">
+        <v>7</v>
+      </c>
+      <c r="B186" t="s">
+        <v>56</v>
+      </c>
+      <c r="C186" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D186" t="s">
+        <v>16</v>
+      </c>
+      <c r="E186">
+        <v>1</v>
+      </c>
+      <c r="F186">
+        <v>2</v>
+      </c>
+      <c r="G186">
+        <v>0</v>
+      </c>
+      <c r="H186">
+        <v>1</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>3</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="187" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A187">
+        <v>7</v>
+      </c>
+      <c r="B187" t="s">
+        <v>56</v>
+      </c>
+      <c r="C187" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D187" t="s">
+        <v>15</v>
+      </c>
+      <c r="E187">
+        <v>1</v>
+      </c>
+      <c r="F187">
+        <v>3</v>
+      </c>
+      <c r="G187">
+        <v>1</v>
+      </c>
+      <c r="H187">
+        <v>1</v>
+      </c>
+      <c r="I187">
+        <v>2</v>
+      </c>
+      <c r="J187">
+        <v>4</v>
+      </c>
+      <c r="K187">
+        <v>0</v>
+      </c>
+      <c r="L187">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A188">
+        <v>7</v>
+      </c>
+      <c r="B188" t="s">
+        <v>56</v>
+      </c>
+      <c r="C188" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D188" t="s">
+        <v>58</v>
+      </c>
+      <c r="E188">
+        <v>0</v>
+      </c>
+      <c r="F188">
+        <v>0</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <v>0</v>
+      </c>
+      <c r="J188">
+        <v>0</v>
+      </c>
+      <c r="K188">
+        <v>0</v>
+      </c>
+      <c r="L188">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A189">
+        <v>7</v>
+      </c>
+      <c r="B189" t="s">
+        <v>56</v>
+      </c>
+      <c r="C189" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D189" t="s">
+        <v>33</v>
+      </c>
+      <c r="E189">
+        <v>1</v>
+      </c>
+      <c r="F189">
+        <v>1</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <v>0</v>
+      </c>
+      <c r="J189">
+        <v>0</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+      <c r="L189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A190">
+        <v>7</v>
+      </c>
+      <c r="B190" t="s">
+        <v>56</v>
+      </c>
+      <c r="C190" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D190" t="s">
+        <v>31</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
+      <c r="F190">
+        <v>1</v>
+      </c>
+      <c r="G190">
+        <v>0</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>1</v>
+      </c>
+      <c r="K190">
+        <v>0</v>
+      </c>
+      <c r="L190">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A191">
+        <v>7</v>
+      </c>
+      <c r="B191" t="s">
+        <v>56</v>
+      </c>
+      <c r="C191" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D191" t="s">
+        <v>32</v>
+      </c>
+      <c r="E191">
+        <v>1</v>
+      </c>
+      <c r="F191">
+        <v>1</v>
+      </c>
+      <c r="G191">
+        <v>0</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>2</v>
+      </c>
+      <c r="K191">
+        <v>0</v>
+      </c>
+      <c r="L191">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A192">
+        <v>7</v>
+      </c>
+      <c r="B192" t="s">
+        <v>56</v>
+      </c>
+      <c r="C192" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D192" t="s">
+        <v>30</v>
+      </c>
+      <c r="E192">
+        <v>1</v>
+      </c>
+      <c r="F192">
+        <v>2</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <v>0</v>
+      </c>
+      <c r="J192">
+        <v>1</v>
+      </c>
+      <c r="K192">
+        <v>0</v>
+      </c>
+      <c r="L192">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A193">
+        <v>7</v>
+      </c>
+      <c r="B193" t="s">
+        <v>56</v>
+      </c>
+      <c r="C193" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D193" t="s">
+        <v>29</v>
+      </c>
+      <c r="E193">
+        <v>1</v>
+      </c>
+      <c r="F193">
+        <v>0</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193">
+        <v>0</v>
+      </c>
+      <c r="J193">
+        <v>0</v>
+      </c>
+      <c r="K193">
+        <v>0</v>
+      </c>
+      <c r="L193">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A194">
+        <v>7</v>
+      </c>
+      <c r="B194" t="s">
+        <v>56</v>
+      </c>
+      <c r="C194" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D194" t="s">
+        <v>26</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
+      <c r="F194">
+        <v>0</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>1</v>
+      </c>
+      <c r="J194">
+        <v>0</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+      <c r="L194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A195">
+        <v>7</v>
+      </c>
+      <c r="B195" t="s">
+        <v>56</v>
+      </c>
+      <c r="C195" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D195" t="s">
+        <v>27</v>
+      </c>
+      <c r="E195">
+        <v>0</v>
+      </c>
+      <c r="F195">
+        <v>0</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <v>0</v>
+      </c>
+      <c r="J195">
+        <v>0</v>
+      </c>
+      <c r="K195">
+        <v>0</v>
+      </c>
+      <c r="L195">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A196">
+        <v>7</v>
+      </c>
+      <c r="B196" t="s">
+        <v>56</v>
+      </c>
+      <c r="C196" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D196" t="s">
+        <v>50</v>
+      </c>
+      <c r="E196">
+        <v>0</v>
+      </c>
+      <c r="F196">
+        <v>0</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>0</v>
+      </c>
+      <c r="J196">
+        <v>0</v>
+      </c>
+      <c r="K196">
+        <v>0</v>
+      </c>
+      <c r="L196">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A197">
+        <v>7</v>
+      </c>
+      <c r="B197" t="s">
+        <v>56</v>
+      </c>
+      <c r="C197" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D197" t="s">
+        <v>49</v>
+      </c>
+      <c r="E197">
+        <v>1</v>
+      </c>
+      <c r="F197">
+        <v>0</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>1</v>
+      </c>
+      <c r="J197">
+        <v>0</v>
+      </c>
+      <c r="K197">
+        <v>0</v>
+      </c>
+      <c r="L197">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A198">
+        <v>7</v>
+      </c>
+      <c r="B198" t="s">
+        <v>56</v>
+      </c>
+      <c r="C198" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D198" t="s">
+        <v>22</v>
+      </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
+      <c r="F198">
+        <v>2</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>0</v>
+      </c>
+      <c r="J198">
+        <v>0</v>
+      </c>
+      <c r="K198">
+        <v>0</v>
+      </c>
+      <c r="L198">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A199">
+        <v>7</v>
+      </c>
+      <c r="B199" t="s">
+        <v>56</v>
+      </c>
+      <c r="C199" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D199" t="s">
+        <v>21</v>
+      </c>
+      <c r="E199">
+        <v>2</v>
+      </c>
+      <c r="F199">
+        <v>0</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>0</v>
+      </c>
+      <c r="J199">
+        <v>2</v>
+      </c>
+      <c r="K199">
+        <v>0</v>
+      </c>
+      <c r="L199">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A200">
+        <v>7</v>
+      </c>
+      <c r="B200" t="s">
+        <v>56</v>
+      </c>
+      <c r="C200" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D200" t="s">
+        <v>20</v>
+      </c>
+      <c r="E200">
+        <v>2</v>
+      </c>
+      <c r="F200">
+        <v>1</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>0</v>
+      </c>
+      <c r="J200">
+        <v>3</v>
+      </c>
+      <c r="K200">
+        <v>0</v>
+      </c>
+      <c r="L200">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A201">
+        <v>7</v>
+      </c>
+      <c r="B201" t="s">
+        <v>56</v>
+      </c>
+      <c r="C201" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D201" t="s">
+        <v>48</v>
+      </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
+      <c r="F201">
+        <v>0</v>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>0</v>
+      </c>
+      <c r="J201">
+        <v>0</v>
+      </c>
+      <c r="K201">
+        <v>0</v>
+      </c>
+      <c r="L201">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A202">
+        <v>7</v>
+      </c>
+      <c r="B202" t="s">
+        <v>56</v>
+      </c>
+      <c r="C202" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D202" t="s">
+        <v>18</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202">
+        <v>0</v>
+      </c>
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
+        <v>0</v>
+      </c>
+      <c r="J202">
+        <v>0</v>
+      </c>
+      <c r="K202">
+        <v>0</v>
+      </c>
+      <c r="L202">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A203">
+        <v>7</v>
+      </c>
+      <c r="B203" t="s">
+        <v>56</v>
+      </c>
+      <c r="C203" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D203" t="s">
         <v>17</v>
       </c>
-      <c r="E184">
-        <v>0</v>
-      </c>
-      <c r="F184">
-        <v>0</v>
-      </c>
-      <c r="G184">
-        <v>0</v>
-      </c>
-      <c r="H184">
-        <v>0</v>
-      </c>
-      <c r="I184">
-        <v>0</v>
-      </c>
-      <c r="J184">
-        <v>0</v>
-      </c>
-      <c r="K184">
-        <v>0</v>
-      </c>
-      <c r="L184">
-        <v>0</v>
-      </c>
+      <c r="E203">
+        <v>1</v>
+      </c>
+      <c r="F203">
+        <v>0</v>
+      </c>
+      <c r="G203">
+        <v>0</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+      <c r="I203">
+        <v>0</v>
+      </c>
+      <c r="J203">
+        <v>0</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+      <c r="L203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A204">
+        <v>7</v>
+      </c>
+      <c r="B204" t="s">
+        <v>56</v>
+      </c>
+      <c r="C204" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D204" t="s">
+        <v>38</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+      <c r="F204">
+        <v>0</v>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <v>0</v>
+      </c>
+      <c r="J204">
+        <v>0</v>
+      </c>
+      <c r="K204">
+        <v>0</v>
+      </c>
+      <c r="L204">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A205">
+        <v>7</v>
+      </c>
+      <c r="B205" t="s">
+        <v>56</v>
+      </c>
+      <c r="C205" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D205" t="s">
+        <v>36</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="F205">
+        <v>0</v>
+      </c>
+      <c r="G205">
+        <v>0</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0</v>
+      </c>
+      <c r="K205">
+        <v>0</v>
+      </c>
+      <c r="L205">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A206">
+        <v>7</v>
+      </c>
+      <c r="B206" t="s">
+        <v>56</v>
+      </c>
+      <c r="C206" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D206" t="s">
+        <v>37</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>0</v>
+      </c>
+      <c r="G206">
+        <v>0</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>0</v>
+      </c>
+      <c r="K206">
+        <v>0</v>
+      </c>
+      <c r="L206">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A207">
+        <v>7</v>
+      </c>
+      <c r="B207" t="s">
+        <v>56</v>
+      </c>
+      <c r="C207" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D207" t="s">
+        <v>34</v>
+      </c>
+      <c r="E207">
+        <v>1</v>
+      </c>
+      <c r="F207">
+        <v>0</v>
+      </c>
+      <c r="G207">
+        <v>0</v>
+      </c>
+      <c r="H207">
+        <v>1</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>0</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A208">
+        <v>7</v>
+      </c>
+      <c r="B208" t="s">
+        <v>56</v>
+      </c>
+      <c r="C208" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D208" t="s">
+        <v>53</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>0</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208">
+        <v>0</v>
+      </c>
+      <c r="J208">
+        <v>0</v>
+      </c>
+      <c r="K208">
+        <v>0</v>
+      </c>
+      <c r="L208">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A209">
+        <v>7</v>
+      </c>
+      <c r="B209" t="s">
+        <v>56</v>
+      </c>
+      <c r="C209" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D209" t="s">
+        <v>51</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>1</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <v>0</v>
+      </c>
+      <c r="J209">
+        <v>1</v>
+      </c>
+      <c r="K209">
+        <v>0</v>
+      </c>
+      <c r="L209">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A210">
+        <v>7</v>
+      </c>
+      <c r="B210" t="s">
+        <v>56</v>
+      </c>
+      <c r="C210" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D210" t="s">
+        <v>52</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>0</v>
+      </c>
+      <c r="G210">
+        <v>0</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210">
+        <v>0</v>
+      </c>
+      <c r="J210">
+        <v>0</v>
+      </c>
+      <c r="K210">
+        <v>0</v>
+      </c>
+      <c r="L210">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A211">
+        <v>7</v>
+      </c>
+      <c r="B211" t="s">
+        <v>56</v>
+      </c>
+      <c r="C211" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D211" t="s">
+        <v>39</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+      <c r="F211">
+        <v>0</v>
+      </c>
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <v>0</v>
+      </c>
+      <c r="J211">
+        <v>0</v>
+      </c>
+      <c r="K211">
+        <v>0</v>
+      </c>
+      <c r="L211">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A212">
+        <v>7</v>
+      </c>
+      <c r="B212" t="s">
+        <v>56</v>
+      </c>
+      <c r="C212" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D212" t="s">
+        <v>40</v>
+      </c>
+      <c r="E212">
+        <v>1</v>
+      </c>
+      <c r="F212">
+        <v>0</v>
+      </c>
+      <c r="G212">
+        <v>0</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <v>0</v>
+      </c>
+      <c r="J212">
+        <v>1</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+      <c r="L212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A213">
+        <v>7</v>
+      </c>
+      <c r="B213" t="s">
+        <v>56</v>
+      </c>
+      <c r="C213" s="2">
+        <v>46309</v>
+      </c>
+      <c r="D213" t="s">
+        <v>41</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
+      <c r="F213">
+        <v>0</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>0</v>
+      </c>
+      <c r="J213">
+        <v>0</v>
+      </c>
+      <c r="K213">
+        <v>0</v>
+      </c>
+      <c r="L213">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C214" s="2"/>
+    </row>
+    <row r="215" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C215" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/SDHL 2026-2027 scoring chances.xlsx
+++ b/SDHL 2026-2027 scoring chances.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mikko/Desktop/Luleå Damjun/Advanced stats_data/SDHL stats/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mikko/Desktop/Luleå Damjun/SDHL stats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B6B245-2387-E840-912E-A7D80C90C54B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20CC70B-8458-6345-A8FB-103FBBBDB4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29620" yWindow="600" windowWidth="30400" windowHeight="22780" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
+    <workbookView xWindow="560" yWindow="2220" windowWidth="30400" windowHeight="17220" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="60">
   <si>
     <t>Goal For</t>
   </si>
@@ -217,6 +217,9 @@
   </si>
   <si>
     <t>OT</t>
+  </si>
+  <si>
+    <t>Frolunda</t>
   </si>
 </sst>
 </file>
@@ -598,7 +601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E4EB1DA-C9FF-4BF6-849D-6254FD5C05A8}">
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:P185"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="10.1640625" style="2" bestFit="1" customWidth="1"/>
@@ -8904,6 +8907,956 @@
         <v>0</v>
       </c>
     </row>
+    <row r="167" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A167">
+        <v>8</v>
+      </c>
+      <c r="B167" t="s">
+        <v>59</v>
+      </c>
+      <c r="C167" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D167">
+        <v>71</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="F167">
+        <v>1</v>
+      </c>
+      <c r="G167">
+        <v>2</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>0</v>
+      </c>
+      <c r="J167">
+        <v>0</v>
+      </c>
+      <c r="K167">
+        <v>0</v>
+      </c>
+      <c r="L167">
+        <v>0</v>
+      </c>
+      <c r="M167">
+        <v>0</v>
+      </c>
+      <c r="N167">
+        <v>2</v>
+      </c>
+      <c r="O167">
+        <v>0</v>
+      </c>
+      <c r="P167">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A168">
+        <v>8</v>
+      </c>
+      <c r="B168" t="s">
+        <v>59</v>
+      </c>
+      <c r="C168" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D168">
+        <v>13</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+      <c r="F168">
+        <v>0</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>1</v>
+      </c>
+      <c r="I168">
+        <v>0</v>
+      </c>
+      <c r="J168">
+        <v>0</v>
+      </c>
+      <c r="K168">
+        <v>0</v>
+      </c>
+      <c r="L168">
+        <v>0</v>
+      </c>
+      <c r="M168">
+        <v>0</v>
+      </c>
+      <c r="N168">
+        <v>1</v>
+      </c>
+      <c r="O168">
+        <v>0</v>
+      </c>
+      <c r="P168">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A169">
+        <v>8</v>
+      </c>
+      <c r="B169" t="s">
+        <v>59</v>
+      </c>
+      <c r="C169" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D169">
+        <v>27</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
+      <c r="F169">
+        <v>0</v>
+      </c>
+      <c r="G169">
+        <v>0</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>0</v>
+      </c>
+      <c r="K169">
+        <v>0</v>
+      </c>
+      <c r="L169">
+        <v>0</v>
+      </c>
+      <c r="M169">
+        <v>0</v>
+      </c>
+      <c r="N169">
+        <v>0</v>
+      </c>
+      <c r="O169">
+        <v>0</v>
+      </c>
+      <c r="P169">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A170">
+        <v>8</v>
+      </c>
+      <c r="B170" t="s">
+        <v>59</v>
+      </c>
+      <c r="C170" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D170">
+        <v>23</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
+      <c r="F170">
+        <v>0</v>
+      </c>
+      <c r="G170">
+        <v>2</v>
+      </c>
+      <c r="H170">
+        <v>1</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>0</v>
+      </c>
+      <c r="K170">
+        <v>0</v>
+      </c>
+      <c r="L170">
+        <v>0</v>
+      </c>
+      <c r="M170">
+        <v>0</v>
+      </c>
+      <c r="N170">
+        <v>0</v>
+      </c>
+      <c r="O170">
+        <v>0</v>
+      </c>
+      <c r="P170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A171">
+        <v>8</v>
+      </c>
+      <c r="B171" t="s">
+        <v>59</v>
+      </c>
+      <c r="C171" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D171">
+        <v>14</v>
+      </c>
+      <c r="E171">
+        <v>1</v>
+      </c>
+      <c r="F171">
+        <v>0</v>
+      </c>
+      <c r="G171">
+        <v>0</v>
+      </c>
+      <c r="H171">
+        <v>3</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>1</v>
+      </c>
+      <c r="K171">
+        <v>0</v>
+      </c>
+      <c r="L171">
+        <v>0</v>
+      </c>
+      <c r="M171">
+        <v>0</v>
+      </c>
+      <c r="N171">
+        <v>0</v>
+      </c>
+      <c r="O171">
+        <v>0</v>
+      </c>
+      <c r="P171">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A172">
+        <v>8</v>
+      </c>
+      <c r="B172" t="s">
+        <v>59</v>
+      </c>
+      <c r="C172" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D172">
+        <v>15</v>
+      </c>
+      <c r="E172">
+        <v>0</v>
+      </c>
+      <c r="F172">
+        <v>0</v>
+      </c>
+      <c r="G172">
+        <v>2</v>
+      </c>
+      <c r="H172">
+        <v>1</v>
+      </c>
+      <c r="I172">
+        <v>0</v>
+      </c>
+      <c r="J172">
+        <v>0</v>
+      </c>
+      <c r="K172">
+        <v>0</v>
+      </c>
+      <c r="L172">
+        <v>0</v>
+      </c>
+      <c r="M172">
+        <v>0</v>
+      </c>
+      <c r="N172">
+        <v>2</v>
+      </c>
+      <c r="O172">
+        <v>0</v>
+      </c>
+      <c r="P172">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A173">
+        <v>8</v>
+      </c>
+      <c r="B173" t="s">
+        <v>59</v>
+      </c>
+      <c r="C173" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D173">
+        <v>42</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+      <c r="F173">
+        <v>0</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>0</v>
+      </c>
+      <c r="J173">
+        <v>0</v>
+      </c>
+      <c r="K173">
+        <v>0</v>
+      </c>
+      <c r="L173">
+        <v>0</v>
+      </c>
+      <c r="M173">
+        <v>0</v>
+      </c>
+      <c r="N173">
+        <v>0</v>
+      </c>
+      <c r="O173">
+        <v>0</v>
+      </c>
+      <c r="P173">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A174">
+        <v>8</v>
+      </c>
+      <c r="B174" t="s">
+        <v>59</v>
+      </c>
+      <c r="C174" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D174">
+        <v>6</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+      <c r="F174">
+        <v>0</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>1</v>
+      </c>
+      <c r="J174">
+        <v>0</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+      <c r="L174">
+        <v>0</v>
+      </c>
+      <c r="M174">
+        <v>1</v>
+      </c>
+      <c r="N174">
+        <v>0</v>
+      </c>
+      <c r="O174">
+        <v>0</v>
+      </c>
+      <c r="P174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A175">
+        <v>8</v>
+      </c>
+      <c r="B175" t="s">
+        <v>59</v>
+      </c>
+      <c r="C175" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D175">
+        <v>8</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175">
+        <v>0</v>
+      </c>
+      <c r="G175">
+        <v>1</v>
+      </c>
+      <c r="H175">
+        <v>1</v>
+      </c>
+      <c r="I175">
+        <v>0</v>
+      </c>
+      <c r="J175">
+        <v>0</v>
+      </c>
+      <c r="K175">
+        <v>0</v>
+      </c>
+      <c r="L175">
+        <v>0</v>
+      </c>
+      <c r="M175">
+        <v>0</v>
+      </c>
+      <c r="N175">
+        <v>5</v>
+      </c>
+      <c r="O175">
+        <v>0</v>
+      </c>
+      <c r="P175">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A176">
+        <v>8</v>
+      </c>
+      <c r="B176" t="s">
+        <v>59</v>
+      </c>
+      <c r="C176" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D176">
+        <v>9</v>
+      </c>
+      <c r="E176">
+        <v>0</v>
+      </c>
+      <c r="F176">
+        <v>0</v>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176">
+        <v>0</v>
+      </c>
+      <c r="J176">
+        <v>0</v>
+      </c>
+      <c r="K176">
+        <v>0</v>
+      </c>
+      <c r="L176">
+        <v>0</v>
+      </c>
+      <c r="M176">
+        <v>0</v>
+      </c>
+      <c r="N176">
+        <v>0</v>
+      </c>
+      <c r="O176">
+        <v>0</v>
+      </c>
+      <c r="P176">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A177">
+        <v>8</v>
+      </c>
+      <c r="B177" t="s">
+        <v>59</v>
+      </c>
+      <c r="C177" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D177">
+        <v>18</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
+      <c r="F177">
+        <v>0</v>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>0</v>
+      </c>
+      <c r="J177">
+        <v>0</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+      <c r="L177">
+        <v>0</v>
+      </c>
+      <c r="M177">
+        <v>0</v>
+      </c>
+      <c r="N177">
+        <v>0</v>
+      </c>
+      <c r="O177">
+        <v>0</v>
+      </c>
+      <c r="P177">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A178">
+        <v>8</v>
+      </c>
+      <c r="B178" t="s">
+        <v>59</v>
+      </c>
+      <c r="C178" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D178">
+        <v>21</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+      <c r="F178">
+        <v>0</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+      <c r="I178">
+        <v>0</v>
+      </c>
+      <c r="J178">
+        <v>0</v>
+      </c>
+      <c r="K178">
+        <v>0</v>
+      </c>
+      <c r="L178">
+        <v>0</v>
+      </c>
+      <c r="M178">
+        <v>0</v>
+      </c>
+      <c r="N178">
+        <v>3</v>
+      </c>
+      <c r="O178">
+        <v>1</v>
+      </c>
+      <c r="P178">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A179">
+        <v>8</v>
+      </c>
+      <c r="B179" t="s">
+        <v>59</v>
+      </c>
+      <c r="C179" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D179">
+        <v>39</v>
+      </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
+      <c r="F179">
+        <v>0</v>
+      </c>
+      <c r="G179">
+        <v>3</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>0</v>
+      </c>
+      <c r="J179">
+        <v>0</v>
+      </c>
+      <c r="K179">
+        <v>0</v>
+      </c>
+      <c r="L179">
+        <v>0</v>
+      </c>
+      <c r="M179">
+        <v>0</v>
+      </c>
+      <c r="N179">
+        <v>0</v>
+      </c>
+      <c r="O179">
+        <v>0</v>
+      </c>
+      <c r="P179">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A180">
+        <v>8</v>
+      </c>
+      <c r="B180" t="s">
+        <v>59</v>
+      </c>
+      <c r="C180" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D180">
+        <v>20</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+      <c r="F180">
+        <v>0</v>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>0</v>
+      </c>
+      <c r="J180">
+        <v>0</v>
+      </c>
+      <c r="K180">
+        <v>0</v>
+      </c>
+      <c r="L180">
+        <v>0</v>
+      </c>
+      <c r="M180">
+        <v>0</v>
+      </c>
+      <c r="N180">
+        <v>0</v>
+      </c>
+      <c r="O180">
+        <v>0</v>
+      </c>
+      <c r="P180">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A181">
+        <v>8</v>
+      </c>
+      <c r="B181" t="s">
+        <v>59</v>
+      </c>
+      <c r="C181" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D181">
+        <v>72</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
+      <c r="F181">
+        <v>0</v>
+      </c>
+      <c r="G181">
+        <v>0</v>
+      </c>
+      <c r="H181">
+        <v>1</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>0</v>
+      </c>
+      <c r="K181">
+        <v>0</v>
+      </c>
+      <c r="L181">
+        <v>0</v>
+      </c>
+      <c r="M181">
+        <v>0</v>
+      </c>
+      <c r="N181">
+        <v>1</v>
+      </c>
+      <c r="O181">
+        <v>0</v>
+      </c>
+      <c r="P181">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A182">
+        <v>8</v>
+      </c>
+      <c r="B182" t="s">
+        <v>59</v>
+      </c>
+      <c r="C182" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D182">
+        <v>81</v>
+      </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
+      <c r="F182">
+        <v>0</v>
+      </c>
+      <c r="G182">
+        <v>0</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>0</v>
+      </c>
+      <c r="K182">
+        <v>0</v>
+      </c>
+      <c r="L182">
+        <v>0</v>
+      </c>
+      <c r="M182">
+        <v>1</v>
+      </c>
+      <c r="N182">
+        <v>2</v>
+      </c>
+      <c r="O182">
+        <v>0</v>
+      </c>
+      <c r="P182">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A183">
+        <v>8</v>
+      </c>
+      <c r="B183" t="s">
+        <v>59</v>
+      </c>
+      <c r="C183" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D183">
+        <v>25</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
+      <c r="F183">
+        <v>0</v>
+      </c>
+      <c r="G183">
+        <v>0</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>0</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+      <c r="L183">
+        <v>0</v>
+      </c>
+      <c r="M183">
+        <v>0</v>
+      </c>
+      <c r="N183">
+        <v>0</v>
+      </c>
+      <c r="O183">
+        <v>0</v>
+      </c>
+      <c r="P183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A184">
+        <v>8</v>
+      </c>
+      <c r="B184" t="s">
+        <v>59</v>
+      </c>
+      <c r="C184" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D184">
+        <v>56</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>0</v>
+      </c>
+      <c r="G184">
+        <v>0</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>0</v>
+      </c>
+      <c r="K184">
+        <v>0</v>
+      </c>
+      <c r="L184">
+        <v>0</v>
+      </c>
+      <c r="M184">
+        <v>0</v>
+      </c>
+      <c r="N184">
+        <v>0</v>
+      </c>
+      <c r="O184">
+        <v>0</v>
+      </c>
+      <c r="P184">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A185">
+        <v>8</v>
+      </c>
+      <c r="B185" t="s">
+        <v>59</v>
+      </c>
+      <c r="C185" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D185">
+        <v>44</v>
+      </c>
+      <c r="E185">
+        <v>0</v>
+      </c>
+      <c r="F185">
+        <v>0</v>
+      </c>
+      <c r="G185">
+        <v>0</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>0</v>
+      </c>
+      <c r="L185">
+        <v>0</v>
+      </c>
+      <c r="M185">
+        <v>0</v>
+      </c>
+      <c r="N185">
+        <v>3</v>
+      </c>
+      <c r="O185">
+        <v>0</v>
+      </c>
+      <c r="P185">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8912,7 +9865,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE8C601-DC7D-42D2-865D-643789981902}">
-  <dimension ref="A1:L215"/>
+  <dimension ref="A1:L241"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -17014,10 +17967,1068 @@
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C214" s="2"/>
+      <c r="A214">
+        <v>8</v>
+      </c>
+      <c r="B214" t="s">
+        <v>59</v>
+      </c>
+      <c r="C214" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D214" t="s">
+        <v>14</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="F214">
+        <v>3</v>
+      </c>
+      <c r="G214">
+        <v>0</v>
+      </c>
+      <c r="H214">
+        <v>0</v>
+      </c>
+      <c r="I214">
+        <v>1</v>
+      </c>
+      <c r="J214">
+        <v>3</v>
+      </c>
+      <c r="K214">
+        <v>0</v>
+      </c>
+      <c r="L214">
+        <v>3</v>
+      </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C215" s="2"/>
+      <c r="A215">
+        <v>8</v>
+      </c>
+      <c r="B215" t="s">
+        <v>59</v>
+      </c>
+      <c r="C215" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D215" t="s">
+        <v>15</v>
+      </c>
+      <c r="E215">
+        <v>1</v>
+      </c>
+      <c r="F215">
+        <v>4</v>
+      </c>
+      <c r="G215">
+        <v>1</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+      <c r="I215">
+        <v>0</v>
+      </c>
+      <c r="J215">
+        <v>10</v>
+      </c>
+      <c r="K215">
+        <v>1</v>
+      </c>
+      <c r="L215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A216">
+        <v>8</v>
+      </c>
+      <c r="B216" t="s">
+        <v>59</v>
+      </c>
+      <c r="C216" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D216" t="s">
+        <v>16</v>
+      </c>
+      <c r="E216">
+        <v>1</v>
+      </c>
+      <c r="F216">
+        <v>3</v>
+      </c>
+      <c r="G216">
+        <v>0</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+      <c r="I216">
+        <v>1</v>
+      </c>
+      <c r="J216">
+        <v>8</v>
+      </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+      <c r="L216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A217">
+        <v>8</v>
+      </c>
+      <c r="B217" t="s">
+        <v>59</v>
+      </c>
+      <c r="C217" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D217" t="s">
+        <v>58</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="F217">
+        <v>0</v>
+      </c>
+      <c r="G217">
+        <v>0</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+      <c r="I217">
+        <v>1</v>
+      </c>
+      <c r="J217">
+        <v>0</v>
+      </c>
+      <c r="K217">
+        <v>0</v>
+      </c>
+      <c r="L217">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A218">
+        <v>8</v>
+      </c>
+      <c r="B218" t="s">
+        <v>59</v>
+      </c>
+      <c r="C218" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D218" t="s">
+        <v>33</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="F218">
+        <v>1</v>
+      </c>
+      <c r="G218">
+        <v>0</v>
+      </c>
+      <c r="H218">
+        <v>0</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>0</v>
+      </c>
+      <c r="K218">
+        <v>0</v>
+      </c>
+      <c r="L218">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A219">
+        <v>8</v>
+      </c>
+      <c r="B219" t="s">
+        <v>59</v>
+      </c>
+      <c r="C219" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D219" t="s">
+        <v>31</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>1</v>
+      </c>
+      <c r="G219">
+        <v>0</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219">
+        <v>1</v>
+      </c>
+      <c r="J219">
+        <v>0</v>
+      </c>
+      <c r="K219">
+        <v>0</v>
+      </c>
+      <c r="L219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A220">
+        <v>8</v>
+      </c>
+      <c r="B220" t="s">
+        <v>59</v>
+      </c>
+      <c r="C220" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D220" t="s">
+        <v>32</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="F220">
+        <v>3</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>2</v>
+      </c>
+      <c r="K220">
+        <v>0</v>
+      </c>
+      <c r="L220">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A221">
+        <v>8</v>
+      </c>
+      <c r="B221" t="s">
+        <v>59</v>
+      </c>
+      <c r="C221" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D221" t="s">
+        <v>30</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="F221">
+        <v>0</v>
+      </c>
+      <c r="G221">
+        <v>0</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>2</v>
+      </c>
+      <c r="K221">
+        <v>0</v>
+      </c>
+      <c r="L221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A222">
+        <v>8</v>
+      </c>
+      <c r="B222" t="s">
+        <v>59</v>
+      </c>
+      <c r="C222" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D222" t="s">
+        <v>29</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>0</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>0</v>
+      </c>
+      <c r="K222">
+        <v>0</v>
+      </c>
+      <c r="L222">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A223">
+        <v>8</v>
+      </c>
+      <c r="B223" t="s">
+        <v>59</v>
+      </c>
+      <c r="C223" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D223" t="s">
+        <v>26</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+      <c r="F223">
+        <v>0</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>0</v>
+      </c>
+      <c r="L223">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A224">
+        <v>8</v>
+      </c>
+      <c r="B224" t="s">
+        <v>59</v>
+      </c>
+      <c r="C224" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D224" t="s">
+        <v>27</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
+      <c r="F224">
+        <v>0</v>
+      </c>
+      <c r="G224">
+        <v>0</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>0</v>
+      </c>
+      <c r="L224">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A225">
+        <v>8</v>
+      </c>
+      <c r="B225" t="s">
+        <v>59</v>
+      </c>
+      <c r="C225" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D225" t="s">
+        <v>50</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>0</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>0</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>0</v>
+      </c>
+      <c r="L225">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A226">
+        <v>8</v>
+      </c>
+      <c r="B226" t="s">
+        <v>59</v>
+      </c>
+      <c r="C226" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D226" t="s">
+        <v>49</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
+      <c r="F226">
+        <v>0</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226">
+        <v>1</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>0</v>
+      </c>
+      <c r="L226">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A227">
+        <v>8</v>
+      </c>
+      <c r="B227" t="s">
+        <v>59</v>
+      </c>
+      <c r="C227" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D227" t="s">
+        <v>22</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>0</v>
+      </c>
+      <c r="G227">
+        <v>0</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>5</v>
+      </c>
+      <c r="K227">
+        <v>0</v>
+      </c>
+      <c r="L227">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A228">
+        <v>8</v>
+      </c>
+      <c r="B228" t="s">
+        <v>59</v>
+      </c>
+      <c r="C228" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D228" t="s">
+        <v>21</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>0</v>
+      </c>
+      <c r="G228">
+        <v>0</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>1</v>
+      </c>
+      <c r="K228">
+        <v>0</v>
+      </c>
+      <c r="L228">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A229">
+        <v>8</v>
+      </c>
+      <c r="B229" t="s">
+        <v>59</v>
+      </c>
+      <c r="C229" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D229" t="s">
+        <v>20</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+      <c r="F229">
+        <v>4</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>1</v>
+      </c>
+      <c r="J229">
+        <v>2</v>
+      </c>
+      <c r="K229">
+        <v>0</v>
+      </c>
+      <c r="L229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A230">
+        <v>8</v>
+      </c>
+      <c r="B230" t="s">
+        <v>59</v>
+      </c>
+      <c r="C230" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D230" t="s">
+        <v>48</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+      <c r="F230">
+        <v>0</v>
+      </c>
+      <c r="G230">
+        <v>0</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>0</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>0</v>
+      </c>
+      <c r="L230">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A231">
+        <v>8</v>
+      </c>
+      <c r="B231" t="s">
+        <v>59</v>
+      </c>
+      <c r="C231" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D231" t="s">
+        <v>18</v>
+      </c>
+      <c r="E231">
+        <v>1</v>
+      </c>
+      <c r="F231">
+        <v>0</v>
+      </c>
+      <c r="G231">
+        <v>0</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>0</v>
+      </c>
+      <c r="L231">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A232">
+        <v>8</v>
+      </c>
+      <c r="B232" t="s">
+        <v>59</v>
+      </c>
+      <c r="C232" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D232" t="s">
+        <v>17</v>
+      </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
+      <c r="F232">
+        <v>1</v>
+      </c>
+      <c r="G232">
+        <v>0</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>4</v>
+      </c>
+      <c r="K232">
+        <v>0</v>
+      </c>
+      <c r="L232">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A233">
+        <v>8</v>
+      </c>
+      <c r="B233" t="s">
+        <v>59</v>
+      </c>
+      <c r="C233" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D233" t="s">
+        <v>38</v>
+      </c>
+      <c r="E233">
+        <v>0</v>
+      </c>
+      <c r="F233">
+        <v>0</v>
+      </c>
+      <c r="G233">
+        <v>0</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+      <c r="L233">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A234">
+        <v>8</v>
+      </c>
+      <c r="B234" t="s">
+        <v>59</v>
+      </c>
+      <c r="C234" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D234" t="s">
+        <v>36</v>
+      </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
+      <c r="F234">
+        <v>0</v>
+      </c>
+      <c r="G234">
+        <v>0</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>0</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>0</v>
+      </c>
+      <c r="L234">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A235">
+        <v>8</v>
+      </c>
+      <c r="B235" t="s">
+        <v>59</v>
+      </c>
+      <c r="C235" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D235" t="s">
+        <v>37</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235">
+        <v>0</v>
+      </c>
+      <c r="G235">
+        <v>0</v>
+      </c>
+      <c r="H235">
+        <v>0</v>
+      </c>
+      <c r="I235">
+        <v>0</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>0</v>
+      </c>
+      <c r="L235">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A236">
+        <v>8</v>
+      </c>
+      <c r="B236" t="s">
+        <v>59</v>
+      </c>
+      <c r="C236" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D236" t="s">
+        <v>34</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+      <c r="F236">
+        <v>0</v>
+      </c>
+      <c r="G236">
+        <v>1</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+      <c r="I236">
+        <v>0</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>0</v>
+      </c>
+      <c r="L236">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A237">
+        <v>8</v>
+      </c>
+      <c r="B237" t="s">
+        <v>59</v>
+      </c>
+      <c r="C237" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D237" t="s">
+        <v>53</v>
+      </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
+      <c r="F237">
+        <v>0</v>
+      </c>
+      <c r="G237">
+        <v>0</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>0</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>0</v>
+      </c>
+      <c r="L237">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A238">
+        <v>8</v>
+      </c>
+      <c r="B238" t="s">
+        <v>59</v>
+      </c>
+      <c r="C238" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D238" t="s">
+        <v>51</v>
+      </c>
+      <c r="E238">
+        <v>0</v>
+      </c>
+      <c r="F238">
+        <v>0</v>
+      </c>
+      <c r="G238">
+        <v>0</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>2</v>
+      </c>
+      <c r="K238">
+        <v>0</v>
+      </c>
+      <c r="L238">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A239">
+        <v>8</v>
+      </c>
+      <c r="B239" t="s">
+        <v>59</v>
+      </c>
+      <c r="C239" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D239" t="s">
+        <v>52</v>
+      </c>
+      <c r="E239">
+        <v>0</v>
+      </c>
+      <c r="F239">
+        <v>0</v>
+      </c>
+      <c r="G239">
+        <v>0</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>2</v>
+      </c>
+      <c r="K239">
+        <v>0</v>
+      </c>
+      <c r="L239">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A240">
+        <v>8</v>
+      </c>
+      <c r="B240" t="s">
+        <v>59</v>
+      </c>
+      <c r="C240" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D240" t="s">
+        <v>39</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+      <c r="F240">
+        <v>0</v>
+      </c>
+      <c r="G240">
+        <v>0</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>0</v>
+      </c>
+      <c r="L240">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A241">
+        <v>8</v>
+      </c>
+      <c r="B241" t="s">
+        <v>59</v>
+      </c>
+      <c r="C241" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D241" t="s">
+        <v>40</v>
+      </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
+      <c r="F241">
+        <v>0</v>
+      </c>
+      <c r="G241">
+        <v>0</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>1</v>
+      </c>
+      <c r="K241">
+        <v>0</v>
+      </c>
+      <c r="L241">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/SDHL 2026-2027 scoring chances.xlsx
+++ b/SDHL 2026-2027 scoring chances.xlsx
@@ -8,14 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mikko/Desktop/Luleå Damjun/SDHL stats/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C20CC70B-8458-6345-A8FB-103FBBBDB4E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968742BC-1C1D-EE4E-BBDC-166B9CC97BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="560" yWindow="2220" windowWidth="30400" windowHeight="17220" activeTab="1" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17220" xr2:uid="{ADDBFA97-6DEC-43CC-A00C-76B611A93AF2}"/>
   </bookViews>
   <sheets>
     <sheet name="Players" sheetId="1" r:id="rId1"/>
     <sheet name="Team" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Team!$A$1:$L$240</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="58">
   <si>
     <t>Goal For</t>
   </si>
@@ -109,9 +112,6 @@
   </si>
   <si>
     <t>Oz reb</t>
-  </si>
-  <si>
-    <t>OZ BL+screen</t>
   </si>
   <si>
     <t>Turnover DZ</t>
@@ -214,9 +214,6 @@
   </si>
   <si>
     <t>Period OT</t>
-  </si>
-  <si>
-    <t>OT</t>
   </si>
   <si>
     <t>Frolunda</t>
@@ -612,10 +609,10 @@
         <v>12</v>
       </c>
       <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D1" t="s">
         <v>13</v>
@@ -662,7 +659,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2">
         <v>46278</v>
@@ -712,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2">
         <v>46278</v>
@@ -762,7 +759,7 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2">
         <v>46278</v>
@@ -812,7 +809,7 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C5" s="2">
         <v>46278</v>
@@ -862,7 +859,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2">
         <v>46278</v>
@@ -912,7 +909,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2">
         <v>46278</v>
@@ -962,7 +959,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2">
         <v>46278</v>
@@ -1012,7 +1009,7 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2">
         <v>46278</v>
@@ -1062,7 +1059,7 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2">
         <v>46278</v>
@@ -1112,7 +1109,7 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C11" s="2">
         <v>46278</v>
@@ -1162,7 +1159,7 @@
         <v>1</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2">
         <v>46278</v>
@@ -1212,7 +1209,7 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="2">
         <v>46278</v>
@@ -1262,7 +1259,7 @@
         <v>1</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="2">
         <v>46278</v>
@@ -1312,7 +1309,7 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2">
         <v>46278</v>
@@ -1362,7 +1359,7 @@
         <v>1</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="2">
         <v>46278</v>
@@ -1412,7 +1409,7 @@
         <v>1</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2">
         <v>46278</v>
@@ -1462,7 +1459,7 @@
         <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2">
         <v>46278</v>
@@ -1512,7 +1509,7 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="2">
         <v>46278</v>
@@ -1562,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2">
         <v>46278</v>
@@ -1612,7 +1609,7 @@
         <v>1</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2">
         <v>46278</v>
@@ -1662,7 +1659,7 @@
         <v>1</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" s="2">
         <v>46278</v>
@@ -1712,7 +1709,7 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C23" s="2">
         <v>46282</v>
@@ -1762,7 +1759,7 @@
         <v>2</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2">
         <v>46282</v>
@@ -1812,7 +1809,7 @@
         <v>2</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C25" s="2">
         <v>46282</v>
@@ -1862,7 +1859,7 @@
         <v>2</v>
       </c>
       <c r="B26" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C26" s="2">
         <v>46282</v>
@@ -1912,7 +1909,7 @@
         <v>2</v>
       </c>
       <c r="B27" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2">
         <v>46282</v>
@@ -1962,7 +1959,7 @@
         <v>2</v>
       </c>
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C28" s="2">
         <v>46282</v>
@@ -2012,7 +2009,7 @@
         <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C29" s="2">
         <v>46282</v>
@@ -2062,7 +2059,7 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C30" s="2">
         <v>46282</v>
@@ -2112,7 +2109,7 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C31" s="2">
         <v>46282</v>
@@ -2162,7 +2159,7 @@
         <v>2</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C32" s="2">
         <v>46282</v>
@@ -2212,7 +2209,7 @@
         <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C33" s="2">
         <v>46282</v>
@@ -2262,7 +2259,7 @@
         <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C34" s="2">
         <v>46282</v>
@@ -2312,7 +2309,7 @@
         <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C35" s="2">
         <v>46282</v>
@@ -2362,7 +2359,7 @@
         <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C36" s="2">
         <v>46282</v>
@@ -2412,7 +2409,7 @@
         <v>2</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C37" s="2">
         <v>46282</v>
@@ -2462,7 +2459,7 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C38" s="2">
         <v>46282</v>
@@ -2512,7 +2509,7 @@
         <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C39" s="2">
         <v>46282</v>
@@ -2562,7 +2559,7 @@
         <v>2</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C40" s="2">
         <v>46282</v>
@@ -2612,7 +2609,7 @@
         <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C41" s="2">
         <v>46282</v>
@@ -2662,7 +2659,7 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C42" s="2">
         <v>46282</v>
@@ -2712,7 +2709,7 @@
         <v>2</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C43" s="2">
         <v>46282</v>
@@ -2762,7 +2759,7 @@
         <v>3</v>
       </c>
       <c r="B44" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C44" s="2">
         <v>46285</v>
@@ -2812,7 +2809,7 @@
         <v>3</v>
       </c>
       <c r="B45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C45" s="2">
         <v>46285</v>
@@ -2862,7 +2859,7 @@
         <v>3</v>
       </c>
       <c r="B46" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C46" s="2">
         <v>46285</v>
@@ -2912,7 +2909,7 @@
         <v>3</v>
       </c>
       <c r="B47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C47" s="2">
         <v>46285</v>
@@ -2962,7 +2959,7 @@
         <v>3</v>
       </c>
       <c r="B48" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C48" s="2">
         <v>46285</v>
@@ -3012,7 +3009,7 @@
         <v>3</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C49" s="2">
         <v>46285</v>
@@ -3062,7 +3059,7 @@
         <v>3</v>
       </c>
       <c r="B50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C50" s="2">
         <v>46285</v>
@@ -3112,7 +3109,7 @@
         <v>3</v>
       </c>
       <c r="B51" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C51" s="2">
         <v>46285</v>
@@ -3162,7 +3159,7 @@
         <v>3</v>
       </c>
       <c r="B52" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C52" s="2">
         <v>46285</v>
@@ -3212,7 +3209,7 @@
         <v>3</v>
       </c>
       <c r="B53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C53" s="2">
         <v>46285</v>
@@ -3262,7 +3259,7 @@
         <v>3</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C54" s="2">
         <v>46285</v>
@@ -3312,7 +3309,7 @@
         <v>3</v>
       </c>
       <c r="B55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C55" s="2">
         <v>46285</v>
@@ -3362,7 +3359,7 @@
         <v>3</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C56" s="2">
         <v>46285</v>
@@ -3412,7 +3409,7 @@
         <v>3</v>
       </c>
       <c r="B57" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C57" s="2">
         <v>46285</v>
@@ -3462,7 +3459,7 @@
         <v>3</v>
       </c>
       <c r="B58" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C58" s="2">
         <v>46285</v>
@@ -3512,7 +3509,7 @@
         <v>3</v>
       </c>
       <c r="B59" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C59" s="2">
         <v>46285</v>
@@ -3562,7 +3559,7 @@
         <v>3</v>
       </c>
       <c r="B60" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C60" s="2">
         <v>46285</v>
@@ -3612,7 +3609,7 @@
         <v>3</v>
       </c>
       <c r="B61" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C61" s="2">
         <v>46285</v>
@@ -3662,7 +3659,7 @@
         <v>3</v>
       </c>
       <c r="B62" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C62" s="2">
         <v>46285</v>
@@ -3712,7 +3709,7 @@
         <v>3</v>
       </c>
       <c r="B63" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C63" s="2">
         <v>46285</v>
@@ -3762,7 +3759,7 @@
         <v>3</v>
       </c>
       <c r="B64" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C64" s="2">
         <v>46285</v>
@@ -3812,7 +3809,7 @@
         <v>4</v>
       </c>
       <c r="B65" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C65" s="2">
         <v>46291</v>
@@ -3862,7 +3859,7 @@
         <v>4</v>
       </c>
       <c r="B66" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C66" s="2">
         <v>46291</v>
@@ -3912,7 +3909,7 @@
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C67" s="2">
         <v>46291</v>
@@ -3962,7 +3959,7 @@
         <v>4</v>
       </c>
       <c r="B68" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C68" s="2">
         <v>46291</v>
@@ -4012,7 +4009,7 @@
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C69" s="2">
         <v>46291</v>
@@ -4062,7 +4059,7 @@
         <v>4</v>
       </c>
       <c r="B70" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C70" s="2">
         <v>46291</v>
@@ -4112,7 +4109,7 @@
         <v>4</v>
       </c>
       <c r="B71" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C71" s="2">
         <v>46291</v>
@@ -4162,7 +4159,7 @@
         <v>4</v>
       </c>
       <c r="B72" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C72" s="2">
         <v>46291</v>
@@ -4212,7 +4209,7 @@
         <v>4</v>
       </c>
       <c r="B73" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C73" s="2">
         <v>46291</v>
@@ -4262,7 +4259,7 @@
         <v>4</v>
       </c>
       <c r="B74" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C74" s="2">
         <v>46291</v>
@@ -4312,7 +4309,7 @@
         <v>4</v>
       </c>
       <c r="B75" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C75" s="2">
         <v>46291</v>
@@ -4362,7 +4359,7 @@
         <v>4</v>
       </c>
       <c r="B76" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C76" s="2">
         <v>46291</v>
@@ -4412,7 +4409,7 @@
         <v>4</v>
       </c>
       <c r="B77" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C77" s="2">
         <v>46291</v>
@@ -4462,7 +4459,7 @@
         <v>4</v>
       </c>
       <c r="B78" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C78" s="2">
         <v>46291</v>
@@ -4512,7 +4509,7 @@
         <v>4</v>
       </c>
       <c r="B79" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C79" s="2">
         <v>46291</v>
@@ -4562,7 +4559,7 @@
         <v>4</v>
       </c>
       <c r="B80" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C80" s="2">
         <v>46291</v>
@@ -4612,7 +4609,7 @@
         <v>4</v>
       </c>
       <c r="B81" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C81" s="2">
         <v>46291</v>
@@ -4662,7 +4659,7 @@
         <v>4</v>
       </c>
       <c r="B82" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C82" s="2">
         <v>46291</v>
@@ -4712,7 +4709,7 @@
         <v>4</v>
       </c>
       <c r="B83" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C83" s="2">
         <v>46291</v>
@@ -4762,7 +4759,7 @@
         <v>4</v>
       </c>
       <c r="B84" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C84" s="2">
         <v>46291</v>
@@ -4812,7 +4809,7 @@
         <v>4</v>
       </c>
       <c r="B85" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C85" s="2">
         <v>46291</v>
@@ -4862,7 +4859,7 @@
         <v>4</v>
       </c>
       <c r="B86" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C86" s="2">
         <v>46291</v>
@@ -4912,7 +4909,7 @@
         <v>4</v>
       </c>
       <c r="B87" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C87" s="2">
         <v>46291</v>
@@ -4962,7 +4959,7 @@
         <v>4</v>
       </c>
       <c r="B88" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C88" s="2">
         <v>46291</v>
@@ -5012,7 +5009,7 @@
         <v>4</v>
       </c>
       <c r="B89" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C89" s="2">
         <v>46291</v>
@@ -5062,7 +5059,7 @@
         <v>4</v>
       </c>
       <c r="B90" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C90" s="2">
         <v>46291</v>
@@ -5112,7 +5109,7 @@
         <v>4</v>
       </c>
       <c r="B91" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C91" s="2">
         <v>46291</v>
@@ -5162,7 +5159,7 @@
         <v>4</v>
       </c>
       <c r="B92" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C92" s="2">
         <v>46291</v>
@@ -5212,7 +5209,7 @@
         <v>4</v>
       </c>
       <c r="B93" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C93" s="2">
         <v>46291</v>
@@ -5262,7 +5259,7 @@
         <v>4</v>
       </c>
       <c r="B94" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C94" s="2">
         <v>46291</v>
@@ -5312,7 +5309,7 @@
         <v>4</v>
       </c>
       <c r="B95" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C95" s="2">
         <v>46291</v>
@@ -5362,7 +5359,7 @@
         <v>5</v>
       </c>
       <c r="B96" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C96" s="2">
         <v>46304</v>
@@ -5412,7 +5409,7 @@
         <v>5</v>
       </c>
       <c r="B97" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C97" s="2">
         <v>46304</v>
@@ -5462,7 +5459,7 @@
         <v>5</v>
       </c>
       <c r="B98" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C98" s="2">
         <v>46304</v>
@@ -5512,7 +5509,7 @@
         <v>5</v>
       </c>
       <c r="B99" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C99" s="2">
         <v>46304</v>
@@ -5562,7 +5559,7 @@
         <v>5</v>
       </c>
       <c r="B100" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C100" s="2">
         <v>46304</v>
@@ -5612,7 +5609,7 @@
         <v>5</v>
       </c>
       <c r="B101" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C101" s="2">
         <v>46304</v>
@@ -5662,7 +5659,7 @@
         <v>5</v>
       </c>
       <c r="B102" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C102" s="2">
         <v>46304</v>
@@ -5712,7 +5709,7 @@
         <v>5</v>
       </c>
       <c r="B103" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C103" s="2">
         <v>46304</v>
@@ -5762,7 +5759,7 @@
         <v>5</v>
       </c>
       <c r="B104" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C104" s="2">
         <v>46304</v>
@@ -5812,7 +5809,7 @@
         <v>5</v>
       </c>
       <c r="B105" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C105" s="2">
         <v>46304</v>
@@ -5862,7 +5859,7 @@
         <v>5</v>
       </c>
       <c r="B106" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C106" s="2">
         <v>46304</v>
@@ -5912,7 +5909,7 @@
         <v>5</v>
       </c>
       <c r="B107" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C107" s="2">
         <v>46304</v>
@@ -5962,7 +5959,7 @@
         <v>5</v>
       </c>
       <c r="B108" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C108" s="2">
         <v>46304</v>
@@ -6012,7 +6009,7 @@
         <v>5</v>
       </c>
       <c r="B109" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C109" s="2">
         <v>46304</v>
@@ -6062,7 +6059,7 @@
         <v>5</v>
       </c>
       <c r="B110" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C110" s="2">
         <v>46304</v>
@@ -6112,7 +6109,7 @@
         <v>5</v>
       </c>
       <c r="B111" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C111" s="2">
         <v>46304</v>
@@ -6162,7 +6159,7 @@
         <v>5</v>
       </c>
       <c r="B112" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C112" s="2">
         <v>46304</v>
@@ -6212,7 +6209,7 @@
         <v>5</v>
       </c>
       <c r="B113" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C113" s="2">
         <v>46304</v>
@@ -6262,7 +6259,7 @@
         <v>5</v>
       </c>
       <c r="B114" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C114" s="2">
         <v>46304</v>
@@ -6312,7 +6309,7 @@
         <v>5</v>
       </c>
       <c r="B115" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C115" s="2">
         <v>46304</v>
@@ -6362,7 +6359,7 @@
         <v>5</v>
       </c>
       <c r="B116" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C116" s="2">
         <v>46304</v>
@@ -6412,7 +6409,7 @@
         <v>5</v>
       </c>
       <c r="B117" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C117" s="2">
         <v>46304</v>
@@ -6462,7 +6459,7 @@
         <v>5</v>
       </c>
       <c r="B118" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C118" s="2">
         <v>46304</v>
@@ -6512,7 +6509,7 @@
         <v>5</v>
       </c>
       <c r="B119" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C119" s="2">
         <v>46304</v>
@@ -6562,7 +6559,7 @@
         <v>5</v>
       </c>
       <c r="B120" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C120" s="2">
         <v>46304</v>
@@ -6612,7 +6609,7 @@
         <v>5</v>
       </c>
       <c r="B121" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C121" s="2">
         <v>46304</v>
@@ -6662,7 +6659,7 @@
         <v>5</v>
       </c>
       <c r="B122" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C122" s="2">
         <v>46304</v>
@@ -6712,7 +6709,7 @@
         <v>5</v>
       </c>
       <c r="B123" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C123" s="2">
         <v>46304</v>
@@ -6762,7 +6759,7 @@
         <v>5</v>
       </c>
       <c r="B124" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C124" s="2">
         <v>46304</v>
@@ -6812,7 +6809,7 @@
         <v>5</v>
       </c>
       <c r="B125" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C125" s="2">
         <v>46304</v>
@@ -6862,7 +6859,7 @@
         <v>5</v>
       </c>
       <c r="B126" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C126" s="2">
         <v>46304</v>
@@ -6912,7 +6909,7 @@
         <v>6</v>
       </c>
       <c r="B127" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C127" s="2">
         <v>46306</v>
@@ -6962,7 +6959,7 @@
         <v>6</v>
       </c>
       <c r="B128" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C128" s="2">
         <v>46306</v>
@@ -7012,7 +7009,7 @@
         <v>6</v>
       </c>
       <c r="B129" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C129" s="2">
         <v>46306</v>
@@ -7062,7 +7059,7 @@
         <v>6</v>
       </c>
       <c r="B130" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C130" s="2">
         <v>46306</v>
@@ -7112,7 +7109,7 @@
         <v>6</v>
       </c>
       <c r="B131" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C131" s="2">
         <v>46306</v>
@@ -7162,7 +7159,7 @@
         <v>6</v>
       </c>
       <c r="B132" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C132" s="2">
         <v>46306</v>
@@ -7212,7 +7209,7 @@
         <v>6</v>
       </c>
       <c r="B133" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C133" s="2">
         <v>46306</v>
@@ -7262,7 +7259,7 @@
         <v>6</v>
       </c>
       <c r="B134" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C134" s="2">
         <v>46306</v>
@@ -7312,7 +7309,7 @@
         <v>6</v>
       </c>
       <c r="B135" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C135" s="2">
         <v>46306</v>
@@ -7362,7 +7359,7 @@
         <v>6</v>
       </c>
       <c r="B136" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C136" s="2">
         <v>46306</v>
@@ -7412,7 +7409,7 @@
         <v>6</v>
       </c>
       <c r="B137" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C137" s="2">
         <v>46306</v>
@@ -7462,7 +7459,7 @@
         <v>6</v>
       </c>
       <c r="B138" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C138" s="2">
         <v>46306</v>
@@ -7512,7 +7509,7 @@
         <v>6</v>
       </c>
       <c r="B139" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C139" s="2">
         <v>46306</v>
@@ -7562,7 +7559,7 @@
         <v>6</v>
       </c>
       <c r="B140" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C140" s="2">
         <v>46306</v>
@@ -7612,7 +7609,7 @@
         <v>6</v>
       </c>
       <c r="B141" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C141" s="2">
         <v>46306</v>
@@ -7662,7 +7659,7 @@
         <v>6</v>
       </c>
       <c r="B142" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C142" s="2">
         <v>46306</v>
@@ -7712,7 +7709,7 @@
         <v>6</v>
       </c>
       <c r="B143" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C143" s="2">
         <v>46306</v>
@@ -7762,7 +7759,7 @@
         <v>6</v>
       </c>
       <c r="B144" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C144" s="2">
         <v>46306</v>
@@ -7812,7 +7809,7 @@
         <v>6</v>
       </c>
       <c r="B145" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C145" s="2">
         <v>46306</v>
@@ -7862,7 +7859,7 @@
         <v>6</v>
       </c>
       <c r="B146" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C146" s="2">
         <v>46306</v>
@@ -7912,7 +7909,7 @@
         <v>6</v>
       </c>
       <c r="B147" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C147" s="2">
         <v>46306</v>
@@ -7962,7 +7959,7 @@
         <v>7</v>
       </c>
       <c r="B148" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C148" s="2">
         <v>46309</v>
@@ -7971,7 +7968,7 @@
         <v>71</v>
       </c>
       <c r="E148">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F148">
         <v>1</v>
@@ -8012,7 +8009,7 @@
         <v>7</v>
       </c>
       <c r="B149" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C149" s="2">
         <v>46309</v>
@@ -8021,7 +8018,7 @@
         <v>13</v>
       </c>
       <c r="E149">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -8062,7 +8059,7 @@
         <v>7</v>
       </c>
       <c r="B150" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C150" s="2">
         <v>46309</v>
@@ -8112,7 +8109,7 @@
         <v>7</v>
       </c>
       <c r="B151" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C151" s="2">
         <v>46309</v>
@@ -8162,7 +8159,7 @@
         <v>7</v>
       </c>
       <c r="B152" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C152" s="2">
         <v>46309</v>
@@ -8171,7 +8168,7 @@
         <v>14</v>
       </c>
       <c r="E152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -8212,7 +8209,7 @@
         <v>7</v>
       </c>
       <c r="B153" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C153" s="2">
         <v>46309</v>
@@ -8221,7 +8218,7 @@
         <v>15</v>
       </c>
       <c r="E153">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F153">
         <v>0</v>
@@ -8262,7 +8259,7 @@
         <v>7</v>
       </c>
       <c r="B154" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C154" s="2">
         <v>46309</v>
@@ -8271,7 +8268,7 @@
         <v>42</v>
       </c>
       <c r="E154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F154">
         <v>0</v>
@@ -8312,7 +8309,7 @@
         <v>7</v>
       </c>
       <c r="B155" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C155" s="2">
         <v>46309</v>
@@ -8321,7 +8318,7 @@
         <v>6</v>
       </c>
       <c r="E155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F155">
         <v>0</v>
@@ -8362,7 +8359,7 @@
         <v>7</v>
       </c>
       <c r="B156" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C156" s="2">
         <v>46309</v>
@@ -8412,7 +8409,7 @@
         <v>7</v>
       </c>
       <c r="B157" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C157" s="2">
         <v>46309</v>
@@ -8462,7 +8459,7 @@
         <v>7</v>
       </c>
       <c r="B158" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C158" s="2">
         <v>46309</v>
@@ -8471,7 +8468,7 @@
         <v>18</v>
       </c>
       <c r="E158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>1</v>
@@ -8512,7 +8509,7 @@
         <v>7</v>
       </c>
       <c r="B159" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C159" s="2">
         <v>46309</v>
@@ -8521,7 +8518,7 @@
         <v>21</v>
       </c>
       <c r="E159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F159">
         <v>1</v>
@@ -8562,7 +8559,7 @@
         <v>7</v>
       </c>
       <c r="B160" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C160" s="2">
         <v>46309</v>
@@ -8612,7 +8609,7 @@
         <v>7</v>
       </c>
       <c r="B161" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C161" s="2">
         <v>46309</v>
@@ -8621,7 +8618,7 @@
         <v>20</v>
       </c>
       <c r="E161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -8662,7 +8659,7 @@
         <v>7</v>
       </c>
       <c r="B162" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C162" s="2">
         <v>46309</v>
@@ -8712,7 +8709,7 @@
         <v>7</v>
       </c>
       <c r="B163" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C163" s="2">
         <v>46309</v>
@@ -8721,7 +8718,7 @@
         <v>81</v>
       </c>
       <c r="E163">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -8762,7 +8759,7 @@
         <v>7</v>
       </c>
       <c r="B164" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C164" s="2">
         <v>46309</v>
@@ -8771,7 +8768,7 @@
         <v>25</v>
       </c>
       <c r="E164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -8812,7 +8809,7 @@
         <v>7</v>
       </c>
       <c r="B165" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C165" s="2">
         <v>46309</v>
@@ -8862,7 +8859,7 @@
         <v>7</v>
       </c>
       <c r="B166" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C166" s="2">
         <v>46309</v>
@@ -8871,7 +8868,7 @@
         <v>44</v>
       </c>
       <c r="E166">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -8912,7 +8909,7 @@
         <v>8</v>
       </c>
       <c r="B167" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C167" s="2">
         <v>46311</v>
@@ -8962,7 +8959,7 @@
         <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C168" s="2">
         <v>46311</v>
@@ -9012,7 +9009,7 @@
         <v>8</v>
       </c>
       <c r="B169" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C169" s="2">
         <v>46311</v>
@@ -9062,7 +9059,7 @@
         <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C170" s="2">
         <v>46311</v>
@@ -9112,7 +9109,7 @@
         <v>8</v>
       </c>
       <c r="B171" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C171" s="2">
         <v>46311</v>
@@ -9162,7 +9159,7 @@
         <v>8</v>
       </c>
       <c r="B172" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C172" s="2">
         <v>46311</v>
@@ -9212,7 +9209,7 @@
         <v>8</v>
       </c>
       <c r="B173" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C173" s="2">
         <v>46311</v>
@@ -9262,7 +9259,7 @@
         <v>8</v>
       </c>
       <c r="B174" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C174" s="2">
         <v>46311</v>
@@ -9312,7 +9309,7 @@
         <v>8</v>
       </c>
       <c r="B175" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C175" s="2">
         <v>46311</v>
@@ -9362,7 +9359,7 @@
         <v>8</v>
       </c>
       <c r="B176" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C176" s="2">
         <v>46311</v>
@@ -9412,7 +9409,7 @@
         <v>8</v>
       </c>
       <c r="B177" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C177" s="2">
         <v>46311</v>
@@ -9462,7 +9459,7 @@
         <v>8</v>
       </c>
       <c r="B178" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C178" s="2">
         <v>46311</v>
@@ -9512,7 +9509,7 @@
         <v>8</v>
       </c>
       <c r="B179" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C179" s="2">
         <v>46311</v>
@@ -9562,7 +9559,7 @@
         <v>8</v>
       </c>
       <c r="B180" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C180" s="2">
         <v>46311</v>
@@ -9612,7 +9609,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C181" s="2">
         <v>46311</v>
@@ -9662,7 +9659,7 @@
         <v>8</v>
       </c>
       <c r="B182" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C182" s="2">
         <v>46311</v>
@@ -9712,7 +9709,7 @@
         <v>8</v>
       </c>
       <c r="B183" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C183" s="2">
         <v>46311</v>
@@ -9762,7 +9759,7 @@
         <v>8</v>
       </c>
       <c r="B184" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C184" s="2">
         <v>46311</v>
@@ -9812,7 +9809,7 @@
         <v>8</v>
       </c>
       <c r="B185" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C185" s="2">
         <v>46311</v>
@@ -9865,7 +9862,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFE8C601-DC7D-42D2-865D-643789981902}">
-  <dimension ref="A1:L241"/>
+  <dimension ref="A1:L240"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
@@ -9877,13 +9874,13 @@
         <v>12</v>
       </c>
       <c r="B1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" t="s">
         <v>43</v>
       </c>
-      <c r="C1" t="s">
-        <v>44</v>
-      </c>
       <c r="D1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -9915,16 +9912,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C2" s="2">
         <v>46278</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F2">
         <v>3</v>
@@ -9933,7 +9930,7 @@
         <v>0</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2">
         <v>1</v>
@@ -9950,13 +9947,13 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C3" s="2">
-        <v>46278</v>
+        <v>46306</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -9965,19 +9962,19 @@
         <v>2</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G3">
         <v>0</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K3">
         <v>0</v>
@@ -9988,22 +9985,22 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C4" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -10015,7 +10012,7 @@
         <v>0</v>
       </c>
       <c r="J4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K4">
         <v>0</v>
@@ -10026,22 +10023,22 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C5" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -10053,7 +10050,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -10067,19 +10064,19 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C6" s="2">
         <v>46278</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -10088,10 +10085,10 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K6">
         <v>0</v>
@@ -10105,16 +10102,16 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C7" s="2">
         <v>46278</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -10129,7 +10126,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7">
         <v>0</v>
@@ -10143,16 +10140,16 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C8" s="2">
         <v>46278</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8">
         <v>0</v>
@@ -10181,13 +10178,13 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C9" s="2">
         <v>46278</v>
       </c>
       <c r="D9" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -10216,22 +10213,22 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
         <v>45</v>
       </c>
       <c r="C10" s="2">
-        <v>46278</v>
+        <v>46282</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -10240,10 +10237,10 @@
         <v>0</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -10254,22 +10251,22 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B11" t="s">
         <v>45</v>
       </c>
       <c r="C11" s="2">
-        <v>46278</v>
+        <v>46282</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -10281,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11">
         <v>0</v>
@@ -10292,19 +10289,19 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="2">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="D12" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
         <v>0</v>
@@ -10330,22 +10327,22 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="2">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -10357,7 +10354,7 @@
         <v>0</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -10368,19 +10365,19 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="2">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14">
         <v>0</v>
@@ -10395,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -10406,34 +10403,34 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="D15" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -10444,22 +10441,22 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="2">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="D16" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -10471,7 +10468,7 @@
         <v>0</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K16">
         <v>0</v>
@@ -10482,22 +10479,22 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" s="2">
-        <v>46278</v>
+        <v>46285</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -10506,13 +10503,13 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17">
         <v>0</v>
@@ -10520,19 +10517,19 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C18" s="2">
-        <v>46278</v>
+        <v>46306</v>
       </c>
       <c r="D18" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F18">
         <v>0</v>
@@ -10547,7 +10544,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K18">
         <v>0</v>
@@ -10558,22 +10555,22 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C19" s="2">
-        <v>46278</v>
+        <v>46306</v>
       </c>
       <c r="D19" t="s">
         <v>30</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F19">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -10582,7 +10579,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J19">
         <v>1</v>
@@ -10596,34 +10593,34 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C20" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G20">
         <v>0</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I20">
         <v>0</v>
       </c>
       <c r="J20">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K20">
         <v>0</v>
@@ -10634,72 +10631,72 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B21" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C21" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D21" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F21">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G21">
         <v>0</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I21">
         <v>0</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C22" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F22">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J22">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K22">
         <v>0</v>
@@ -10710,19 +10707,19 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C23" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -10737,7 +10734,7 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -10748,34 +10745,34 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C24" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D24" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G24">
         <v>0</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I24">
         <v>0</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -10786,22 +10783,22 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D25" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F25">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -10810,10 +10807,10 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -10824,19 +10821,19 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D26" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26">
         <v>0</v>
@@ -10862,19 +10859,19 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B27" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C27" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D27" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F27">
         <v>0</v>
@@ -10886,7 +10883,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -10900,19 +10897,19 @@
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C28" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D28" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F28">
         <v>0</v>
@@ -10938,57 +10935,57 @@
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C29" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D29" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>0</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I29">
         <v>0</v>
       </c>
       <c r="J29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B30" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2">
-        <v>46278</v>
+        <v>46309</v>
       </c>
       <c r="D30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F30">
         <v>0</v>
@@ -11003,7 +11000,7 @@
         <v>0</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K30">
         <v>0</v>
@@ -11014,60 +11011,60 @@
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31">
+        <v>8</v>
+      </c>
+      <c r="B31" t="s">
+        <v>57</v>
+      </c>
+      <c r="C31" s="2">
+        <v>46311</v>
+      </c>
+      <c r="D31" t="s">
+        <v>15</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>10</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31">
         <v>2</v>
-      </c>
-      <c r="B31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="2">
-        <v>46282</v>
-      </c>
-      <c r="D31" t="s">
-        <v>18</v>
-      </c>
-      <c r="E31">
-        <v>1</v>
-      </c>
-      <c r="F31">
-        <v>0</v>
-      </c>
-      <c r="G31">
-        <v>0</v>
-      </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>2</v>
-      </c>
-      <c r="J31">
-        <v>1</v>
-      </c>
-      <c r="K31">
-        <v>0</v>
-      </c>
-      <c r="L31">
-        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C32" s="2">
-        <v>46282</v>
+        <v>46311</v>
       </c>
       <c r="D32" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F32">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -11076,10 +11073,10 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -11090,22 +11087,22 @@
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A33">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="C33" s="2">
-        <v>46282</v>
+        <v>46311</v>
       </c>
       <c r="D33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F33">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -11117,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="J33">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K33">
         <v>0</v>
@@ -11128,22 +11125,22 @@
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A34">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C34" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D34" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E34">
         <v>0</v>
       </c>
       <c r="F34">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -11152,10 +11149,10 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -11166,16 +11163,16 @@
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A35">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B35" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C35" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D35" t="s">
-        <v>22</v>
+        <v>56</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -11204,13 +11201,13 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A36">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B36" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C36" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D36" t="s">
         <v>17</v>
@@ -11228,7 +11225,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J36">
         <v>0</v>
@@ -11242,16 +11239,16 @@
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B37" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C37" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D37" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -11280,22 +11277,22 @@
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B38" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C38" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D38" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="E38">
         <v>0</v>
       </c>
       <c r="F38">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -11307,7 +11304,7 @@
         <v>0</v>
       </c>
       <c r="J38">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -11318,22 +11315,22 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B39" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C39" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D39" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="E39">
         <v>0</v>
       </c>
       <c r="F39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -11356,22 +11353,22 @@
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A40">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C40" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D40" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -11383,7 +11380,7 @@
         <v>0</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -11394,16 +11391,16 @@
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B41" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C41" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D41" t="s">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -11432,22 +11429,22 @@
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C42" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D42" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E42">
         <v>0</v>
       </c>
       <c r="F42">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -11459,7 +11456,7 @@
         <v>0</v>
       </c>
       <c r="J42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -11470,22 +11467,22 @@
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A43">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B43" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C43" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D43" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="E43">
         <v>0</v>
       </c>
       <c r="F43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -11508,16 +11505,16 @@
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A44">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B44" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C44" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D44" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -11546,16 +11543,16 @@
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A45">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B45" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C45" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D45" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -11584,16 +11581,16 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B46" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C46" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D46" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -11608,7 +11605,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -11622,16 +11619,16 @@
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B47" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C47" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D47" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -11660,16 +11657,16 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B48" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C48" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D48" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -11687,7 +11684,7 @@
         <v>0</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48">
         <v>0</v>
@@ -11698,16 +11695,16 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C49" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D49" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -11725,7 +11722,7 @@
         <v>0</v>
       </c>
       <c r="J49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K49">
         <v>0</v>
@@ -11736,22 +11733,22 @@
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C50" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D50" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E50">
         <v>0</v>
       </c>
       <c r="F50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -11763,27 +11760,27 @@
         <v>0</v>
       </c>
       <c r="J50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50">
         <v>0</v>
       </c>
       <c r="L50">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C51" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D51" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -11795,7 +11792,7 @@
         <v>0</v>
       </c>
       <c r="H51">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I51">
         <v>0</v>
@@ -11812,34 +11809,34 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52">
+        <v>1</v>
+      </c>
+      <c r="B52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" s="2">
+        <v>46278</v>
+      </c>
+      <c r="D52" t="s">
+        <v>35</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
+      <c r="H52">
+        <v>0</v>
+      </c>
+      <c r="I52">
+        <v>1</v>
+      </c>
+      <c r="J52">
         <v>2</v>
-      </c>
-      <c r="B52" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" s="2">
-        <v>46282</v>
-      </c>
-      <c r="D52" t="s">
-        <v>38</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>0</v>
-      </c>
-      <c r="G52">
-        <v>0</v>
-      </c>
-      <c r="H52">
-        <v>0</v>
-      </c>
-      <c r="I52">
-        <v>0</v>
-      </c>
-      <c r="J52">
-        <v>0</v>
       </c>
       <c r="K52">
         <v>0</v>
@@ -11850,16 +11847,16 @@
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B53" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C53" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D53" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -11888,16 +11885,16 @@
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B54" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C54" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D54" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -11926,16 +11923,16 @@
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C55" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D55" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -11953,7 +11950,7 @@
         <v>0</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K55">
         <v>0</v>
@@ -11964,34 +11961,34 @@
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56">
+        <v>1</v>
+      </c>
+      <c r="B56" t="s">
+        <v>44</v>
+      </c>
+      <c r="C56" s="2">
+        <v>46278</v>
+      </c>
+      <c r="D56" t="s">
+        <v>39</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+      <c r="F56">
+        <v>1</v>
+      </c>
+      <c r="G56">
+        <v>0</v>
+      </c>
+      <c r="H56">
+        <v>0</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
         <v>2</v>
-      </c>
-      <c r="B56" t="s">
-        <v>46</v>
-      </c>
-      <c r="C56" s="2">
-        <v>46282</v>
-      </c>
-      <c r="D56" t="s">
-        <v>14</v>
-      </c>
-      <c r="E56">
-        <v>1</v>
-      </c>
-      <c r="F56">
-        <v>7</v>
-      </c>
-      <c r="G56">
-        <v>0</v>
-      </c>
-      <c r="H56">
-        <v>0</v>
-      </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
-        <v>3</v>
       </c>
       <c r="K56">
         <v>0</v>
@@ -12002,22 +11999,22 @@
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C57" s="2">
-        <v>46282</v>
+        <v>46278</v>
       </c>
       <c r="D57" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57">
         <v>0</v>
@@ -12026,10 +12023,10 @@
         <v>0</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J57">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K57">
         <v>0</v>
@@ -12043,19 +12040,19 @@
         <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C58" s="2">
         <v>46282</v>
       </c>
       <c r="D58" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G58">
         <v>0</v>
@@ -12064,16 +12061,16 @@
         <v>0</v>
       </c>
       <c r="I58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K58">
         <v>0</v>
       </c>
       <c r="L58">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -12081,19 +12078,19 @@
         <v>2</v>
       </c>
       <c r="B59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C59" s="2">
         <v>46282</v>
       </c>
       <c r="D59" t="s">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G59">
         <v>0</v>
@@ -12105,7 +12102,7 @@
         <v>0</v>
       </c>
       <c r="J59">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K59">
         <v>0</v>
@@ -12116,16 +12113,16 @@
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B60" t="s">
         <v>45</v>
       </c>
       <c r="C60" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D60" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -12154,19 +12151,19 @@
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B61" t="s">
         <v>45</v>
       </c>
       <c r="C61" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D61" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -12192,16 +12189,16 @@
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B62" t="s">
         <v>45</v>
       </c>
       <c r="C62" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D62" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -12219,7 +12216,7 @@
         <v>0</v>
       </c>
       <c r="J62">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K62">
         <v>0</v>
@@ -12230,16 +12227,16 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B63" t="s">
         <v>45</v>
       </c>
       <c r="C63" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D63" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -12254,7 +12251,7 @@
         <v>0</v>
       </c>
       <c r="I63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J63">
         <v>0</v>
@@ -12268,22 +12265,22 @@
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B64" t="s">
         <v>45</v>
       </c>
       <c r="C64" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D64" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G64">
         <v>0</v>
@@ -12295,7 +12292,7 @@
         <v>0</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K64">
         <v>0</v>
@@ -12306,16 +12303,16 @@
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B65" t="s">
         <v>45</v>
       </c>
       <c r="C65" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D65" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -12344,16 +12341,16 @@
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B66" t="s">
         <v>45</v>
       </c>
       <c r="C66" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D66" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -12371,7 +12368,7 @@
         <v>0</v>
       </c>
       <c r="J66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K66">
         <v>0</v>
@@ -12382,16 +12379,16 @@
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B67" t="s">
         <v>45</v>
       </c>
       <c r="C67" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D67" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -12409,7 +12406,7 @@
         <v>0</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K67">
         <v>0</v>
@@ -12420,22 +12417,22 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s">
         <v>45</v>
       </c>
       <c r="C68" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D68" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E68">
         <v>0</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G68">
         <v>0</v>
@@ -12458,22 +12455,22 @@
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B69" t="s">
         <v>45</v>
       </c>
       <c r="C69" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D69" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="E69">
         <v>0</v>
       </c>
       <c r="F69">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G69">
         <v>0</v>
@@ -12496,22 +12493,22 @@
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B70" t="s">
         <v>45</v>
       </c>
       <c r="C70" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D70" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E70">
         <v>0</v>
       </c>
       <c r="F70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70">
         <v>0</v>
@@ -12534,22 +12531,22 @@
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A71">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B71" t="s">
         <v>45</v>
       </c>
       <c r="C71" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D71" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E71">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G71">
         <v>0</v>
@@ -12572,22 +12569,22 @@
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B72" t="s">
         <v>45</v>
       </c>
       <c r="C72" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D72" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E72">
         <v>0</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G72">
         <v>0</v>
@@ -12596,10 +12593,10 @@
         <v>0</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K72">
         <v>0</v>
@@ -12610,19 +12607,19 @@
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B73" t="s">
         <v>45</v>
       </c>
       <c r="C73" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D73" t="s">
         <v>31</v>
       </c>
       <c r="E73">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -12648,16 +12645,16 @@
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B74" t="s">
         <v>45</v>
       </c>
       <c r="C74" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D74" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -12672,10 +12669,10 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J74">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K74">
         <v>0</v>
@@ -12686,16 +12683,16 @@
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B75" t="s">
         <v>45</v>
       </c>
       <c r="C75" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D75" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -12724,16 +12721,16 @@
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B76" t="s">
         <v>45</v>
       </c>
       <c r="C76" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D76" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -12757,18 +12754,18 @@
         <v>0</v>
       </c>
       <c r="L76">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B77" t="s">
         <v>45</v>
       </c>
       <c r="C77" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D77" t="s">
         <v>34</v>
@@ -12780,10 +12777,10 @@
         <v>0</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -12800,16 +12797,16 @@
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B78" t="s">
         <v>45</v>
       </c>
       <c r="C78" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D78" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -12838,16 +12835,16 @@
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B79" t="s">
         <v>45</v>
       </c>
       <c r="C79" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D79" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -12859,7 +12856,7 @@
         <v>0</v>
       </c>
       <c r="H79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I79">
         <v>0</v>
@@ -12876,16 +12873,16 @@
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B80" t="s">
         <v>45</v>
       </c>
       <c r="C80" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D80" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -12914,16 +12911,16 @@
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B81" t="s">
         <v>45</v>
       </c>
       <c r="C81" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D81" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -12941,10 +12938,10 @@
         <v>0</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K81">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L81">
         <v>0</v>
@@ -12952,22 +12949,22 @@
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B82" t="s">
         <v>45</v>
       </c>
       <c r="C82" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D82" t="s">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="E82">
         <v>0</v>
       </c>
       <c r="F82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G82">
         <v>0</v>
@@ -12976,10 +12973,10 @@
         <v>0</v>
       </c>
       <c r="I82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J82">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K82">
         <v>0</v>
@@ -12990,22 +12987,22 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B83" t="s">
         <v>45</v>
       </c>
       <c r="C83" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D83" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="E83">
         <v>0</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -13014,30 +13011,30 @@
         <v>0</v>
       </c>
       <c r="I83">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J83">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K83">
         <v>0</v>
       </c>
       <c r="L83">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B84" t="s">
         <v>45</v>
       </c>
       <c r="C84" s="2">
-        <v>46285</v>
+        <v>46282</v>
       </c>
       <c r="D84" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -13069,31 +13066,31 @@
         <v>3</v>
       </c>
       <c r="B85" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C85" s="2">
         <v>46285</v>
       </c>
       <c r="D85" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H85">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J85">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K85">
         <v>0</v>
@@ -13107,19 +13104,19 @@
         <v>3</v>
       </c>
       <c r="B86" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C86" s="2">
         <v>46285</v>
       </c>
       <c r="D86" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F86">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G86">
         <v>0</v>
@@ -13131,7 +13128,7 @@
         <v>0</v>
       </c>
       <c r="J86">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K86">
         <v>0</v>
@@ -13145,19 +13142,19 @@
         <v>3</v>
       </c>
       <c r="B87" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C87" s="2">
         <v>46285</v>
       </c>
       <c r="D87" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="E87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G87">
         <v>0</v>
@@ -13169,10 +13166,10 @@
         <v>1</v>
       </c>
       <c r="J87">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K87">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L87">
         <v>0</v>
@@ -13183,13 +13180,13 @@
         <v>3</v>
       </c>
       <c r="B88" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C88" s="2">
         <v>46285</v>
       </c>
       <c r="D88" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -13207,7 +13204,7 @@
         <v>0</v>
       </c>
       <c r="J88">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K88">
         <v>0</v>
@@ -13218,16 +13215,16 @@
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B89" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C89" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D89" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -13256,16 +13253,16 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B90" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C90" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D90" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -13283,7 +13280,7 @@
         <v>0</v>
       </c>
       <c r="J90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K90">
         <v>0</v>
@@ -13294,22 +13291,22 @@
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B91" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C91" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D91" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="E91">
         <v>0</v>
       </c>
       <c r="F91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G91">
         <v>0</v>
@@ -13321,7 +13318,7 @@
         <v>0</v>
       </c>
       <c r="J91">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K91">
         <v>0</v>
@@ -13332,22 +13329,22 @@
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B92" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C92" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D92" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="E92">
         <v>0</v>
       </c>
       <c r="F92">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G92">
         <v>0</v>
@@ -13370,22 +13367,22 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B93" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C93" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D93" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="E93">
         <v>0</v>
       </c>
       <c r="F93">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G93">
         <v>0</v>
@@ -13408,22 +13405,22 @@
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B94" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C94" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D94" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="E94">
         <v>0</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94">
         <v>0</v>
@@ -13446,34 +13443,34 @@
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95">
+        <v>3</v>
+      </c>
+      <c r="B95" t="s">
+        <v>44</v>
+      </c>
+      <c r="C95" s="2">
+        <v>46285</v>
+      </c>
+      <c r="D95" t="s">
+        <v>32</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>2</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
         <v>4</v>
-      </c>
-      <c r="B95" t="s">
-        <v>47</v>
-      </c>
-      <c r="C95" s="2">
-        <v>46291</v>
-      </c>
-      <c r="D95" t="s">
-        <v>18</v>
-      </c>
-      <c r="E95">
-        <v>0</v>
-      </c>
-      <c r="F95">
-        <v>0</v>
-      </c>
-      <c r="G95">
-        <v>0</v>
-      </c>
-      <c r="H95">
-        <v>0</v>
-      </c>
-      <c r="I95">
-        <v>2</v>
-      </c>
-      <c r="J95">
-        <v>0</v>
       </c>
       <c r="K95">
         <v>0</v>
@@ -13484,16 +13481,16 @@
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B96" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C96" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D96" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -13508,10 +13505,10 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J96">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K96">
         <v>0</v>
@@ -13522,22 +13519,22 @@
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B97" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C97" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D97" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="E97">
         <v>0</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97">
         <v>0</v>
@@ -13546,10 +13543,10 @@
         <v>0</v>
       </c>
       <c r="I97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J97">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K97">
         <v>0</v>
@@ -13560,16 +13557,16 @@
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B98" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C98" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D98" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -13587,7 +13584,7 @@
         <v>0</v>
       </c>
       <c r="J98">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K98">
         <v>0</v>
@@ -13598,16 +13595,16 @@
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B99" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C99" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D99" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -13616,10 +13613,10 @@
         <v>0</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H99">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -13636,22 +13633,22 @@
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B100" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C100" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D100" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="E100">
         <v>0</v>
       </c>
       <c r="F100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G100">
         <v>0</v>
@@ -13663,7 +13660,7 @@
         <v>0</v>
       </c>
       <c r="J100">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K100">
         <v>0</v>
@@ -13674,28 +13671,28 @@
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B101" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C101" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D101" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="E101">
         <v>0</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101">
         <v>0</v>
       </c>
       <c r="H101">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I101">
         <v>0</v>
@@ -13712,16 +13709,16 @@
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B102" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C102" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D102" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -13750,22 +13747,22 @@
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B103" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C103" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D103" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="E103">
         <v>0</v>
       </c>
       <c r="F103">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G103">
         <v>0</v>
@@ -13780,7 +13777,7 @@
         <v>0</v>
       </c>
       <c r="K103">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L103">
         <v>0</v>
@@ -13788,16 +13785,16 @@
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B104" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C104" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D104" t="s">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -13826,16 +13823,16 @@
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B105" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C105" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D105" t="s">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -13864,16 +13861,16 @@
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B106" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C106" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D106" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -13902,16 +13899,16 @@
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B107" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C107" s="2">
-        <v>46291</v>
+        <v>46285</v>
       </c>
       <c r="D107" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -13943,13 +13940,13 @@
         <v>4</v>
       </c>
       <c r="B108" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C108" s="2">
         <v>46291</v>
       </c>
       <c r="D108" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -13981,13 +13978,13 @@
         <v>4</v>
       </c>
       <c r="B109" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C109" s="2">
         <v>46291</v>
       </c>
       <c r="D109" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -14011,7 +14008,7 @@
         <v>0</v>
       </c>
       <c r="L109">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
@@ -14019,22 +14016,22 @@
         <v>4</v>
       </c>
       <c r="B110" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C110" s="2">
         <v>46291</v>
       </c>
       <c r="D110" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="E110">
         <v>0</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H110">
         <v>0</v>
@@ -14046,7 +14043,7 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L110">
         <v>0</v>
@@ -14057,19 +14054,19 @@
         <v>4</v>
       </c>
       <c r="B111" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C111" s="2">
         <v>46291</v>
       </c>
       <c r="D111" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="E111">
         <v>0</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G111">
         <v>0</v>
@@ -14078,7 +14075,7 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J111">
         <v>0</v>
@@ -14095,19 +14092,19 @@
         <v>4</v>
       </c>
       <c r="B112" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C112" s="2">
         <v>46291</v>
       </c>
       <c r="D112" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E112">
         <v>0</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G112">
         <v>0</v>
@@ -14133,13 +14130,13 @@
         <v>4</v>
       </c>
       <c r="B113" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C113" s="2">
         <v>46291</v>
       </c>
       <c r="D113" t="s">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E113">
         <v>0</v>
@@ -14157,7 +14154,7 @@
         <v>0</v>
       </c>
       <c r="J113">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K113">
         <v>0</v>
@@ -14171,13 +14168,13 @@
         <v>4</v>
       </c>
       <c r="B114" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C114" s="2">
         <v>46291</v>
       </c>
       <c r="D114" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -14192,7 +14189,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J114">
         <v>0</v>
@@ -14209,19 +14206,19 @@
         <v>4</v>
       </c>
       <c r="B115" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C115" s="2">
         <v>46291</v>
       </c>
       <c r="D115" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="E115">
         <v>0</v>
       </c>
       <c r="F115">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -14247,19 +14244,19 @@
         <v>4</v>
       </c>
       <c r="B116" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C116" s="2">
         <v>46291</v>
       </c>
       <c r="D116" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="E116">
         <v>0</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116">
         <v>0</v>
@@ -14268,10 +14265,10 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J116">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K116">
         <v>0</v>
@@ -14285,13 +14282,13 @@
         <v>4</v>
       </c>
       <c r="B117" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C117" s="2">
         <v>46291</v>
       </c>
       <c r="D117" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -14309,7 +14306,7 @@
         <v>0</v>
       </c>
       <c r="J117">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K117">
         <v>0</v>
@@ -14323,13 +14320,13 @@
         <v>4</v>
       </c>
       <c r="B118" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C118" s="2">
         <v>46291</v>
       </c>
       <c r="D118" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -14361,31 +14358,31 @@
         <v>4</v>
       </c>
       <c r="B119" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C119" s="2">
         <v>46291</v>
       </c>
       <c r="D119" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="E119">
         <v>0</v>
       </c>
       <c r="F119">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H119">
         <v>0</v>
       </c>
       <c r="I119">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J119">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K119">
         <v>0</v>
@@ -14399,19 +14396,19 @@
         <v>4</v>
       </c>
       <c r="B120" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C120" s="2">
         <v>46291</v>
       </c>
       <c r="D120" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E120">
         <v>0</v>
       </c>
       <c r="F120">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G120">
         <v>0</v>
@@ -14420,16 +14417,16 @@
         <v>0</v>
       </c>
       <c r="I120">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J120">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K120">
         <v>0</v>
       </c>
       <c r="L120">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
@@ -14437,19 +14434,19 @@
         <v>4</v>
       </c>
       <c r="B121" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C121" s="2">
         <v>46291</v>
       </c>
       <c r="D121" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E121">
         <v>0</v>
       </c>
       <c r="F121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G121">
         <v>0</v>
@@ -14458,16 +14455,16 @@
         <v>0</v>
       </c>
       <c r="I121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J121">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L121">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
@@ -14475,19 +14472,19 @@
         <v>4</v>
       </c>
       <c r="B122" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C122" s="2">
         <v>46291</v>
       </c>
       <c r="D122" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E122">
         <v>0</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G122">
         <v>0</v>
@@ -14510,22 +14507,22 @@
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B123" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C123" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D123" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="E123">
         <v>0</v>
       </c>
       <c r="F123">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G123">
         <v>0</v>
@@ -14548,22 +14545,22 @@
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B124" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C124" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D124" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="E124">
         <v>0</v>
       </c>
       <c r="F124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G124">
         <v>0</v>
@@ -14575,7 +14572,7 @@
         <v>0</v>
       </c>
       <c r="J124">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124">
         <v>0</v>
@@ -14586,22 +14583,22 @@
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B125" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C125" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D125" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="E125">
         <v>0</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125">
         <v>0</v>
@@ -14613,7 +14610,7 @@
         <v>0</v>
       </c>
       <c r="J125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K125">
         <v>0</v>
@@ -14624,22 +14621,22 @@
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B126" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C126" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D126" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E126">
         <v>0</v>
       </c>
       <c r="F126">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G126">
         <v>0</v>
@@ -14662,22 +14659,22 @@
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B127" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C127" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D127" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E127">
         <v>0</v>
       </c>
       <c r="F127">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G127">
         <v>0</v>
@@ -14689,7 +14686,7 @@
         <v>0</v>
       </c>
       <c r="J127">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K127">
         <v>0</v>
@@ -14700,22 +14697,22 @@
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B128" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C128" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D128" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E128">
         <v>0</v>
       </c>
       <c r="F128">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G128">
         <v>0</v>
@@ -14733,30 +14730,30 @@
         <v>0</v>
       </c>
       <c r="L128">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B129" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C129" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D129" t="s">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="E129">
         <v>0</v>
       </c>
       <c r="F129">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129">
         <v>0</v>
@@ -14768,7 +14765,7 @@
         <v>0</v>
       </c>
       <c r="K129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L129">
         <v>0</v>
@@ -14776,16 +14773,16 @@
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B130" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C130" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D130" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="E130">
         <v>0</v>
@@ -14800,7 +14797,7 @@
         <v>0</v>
       </c>
       <c r="I130">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J130">
         <v>0</v>
@@ -14814,22 +14811,22 @@
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B131" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C131" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D131" t="s">
-        <v>20</v>
+        <v>39</v>
       </c>
       <c r="E131">
         <v>0</v>
       </c>
       <c r="F131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G131">
         <v>0</v>
@@ -14841,7 +14838,7 @@
         <v>0</v>
       </c>
       <c r="J131">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K131">
         <v>0</v>
@@ -14852,34 +14849,34 @@
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B132" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C132" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D132" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="E132">
         <v>0</v>
       </c>
       <c r="F132">
+        <v>0</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>0</v>
+      </c>
+      <c r="J132">
         <v>2</v>
-      </c>
-      <c r="G132">
-        <v>0</v>
-      </c>
-      <c r="H132">
-        <v>0</v>
-      </c>
-      <c r="I132">
-        <v>0</v>
-      </c>
-      <c r="J132">
-        <v>0</v>
       </c>
       <c r="K132">
         <v>0</v>
@@ -14890,13 +14887,13 @@
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B133" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C133" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D133" t="s">
         <v>23</v>
@@ -14928,22 +14925,22 @@
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A134">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B134" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C134" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D134" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="E134">
         <v>0</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G134">
         <v>0</v>
@@ -14966,16 +14963,16 @@
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B135" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C135" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D135" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -15004,22 +15001,22 @@
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B136" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C136" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D136" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="E136">
         <v>0</v>
       </c>
       <c r="F136">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -15031,7 +15028,7 @@
         <v>0</v>
       </c>
       <c r="J136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K136">
         <v>0</v>
@@ -15042,22 +15039,22 @@
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A137">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B137" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C137" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D137" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="E137">
         <v>0</v>
       </c>
       <c r="F137">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G137">
         <v>0</v>
@@ -15069,7 +15066,7 @@
         <v>0</v>
       </c>
       <c r="J137">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K137">
         <v>0</v>
@@ -15080,34 +15077,34 @@
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138">
+        <v>4</v>
+      </c>
+      <c r="B138" t="s">
+        <v>46</v>
+      </c>
+      <c r="C138" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D138" t="s">
+        <v>14</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
         <v>5</v>
       </c>
-      <c r="B138" t="s">
-        <v>54</v>
-      </c>
-      <c r="C138" s="2">
-        <v>46304</v>
-      </c>
-      <c r="D138" t="s">
-        <v>55</v>
-      </c>
-      <c r="E138">
-        <v>0</v>
-      </c>
-      <c r="F138">
-        <v>0</v>
-      </c>
       <c r="G138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H138">
         <v>0</v>
       </c>
       <c r="I138">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J138">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K138">
         <v>0</v>
@@ -15118,23 +15115,23 @@
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139">
+        <v>4</v>
+      </c>
+      <c r="B139" t="s">
+        <v>46</v>
+      </c>
+      <c r="C139" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D139" t="s">
+        <v>15</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
         <v>5</v>
       </c>
-      <c r="B139" t="s">
-        <v>54</v>
-      </c>
-      <c r="C139" s="2">
-        <v>46304</v>
-      </c>
-      <c r="D139" t="s">
-        <v>25</v>
-      </c>
-      <c r="E139">
-        <v>0</v>
-      </c>
-      <c r="F139">
-        <v>0</v>
-      </c>
       <c r="G139">
         <v>0</v>
       </c>
@@ -15142,68 +15139,68 @@
         <v>0</v>
       </c>
       <c r="I139">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J139">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K139">
         <v>0</v>
       </c>
       <c r="L139">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A140">
+        <v>4</v>
+      </c>
+      <c r="B140" t="s">
+        <v>46</v>
+      </c>
+      <c r="C140" s="2">
+        <v>46291</v>
+      </c>
+      <c r="D140" t="s">
+        <v>16</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>1</v>
+      </c>
+      <c r="J140">
         <v>5</v>
       </c>
-      <c r="B140" t="s">
-        <v>54</v>
-      </c>
-      <c r="C140" s="2">
-        <v>46304</v>
-      </c>
-      <c r="D140" t="s">
-        <v>50</v>
-      </c>
-      <c r="E140">
-        <v>0</v>
-      </c>
-      <c r="F140">
-        <v>1</v>
-      </c>
-      <c r="G140">
-        <v>0</v>
-      </c>
-      <c r="H140">
-        <v>0</v>
-      </c>
-      <c r="I140">
-        <v>0</v>
-      </c>
-      <c r="J140">
-        <v>0</v>
-      </c>
       <c r="K140">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A141">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B141" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C141" s="2">
-        <v>46304</v>
+        <v>46291</v>
       </c>
       <c r="D141" t="s">
-        <v>26</v>
+        <v>56</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -15235,19 +15232,19 @@
         <v>5</v>
       </c>
       <c r="B142" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C142" s="2">
         <v>46304</v>
       </c>
       <c r="D142" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="E142">
         <v>0</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G142">
         <v>0</v>
@@ -15273,19 +15270,19 @@
         <v>5</v>
       </c>
       <c r="B143" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C143" s="2">
         <v>46304</v>
       </c>
       <c r="D143" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="E143">
         <v>0</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G143">
         <v>0</v>
@@ -15297,7 +15294,7 @@
         <v>0</v>
       </c>
       <c r="J143">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K143">
         <v>0</v>
@@ -15311,19 +15308,19 @@
         <v>5</v>
       </c>
       <c r="B144" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C144" s="2">
         <v>46304</v>
       </c>
       <c r="D144" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E144">
         <v>0</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144">
         <v>0</v>
@@ -15335,13 +15332,13 @@
         <v>0</v>
       </c>
       <c r="J144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K144">
         <v>0</v>
       </c>
       <c r="L144">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
@@ -15349,19 +15346,19 @@
         <v>5</v>
       </c>
       <c r="B145" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C145" s="2">
         <v>46304</v>
       </c>
       <c r="D145" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E145">
         <v>0</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G145">
         <v>0</v>
@@ -15379,7 +15376,7 @@
         <v>0</v>
       </c>
       <c r="L145">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
@@ -15387,31 +15384,31 @@
         <v>5</v>
       </c>
       <c r="B146" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C146" s="2">
         <v>46304</v>
       </c>
       <c r="D146" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="E146">
         <v>0</v>
       </c>
       <c r="F146">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G146">
         <v>0</v>
       </c>
       <c r="H146">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I146">
         <v>0</v>
       </c>
       <c r="J146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K146">
         <v>0</v>
@@ -15425,25 +15422,25 @@
         <v>5</v>
       </c>
       <c r="B147" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C147" s="2">
         <v>46304</v>
       </c>
       <c r="D147" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="E147">
         <v>0</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H147">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I147">
         <v>0</v>
@@ -15455,7 +15452,7 @@
         <v>0</v>
       </c>
       <c r="L147">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
@@ -15463,19 +15460,19 @@
         <v>5</v>
       </c>
       <c r="B148" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C148" s="2">
         <v>46304</v>
       </c>
       <c r="D148" t="s">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="E148">
         <v>0</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G148">
         <v>0</v>
@@ -15501,13 +15498,13 @@
         <v>5</v>
       </c>
       <c r="B149" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C149" s="2">
         <v>46304</v>
       </c>
       <c r="D149" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -15539,19 +15536,19 @@
         <v>5</v>
       </c>
       <c r="B150" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C150" s="2">
         <v>46304</v>
       </c>
       <c r="D150" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="E150">
         <v>0</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G150">
         <v>0</v>
@@ -15563,7 +15560,7 @@
         <v>0</v>
       </c>
       <c r="J150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K150">
         <v>0</v>
@@ -15577,37 +15574,37 @@
         <v>5</v>
       </c>
       <c r="B151" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C151" s="2">
         <v>46304</v>
       </c>
       <c r="D151" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E151">
         <v>0</v>
       </c>
       <c r="F151">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G151">
         <v>0</v>
       </c>
       <c r="H151">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I151">
         <v>0</v>
       </c>
       <c r="J151">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K151">
         <v>0</v>
       </c>
       <c r="L151">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
@@ -15615,19 +15612,19 @@
         <v>5</v>
       </c>
       <c r="B152" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C152" s="2">
         <v>46304</v>
       </c>
       <c r="D152" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E152">
         <v>0</v>
       </c>
       <c r="F152">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G152">
         <v>0</v>
@@ -15639,7 +15636,7 @@
         <v>0</v>
       </c>
       <c r="J152">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K152">
         <v>0</v>
@@ -15653,31 +15650,31 @@
         <v>5</v>
       </c>
       <c r="B153" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C153" s="2">
         <v>46304</v>
       </c>
       <c r="D153" t="s">
-        <v>16</v>
+        <v>48</v>
       </c>
       <c r="E153">
         <v>0</v>
       </c>
       <c r="F153">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G153">
         <v>0</v>
       </c>
       <c r="H153">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I153">
         <v>0</v>
       </c>
       <c r="J153">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K153">
         <v>0</v>
@@ -15691,22 +15688,22 @@
         <v>5</v>
       </c>
       <c r="B154" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C154" s="2">
         <v>46304</v>
       </c>
       <c r="D154" t="s">
-        <v>57</v>
+        <v>22</v>
       </c>
       <c r="E154">
         <v>0</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H154">
         <v>0</v>
@@ -15715,7 +15712,7 @@
         <v>0</v>
       </c>
       <c r="J154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K154">
         <v>0</v>
@@ -15726,16 +15723,16 @@
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B155" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C155" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D155" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -15753,7 +15750,7 @@
         <v>0</v>
       </c>
       <c r="J155">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K155">
         <v>0</v>
@@ -15764,16 +15761,16 @@
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B156" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C156" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D156" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -15791,7 +15788,7 @@
         <v>0</v>
       </c>
       <c r="J156">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K156">
         <v>0</v>
@@ -15802,22 +15799,22 @@
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B157" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C157" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D157" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E157">
         <v>0</v>
       </c>
       <c r="F157">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G157">
         <v>0</v>
@@ -15829,7 +15826,7 @@
         <v>0</v>
       </c>
       <c r="J157">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K157">
         <v>0</v>
@@ -15840,22 +15837,22 @@
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B158" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C158" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D158" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="E158">
         <v>0</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G158">
         <v>0</v>
@@ -15867,7 +15864,7 @@
         <v>0</v>
       </c>
       <c r="J158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158">
         <v>0</v>
@@ -15878,19 +15875,19 @@
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B159" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C159" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D159" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E159">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F159">
         <v>0</v>
@@ -15905,7 +15902,7 @@
         <v>0</v>
       </c>
       <c r="J159">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K159">
         <v>0</v>
@@ -15916,16 +15913,16 @@
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B160" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C160" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D160" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -15954,22 +15951,22 @@
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A161">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B161" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C161" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D161" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E161">
         <v>0</v>
       </c>
       <c r="F161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161">
         <v>0</v>
@@ -15981,7 +15978,7 @@
         <v>0</v>
       </c>
       <c r="J161">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K161">
         <v>0</v>
@@ -15992,16 +15989,16 @@
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A162">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B162" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C162" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D162" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -16025,21 +16022,21 @@
         <v>0</v>
       </c>
       <c r="L162">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A163">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B163" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C163" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D163" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -16063,33 +16060,33 @@
         <v>0</v>
       </c>
       <c r="L163">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A164">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B164" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C164" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D164" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="E164">
         <v>0</v>
       </c>
       <c r="F164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G164">
         <v>0</v>
       </c>
       <c r="H164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I164">
         <v>0</v>
@@ -16106,16 +16103,16 @@
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A165">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B165" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C165" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D165" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -16124,10 +16121,10 @@
         <v>0</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I165">
         <v>0</v>
@@ -16139,21 +16136,21 @@
         <v>0</v>
       </c>
       <c r="L165">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A166">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B166" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C166" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D166" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -16182,16 +16179,16 @@
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A167">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B167" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C167" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D167" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -16220,16 +16217,16 @@
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A168">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B168" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C168" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D168" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -16247,7 +16244,7 @@
         <v>0</v>
       </c>
       <c r="J168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K168">
         <v>0</v>
@@ -16258,60 +16255,60 @@
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A169">
+        <v>5</v>
+      </c>
+      <c r="B169" t="s">
+        <v>53</v>
+      </c>
+      <c r="C169" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D169" t="s">
+        <v>14</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
+      <c r="F169">
         <v>6</v>
       </c>
-      <c r="B169" t="s">
-        <v>56</v>
-      </c>
-      <c r="C169" s="2">
-        <v>46306</v>
-      </c>
-      <c r="D169" t="s">
-        <v>39</v>
-      </c>
-      <c r="E169">
-        <v>0</v>
-      </c>
-      <c r="F169">
-        <v>0</v>
-      </c>
       <c r="G169">
         <v>0</v>
       </c>
       <c r="H169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I169">
         <v>0</v>
       </c>
       <c r="J169">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K169">
         <v>0</v>
       </c>
       <c r="L169">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A170">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B170" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C170" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D170" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E170">
         <v>0</v>
       </c>
       <c r="F170">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G170">
         <v>0</v>
@@ -16323,7 +16320,7 @@
         <v>0</v>
       </c>
       <c r="J170">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K170">
         <v>0</v>
@@ -16334,34 +16331,34 @@
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A171">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B171" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C171" s="2">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="D171" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="E171">
         <v>0</v>
       </c>
       <c r="F171">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G171">
         <v>0</v>
       </c>
       <c r="H171">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I171">
         <v>0</v>
       </c>
       <c r="J171">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K171">
         <v>0</v>
@@ -16372,34 +16369,34 @@
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A172">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B172" t="s">
+        <v>53</v>
+      </c>
+      <c r="C172" s="2">
+        <v>46304</v>
+      </c>
+      <c r="D172" t="s">
         <v>56</v>
       </c>
-      <c r="C172" s="2">
-        <v>46306</v>
-      </c>
-      <c r="D172" t="s">
-        <v>31</v>
-      </c>
       <c r="E172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F172">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G172">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H172">
         <v>0</v>
       </c>
       <c r="I172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K172">
         <v>0</v>
@@ -16413,19 +16410,19 @@
         <v>6</v>
       </c>
       <c r="B173" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C173" s="2">
         <v>46306</v>
       </c>
       <c r="D173" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="E173">
         <v>0</v>
       </c>
       <c r="F173">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G173">
         <v>0</v>
@@ -16437,7 +16434,7 @@
         <v>0</v>
       </c>
       <c r="J173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K173">
         <v>0</v>
@@ -16451,13 +16448,13 @@
         <v>6</v>
       </c>
       <c r="B174" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C174" s="2">
         <v>46306</v>
       </c>
       <c r="D174" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -16475,7 +16472,7 @@
         <v>0</v>
       </c>
       <c r="J174">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K174">
         <v>0</v>
@@ -16489,19 +16486,19 @@
         <v>6</v>
       </c>
       <c r="B175" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C175" s="2">
         <v>46306</v>
       </c>
       <c r="D175" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E175">
         <v>0</v>
       </c>
       <c r="F175">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G175">
         <v>0</v>
@@ -16513,7 +16510,7 @@
         <v>0</v>
       </c>
       <c r="J175">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K175">
         <v>0</v>
@@ -16527,13 +16524,13 @@
         <v>6</v>
       </c>
       <c r="B176" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C176" s="2">
         <v>46306</v>
       </c>
       <c r="D176" t="s">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -16551,7 +16548,7 @@
         <v>0</v>
       </c>
       <c r="J176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K176">
         <v>0</v>
@@ -16565,13 +16562,13 @@
         <v>6</v>
       </c>
       <c r="B177" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C177" s="2">
         <v>46306</v>
       </c>
       <c r="D177" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -16603,19 +16600,19 @@
         <v>6</v>
       </c>
       <c r="B178" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C178" s="2">
         <v>46306</v>
       </c>
       <c r="D178" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E178">
         <v>0</v>
       </c>
       <c r="F178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G178">
         <v>0</v>
@@ -16627,13 +16624,13 @@
         <v>0</v>
       </c>
       <c r="J178">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K178">
         <v>0</v>
       </c>
       <c r="L178">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
@@ -16641,19 +16638,19 @@
         <v>6</v>
       </c>
       <c r="B179" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C179" s="2">
         <v>46306</v>
       </c>
       <c r="D179" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E179">
         <v>0</v>
       </c>
       <c r="F179">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G179">
         <v>0</v>
@@ -16665,7 +16662,7 @@
         <v>0</v>
       </c>
       <c r="J179">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K179">
         <v>0</v>
@@ -16679,13 +16676,13 @@
         <v>6</v>
       </c>
       <c r="B180" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C180" s="2">
         <v>46306</v>
       </c>
       <c r="D180" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -16703,7 +16700,7 @@
         <v>0</v>
       </c>
       <c r="J180">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K180">
         <v>0</v>
@@ -16717,19 +16714,19 @@
         <v>6</v>
       </c>
       <c r="B181" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C181" s="2">
         <v>46306</v>
       </c>
       <c r="D181" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="E181">
         <v>0</v>
       </c>
       <c r="F181">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G181">
         <v>0</v>
@@ -16741,13 +16738,13 @@
         <v>0</v>
       </c>
       <c r="J181">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K181">
         <v>0</v>
       </c>
       <c r="L181">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
@@ -16755,19 +16752,19 @@
         <v>6</v>
       </c>
       <c r="B182" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C182" s="2">
         <v>46306</v>
       </c>
       <c r="D182" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E182">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F182">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G182">
         <v>0</v>
@@ -16779,7 +16776,7 @@
         <v>0</v>
       </c>
       <c r="J182">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K182">
         <v>0</v>
@@ -16793,19 +16790,19 @@
         <v>6</v>
       </c>
       <c r="B183" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C183" s="2">
         <v>46306</v>
       </c>
       <c r="D183" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E183">
         <v>0</v>
       </c>
       <c r="F183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G183">
         <v>0</v>
@@ -16814,16 +16811,16 @@
         <v>0</v>
       </c>
       <c r="I183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J183">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K183">
         <v>0</v>
       </c>
       <c r="L183">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
@@ -16831,13 +16828,13 @@
         <v>6</v>
       </c>
       <c r="B184" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C184" s="2">
         <v>46306</v>
       </c>
       <c r="D184" t="s">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -16866,34 +16863,34 @@
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A185">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B185" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C185" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D185" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="E185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F185">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G185">
         <v>0</v>
       </c>
       <c r="H185">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I185">
         <v>0</v>
       </c>
       <c r="J185">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K185">
         <v>0</v>
@@ -16904,72 +16901,72 @@
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A186">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B186" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C186" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D186" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F186">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G186">
         <v>0</v>
       </c>
       <c r="H186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I186">
         <v>0</v>
       </c>
       <c r="J186">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K186">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L186">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="187" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A187">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B187" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C187" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D187" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="E187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F187">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H187">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I187">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J187">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K187">
         <v>0</v>
@@ -16980,16 +16977,16 @@
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A188">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B188" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C188" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D188" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -17018,22 +17015,22 @@
     </row>
     <row r="189" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A189">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B189" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C189" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D189" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F189">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G189">
         <v>0</v>
@@ -17045,7 +17042,7 @@
         <v>0</v>
       </c>
       <c r="J189">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K189">
         <v>0</v>
@@ -17056,22 +17053,22 @@
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A190">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B190" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C190" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D190" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="E190">
         <v>0</v>
       </c>
       <c r="F190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G190">
         <v>0</v>
@@ -17094,22 +17091,22 @@
     </row>
     <row r="191" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A191">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B191" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C191" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D191" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F191">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G191">
         <v>0</v>
@@ -17121,7 +17118,7 @@
         <v>0</v>
       </c>
       <c r="J191">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K191">
         <v>0</v>
@@ -17132,22 +17129,22 @@
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A192">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B192" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C192" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D192" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F192">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G192">
         <v>0</v>
@@ -17159,7 +17156,7 @@
         <v>0</v>
       </c>
       <c r="J192">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K192">
         <v>0</v>
@@ -17170,19 +17167,19 @@
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B193" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C193" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D193" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="E193">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F193">
         <v>0</v>
@@ -17208,16 +17205,16 @@
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B194" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C194" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D194" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -17232,7 +17229,7 @@
         <v>0</v>
       </c>
       <c r="I194">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J194">
         <v>0</v>
@@ -17241,27 +17238,27 @@
         <v>0</v>
       </c>
       <c r="L194">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B195" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C195" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D195" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E195">
         <v>0</v>
       </c>
       <c r="F195">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G195">
         <v>0</v>
@@ -17273,7 +17270,7 @@
         <v>0</v>
       </c>
       <c r="J195">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K195">
         <v>0</v>
@@ -17284,16 +17281,16 @@
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B196" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C196" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D196" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -17311,7 +17308,7 @@
         <v>0</v>
       </c>
       <c r="J196">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K196">
         <v>0</v>
@@ -17322,23 +17319,23 @@
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197">
+        <v>6</v>
+      </c>
+      <c r="B197" t="s">
+        <v>55</v>
+      </c>
+      <c r="C197" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D197" t="s">
+        <v>14</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+      <c r="F197">
         <v>7</v>
       </c>
-      <c r="B197" t="s">
-        <v>56</v>
-      </c>
-      <c r="C197" s="2">
-        <v>46309</v>
-      </c>
-      <c r="D197" t="s">
-        <v>49</v>
-      </c>
-      <c r="E197">
-        <v>1</v>
-      </c>
-      <c r="F197">
-        <v>0</v>
-      </c>
       <c r="G197">
         <v>0</v>
       </c>
@@ -17346,36 +17343,36 @@
         <v>0</v>
       </c>
       <c r="I197">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J197">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K197">
         <v>0</v>
       </c>
       <c r="L197">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B198" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C198" s="2">
-        <v>46309</v>
+        <v>46306</v>
       </c>
       <c r="D198" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E198">
         <v>0</v>
       </c>
       <c r="F198">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -17384,33 +17381,33 @@
         <v>0</v>
       </c>
       <c r="I198">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J198">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K198">
         <v>0</v>
       </c>
       <c r="L198">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B199" t="s">
+        <v>55</v>
+      </c>
+      <c r="C199" s="2">
+        <v>46306</v>
+      </c>
+      <c r="D199" t="s">
         <v>56</v>
       </c>
-      <c r="C199" s="2">
-        <v>46309</v>
-      </c>
-      <c r="D199" t="s">
-        <v>21</v>
-      </c>
       <c r="E199">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -17425,7 +17422,7 @@
         <v>0</v>
       </c>
       <c r="J199">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K199">
         <v>0</v>
@@ -17439,19 +17436,19 @@
         <v>7</v>
       </c>
       <c r="B200" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C200" s="2">
         <v>46309</v>
       </c>
       <c r="D200" t="s">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="E200">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G200">
         <v>0</v>
@@ -17463,7 +17460,7 @@
         <v>0</v>
       </c>
       <c r="J200">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K200">
         <v>0</v>
@@ -17477,19 +17474,19 @@
         <v>7</v>
       </c>
       <c r="B201" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C201" s="2">
         <v>46309</v>
       </c>
       <c r="D201" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="E201">
         <v>0</v>
       </c>
       <c r="F201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G201">
         <v>0</v>
@@ -17501,7 +17498,7 @@
         <v>0</v>
       </c>
       <c r="J201">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K201">
         <v>0</v>
@@ -17515,13 +17512,13 @@
         <v>7</v>
       </c>
       <c r="B202" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C202" s="2">
         <v>46309</v>
       </c>
       <c r="D202" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -17536,7 +17533,7 @@
         <v>0</v>
       </c>
       <c r="I202">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J202">
         <v>0</v>
@@ -17553,16 +17550,16 @@
         <v>7</v>
       </c>
       <c r="B203" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C203" s="2">
         <v>46309</v>
       </c>
       <c r="D203" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="E203">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F203">
         <v>0</v>
@@ -17591,13 +17588,13 @@
         <v>7</v>
       </c>
       <c r="B204" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C204" s="2">
         <v>46309</v>
       </c>
       <c r="D204" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -17629,19 +17626,19 @@
         <v>7</v>
       </c>
       <c r="B205" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C205" s="2">
         <v>46309</v>
       </c>
       <c r="D205" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="E205">
         <v>0</v>
       </c>
       <c r="F205">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G205">
         <v>0</v>
@@ -17667,13 +17664,13 @@
         <v>7</v>
       </c>
       <c r="B206" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C206" s="2">
         <v>46309</v>
       </c>
       <c r="D206" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -17705,16 +17702,16 @@
         <v>7</v>
       </c>
       <c r="B207" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C207" s="2">
         <v>46309</v>
       </c>
       <c r="D207" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F207">
         <v>0</v>
@@ -17723,7 +17720,7 @@
         <v>0</v>
       </c>
       <c r="H207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I207">
         <v>0</v>
@@ -17732,10 +17729,10 @@
         <v>0</v>
       </c>
       <c r="K207">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L207">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.2">
@@ -17743,13 +17740,13 @@
         <v>7</v>
       </c>
       <c r="B208" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C208" s="2">
         <v>46309</v>
       </c>
       <c r="D208" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -17781,19 +17778,19 @@
         <v>7</v>
       </c>
       <c r="B209" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C209" s="2">
         <v>46309</v>
       </c>
       <c r="D209" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="E209">
         <v>0</v>
       </c>
       <c r="F209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G209">
         <v>0</v>
@@ -17805,7 +17802,7 @@
         <v>0</v>
       </c>
       <c r="J209">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K209">
         <v>0</v>
@@ -17819,13 +17816,13 @@
         <v>7</v>
       </c>
       <c r="B210" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C210" s="2">
         <v>46309</v>
       </c>
       <c r="D210" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -17857,13 +17854,13 @@
         <v>7</v>
       </c>
       <c r="B211" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C211" s="2">
         <v>46309</v>
       </c>
       <c r="D211" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -17895,19 +17892,19 @@
         <v>7</v>
       </c>
       <c r="B212" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C212" s="2">
         <v>46309</v>
       </c>
       <c r="D212" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F212">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G212">
         <v>0</v>
@@ -17933,13 +17930,13 @@
         <v>7</v>
       </c>
       <c r="B213" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C213" s="2">
         <v>46309</v>
       </c>
       <c r="D213" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -17968,22 +17965,22 @@
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A214">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B214" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C214" s="2">
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="D214" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="E214">
         <v>0</v>
       </c>
       <c r="F214">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G214">
         <v>0</v>
@@ -17992,39 +17989,39 @@
         <v>0</v>
       </c>
       <c r="I214">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J214">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K214">
         <v>0</v>
       </c>
       <c r="L214">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="215" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A215">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B215" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C215" s="2">
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="D215" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="E215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F215">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H215">
         <v>0</v>
@@ -18033,13 +18030,13 @@
         <v>0</v>
       </c>
       <c r="J215">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K215">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L215">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.2">
@@ -18047,16 +18044,16 @@
         <v>8</v>
       </c>
       <c r="B216" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C216" s="2">
         <v>46311</v>
       </c>
       <c r="D216" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E216">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F216">
         <v>3</v>
@@ -18071,13 +18068,13 @@
         <v>1</v>
       </c>
       <c r="J216">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K216">
         <v>0</v>
       </c>
       <c r="L216">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="217" spans="1:12" x14ac:dyDescent="0.2">
@@ -18085,13 +18082,13 @@
         <v>8</v>
       </c>
       <c r="B217" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C217" s="2">
         <v>46311</v>
       </c>
       <c r="D217" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -18123,13 +18120,13 @@
         <v>8</v>
       </c>
       <c r="B218" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C218" s="2">
         <v>46311</v>
       </c>
       <c r="D218" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -18161,13 +18158,13 @@
         <v>8</v>
       </c>
       <c r="B219" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C219" s="2">
         <v>46311</v>
       </c>
       <c r="D219" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -18199,13 +18196,13 @@
         <v>8</v>
       </c>
       <c r="B220" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C220" s="2">
         <v>46311</v>
       </c>
       <c r="D220" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -18237,13 +18234,13 @@
         <v>8</v>
       </c>
       <c r="B221" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C221" s="2">
         <v>46311</v>
       </c>
       <c r="D221" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -18275,13 +18272,13 @@
         <v>8</v>
       </c>
       <c r="B222" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C222" s="2">
         <v>46311</v>
       </c>
       <c r="D222" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -18313,13 +18310,13 @@
         <v>8</v>
       </c>
       <c r="B223" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C223" s="2">
         <v>46311</v>
       </c>
       <c r="D223" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -18351,13 +18348,13 @@
         <v>8</v>
       </c>
       <c r="B224" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C224" s="2">
         <v>46311</v>
       </c>
       <c r="D224" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -18389,13 +18386,13 @@
         <v>8</v>
       </c>
       <c r="B225" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C225" s="2">
         <v>46311</v>
       </c>
       <c r="D225" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -18427,13 +18424,13 @@
         <v>8</v>
       </c>
       <c r="B226" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C226" s="2">
         <v>46311</v>
       </c>
       <c r="D226" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -18465,7 +18462,7 @@
         <v>8</v>
       </c>
       <c r="B227" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C227" s="2">
         <v>46311</v>
@@ -18503,7 +18500,7 @@
         <v>8</v>
       </c>
       <c r="B228" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C228" s="2">
         <v>46311</v>
@@ -18541,7 +18538,7 @@
         <v>8</v>
       </c>
       <c r="B229" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C229" s="2">
         <v>46311</v>
@@ -18579,13 +18576,13 @@
         <v>8</v>
       </c>
       <c r="B230" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C230" s="2">
         <v>46311</v>
       </c>
       <c r="D230" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -18617,19 +18614,19 @@
         <v>8</v>
       </c>
       <c r="B231" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C231" s="2">
         <v>46311</v>
       </c>
       <c r="D231" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E231">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G231">
         <v>0</v>
@@ -18641,7 +18638,7 @@
         <v>0</v>
       </c>
       <c r="J231">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K231">
         <v>0</v>
@@ -18655,19 +18652,19 @@
         <v>8</v>
       </c>
       <c r="B232" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C232" s="2">
         <v>46311</v>
       </c>
       <c r="D232" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
       <c r="E232">
         <v>0</v>
       </c>
       <c r="F232">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G232">
         <v>0</v>
@@ -18679,10 +18676,10 @@
         <v>0</v>
       </c>
       <c r="J232">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L232">
         <v>0</v>
@@ -18693,13 +18690,13 @@
         <v>8</v>
       </c>
       <c r="B233" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C233" s="2">
         <v>46311</v>
       </c>
       <c r="D233" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -18720,7 +18717,7 @@
         <v>0</v>
       </c>
       <c r="K233">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L233">
         <v>0</v>
@@ -18731,7 +18728,7 @@
         <v>8</v>
       </c>
       <c r="B234" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C234" s="2">
         <v>46311</v>
@@ -18769,13 +18766,13 @@
         <v>8</v>
       </c>
       <c r="B235" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C235" s="2">
         <v>46311</v>
       </c>
       <c r="D235" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -18784,7 +18781,7 @@
         <v>0</v>
       </c>
       <c r="G235">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H235">
         <v>0</v>
@@ -18799,7 +18796,7 @@
         <v>0</v>
       </c>
       <c r="L235">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.2">
@@ -18807,13 +18804,13 @@
         <v>8</v>
       </c>
       <c r="B236" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C236" s="2">
         <v>46311</v>
       </c>
       <c r="D236" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -18822,7 +18819,7 @@
         <v>0</v>
       </c>
       <c r="G236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H236">
         <v>0</v>
@@ -18837,7 +18834,7 @@
         <v>0</v>
       </c>
       <c r="L236">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="237" spans="1:12" x14ac:dyDescent="0.2">
@@ -18845,13 +18842,13 @@
         <v>8</v>
       </c>
       <c r="B237" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C237" s="2">
         <v>46311</v>
       </c>
       <c r="D237" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -18869,7 +18866,7 @@
         <v>0</v>
       </c>
       <c r="J237">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K237">
         <v>0</v>
@@ -18883,7 +18880,7 @@
         <v>8</v>
       </c>
       <c r="B238" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C238" s="2">
         <v>46311</v>
@@ -18921,13 +18918,13 @@
         <v>8</v>
       </c>
       <c r="B239" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C239" s="2">
         <v>46311</v>
       </c>
       <c r="D239" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -18945,7 +18942,7 @@
         <v>0</v>
       </c>
       <c r="J239">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K239">
         <v>0</v>
@@ -18959,7 +18956,7 @@
         <v>8</v>
       </c>
       <c r="B240" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C240" s="2">
         <v>46311</v>
@@ -18983,7 +18980,7 @@
         <v>0</v>
       </c>
       <c r="J240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K240">
         <v>0</v>
@@ -18992,45 +18989,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A241">
-        <v>8</v>
-      </c>
-      <c r="B241" t="s">
-        <v>59</v>
-      </c>
-      <c r="C241" s="2">
-        <v>46311</v>
-      </c>
-      <c r="D241" t="s">
-        <v>40</v>
-      </c>
-      <c r="E241">
-        <v>0</v>
-      </c>
-      <c r="F241">
-        <v>0</v>
-      </c>
-      <c r="G241">
-        <v>0</v>
-      </c>
-      <c r="H241">
-        <v>0</v>
-      </c>
-      <c r="I241">
-        <v>0</v>
-      </c>
-      <c r="J241">
-        <v>1</v>
-      </c>
-      <c r="K241">
-        <v>0</v>
-      </c>
-      <c r="L241">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:L240" xr:uid="{FFE8C601-DC7D-42D2-865D-643789981902}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L240">
+      <sortCondition descending="1" ref="E1:E240"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
